--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA ? (file ?) to FHIR MedicationRequest</t>
+    <t>This StructureDefinition contains the maps for VistA file ? (#?) to us-core-medicationrequest</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1206,7 +1206,7 @@
     <t>PV1-19-Visit Number</t>
   </si>
   <si>
-    <t>++: reference</t>
+    <t>1724: reference</t>
   </si>
   <si>
     <t>MedicationRequest.supportingInformation</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$120</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5132" uniqueCount="818">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4817" uniqueCount="802">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -872,10 +872,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>A code specifying the state of the prescribing event. Describes the lifecycle of the prescription.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFOutMedRequestStatus</t>
   </si>
   <si>
     <t>Request.status</t>
@@ -890,52 +887,7 @@
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>799: transform using VF_OutMedRequestStatus on PRESCRIPTION - STATUS (#52-100)</t>
-  </si>
-  <si>
-    <t>MedicationRequest.status.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.status.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.status.extension:11179-permitted-value-conceptmap</t>
-  </si>
-  <si>
-    <t>MedicationRequest.status.extension:11179-permitted-value-conceptmap.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.status.extension.id</t>
-  </si>
-  <si>
-    <t>MedicationRequest.status.extension:11179-permitted-value-conceptmap.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.status.extension.extension</t>
-  </si>
-  <si>
-    <t>MedicationRequest.status.extension:11179-permitted-value-conceptmap.url</t>
-  </si>
-  <si>
-    <t>MedicationRequest.status.extension.url</t>
-  </si>
-  <si>
-    <t>MedicationRequest.status.extension:11179-permitted-value-conceptmap.value[x]</t>
-  </si>
-  <si>
-    <t>MedicationRequest.status.extension.value[x]</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ConceptMap/CMVFOutMedRequestStatus</t>
-  </si>
-  <si>
-    <t>MedicationRequest.status.value</t>
-  </si>
-  <si>
-    <t>Primitive value for code</t>
-  </si>
-  <si>
-    <t>string.value</t>
+    <t>799: terminologyMaps using VF_OutMedRequestStatus on PRESCRIPTION - STATUS (#52-100)</t>
   </si>
   <si>
     <t>MedicationRequest.statusReason</t>
@@ -2869,7 +2821,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR128"/>
+  <dimension ref="A1:AR120"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="102.30859375" customWidth="true" bestFit="true"/>
@@ -7002,11 +6954,9 @@
       <c r="X33" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="Y33" t="s" s="2">
+      <c r="Y33" s="2"/>
+      <c r="Z33" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>84</v>
@@ -7039,22 +6989,22 @@
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AL33" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AM33" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AN33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP33" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>206</v>
@@ -7065,10 +7015,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -7091,15 +7041,17 @@
         <v>84</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>147</v>
+        <v>283</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>229</v>
+        <v>284</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -7124,13 +7076,13 @@
         <v>84</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>84</v>
+        <v>287</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>84</v>
+        <v>288</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>84</v>
+        <v>289</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>84</v>
@@ -7148,7 +7100,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>150</v>
+        <v>282</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -7160,16 +7112,16 @@
         <v>84</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>84</v>
+        <v>290</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>84</v>
+        <v>291</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>84</v>
@@ -7189,10 +7141,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7200,30 +7152,32 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>140</v>
+        <v>293</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -7248,59 +7202,61 @@
         <v>84</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>84</v>
+        <v>275</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>84</v>
+        <v>296</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>84</v>
+        <v>297</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="AC35" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>156</v>
+        <v>292</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>84</v>
+        <v>298</v>
       </c>
       <c r="AL35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>84</v>
+        <v>299</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>84</v>
+        <v>300</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>84</v>
+        <v>301</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -7311,14 +7267,12 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>84</v>
       </c>
@@ -7327,10 +7281,10 @@
         <v>82</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>84</v>
@@ -7339,16 +7293,16 @@
         <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>234</v>
+        <v>283</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>235</v>
+        <v>303</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>236</v>
+        <v>304</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>237</v>
+        <v>305</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -7374,31 +7328,29 @@
         <v>84</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>84</v>
+        <v>287</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>84</v>
+        <v>306</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>84</v>
+        <v>307</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="AC36" s="2"/>
       <c r="AD36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>156</v>
+        <v>302</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7407,25 +7359,25 @@
         <v>83</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>238</v>
+        <v>84</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>84</v>
+        <v>309</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>137</v>
+        <v>310</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>84</v>
+        <v>300</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="AP36" t="s" s="2">
         <v>84</v>
@@ -7439,12 +7391,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C37" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>312</v>
+      </c>
       <c r="D37" t="s" s="2">
         <v>84</v>
       </c>
@@ -7453,10 +7407,10 @@
         <v>82</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>84</v>
@@ -7465,15 +7419,17 @@
         <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>147</v>
+        <v>283</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>148</v>
+        <v>303</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>304</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>305</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -7498,13 +7454,13 @@
         <v>84</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>84</v>
+        <v>275</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>84</v>
+        <v>313</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>84</v>
+        <v>307</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>84</v>
@@ -7522,31 +7478,31 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>150</v>
+        <v>302</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>84</v>
+        <v>309</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>151</v>
+        <v>310</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>84</v>
+        <v>300</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>84</v>
@@ -7563,10 +7519,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>288</v>
+        <v>314</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>289</v>
+        <v>314</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7577,7 +7533,7 @@
         <v>82</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>84</v>
@@ -7586,16 +7542,16 @@
         <v>84</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>140</v>
+        <v>315</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>141</v>
+        <v>316</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7622,55 +7578,55 @@
         <v>84</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>84</v>
+        <v>275</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>84</v>
+        <v>317</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>84</v>
+        <v>318</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>153</v>
+        <v>84</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>156</v>
+        <v>314</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>84</v>
+        <v>319</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>84</v>
+        <v>320</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>84</v>
+        <v>321</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>84</v>
@@ -7687,10 +7643,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>290</v>
+        <v>322</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>291</v>
+        <v>322</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7698,7 +7654,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
@@ -7707,22 +7663,22 @@
         <v>84</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>108</v>
+        <v>217</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>158</v>
+        <v>323</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>159</v>
+        <v>324</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>160</v>
+        <v>325</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -7730,7 +7686,7 @@
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>245</v>
+        <v>84</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>84</v>
@@ -7772,10 +7728,10 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>161</v>
+        <v>322</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>93</v>
@@ -7784,7 +7740,7 @@
         <v>84</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>84</v>
@@ -7793,7 +7749,7 @@
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>137</v>
+        <v>326</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>84</v>
@@ -7813,10 +7769,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>292</v>
+        <v>327</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>293</v>
+        <v>327</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7824,28 +7780,28 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>248</v>
+        <v>328</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>164</v>
+        <v>329</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>249</v>
+        <v>330</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7857,7 +7813,7 @@
         <v>84</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>294</v>
+        <v>84</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>84</v>
@@ -7896,7 +7852,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>168</v>
+        <v>327</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7917,7 +7873,7 @@
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>137</v>
+        <v>331</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>84</v>
@@ -7937,10 +7893,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>295</v>
+        <v>332</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>295</v>
+        <v>332</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7948,30 +7904,32 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>147</v>
+        <v>333</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>296</v>
+        <v>334</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7996,13 +7954,11 @@
         <v>84</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>84</v>
+        <v>338</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>84</v>
@@ -8020,10 +7976,10 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>297</v>
+        <v>332</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>93</v>
@@ -8032,22 +7988,22 @@
         <v>84</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>84</v>
+        <v>339</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>84</v>
+        <v>340</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>84</v>
+        <v>341</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>84</v>
+        <v>342</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>84</v>
+        <v>343</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>84</v>
@@ -8061,10 +8017,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8072,31 +8028,31 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>299</v>
+        <v>345</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>300</v>
+        <v>346</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>301</v>
+        <v>347</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>302</v>
+        <v>348</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -8122,13 +8078,13 @@
         <v>84</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>303</v>
+        <v>84</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>304</v>
+        <v>84</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>305</v>
+        <v>84</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>84</v>
@@ -8146,10 +8102,10 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>298</v>
+        <v>344</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>93</v>
@@ -8161,22 +8117,22 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>306</v>
+        <v>349</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>84</v>
+        <v>350</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>307</v>
+        <v>351</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>84</v>
+        <v>352</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>84</v>
+        <v>353</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>84</v>
+        <v>354</v>
       </c>
       <c r="AQ42" t="s" s="2">
         <v>84</v>
@@ -8187,10 +8143,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>308</v>
+        <v>355</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>308</v>
+        <v>355</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8198,7 +8154,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>93</v>
@@ -8207,22 +8163,22 @@
         <v>94</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>114</v>
+        <v>356</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>309</v>
+        <v>357</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>310</v>
+        <v>358</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>311</v>
+        <v>359</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -8248,13 +8204,13 @@
         <v>84</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>275</v>
+        <v>84</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>312</v>
+        <v>84</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>313</v>
+        <v>84</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>84</v>
@@ -8272,10 +8228,10 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>308</v>
+        <v>355</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>93</v>
@@ -8287,22 +8243,22 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>314</v>
+        <v>360</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>84</v>
+        <v>278</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>315</v>
+        <v>361</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>316</v>
+        <v>362</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>84</v>
+        <v>363</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>317</v>
+        <v>364</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -8313,10 +8269,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>318</v>
+        <v>365</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>318</v>
+        <v>365</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8330,7 +8286,7 @@
         <v>83</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>84</v>
@@ -8339,17 +8295,15 @@
         <v>84</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>299</v>
+        <v>366</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>319</v>
+        <v>367</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -8374,29 +8328,31 @@
         <v>84</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>303</v>
+        <v>84</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>322</v>
+        <v>84</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>323</v>
+        <v>84</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="AC44" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>318</v>
+        <v>365</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -8411,16 +8367,16 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>84</v>
+        <v>369</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>325</v>
+        <v>84</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>326</v>
+        <v>370</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>316</v>
+        <v>362</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
@@ -8437,14 +8393,12 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>327</v>
+        <v>371</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>328</v>
-      </c>
+        <v>371</v>
+      </c>
+      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>84</v>
       </c>
@@ -8453,7 +8407,7 @@
         <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>94</v>
@@ -8462,20 +8416,18 @@
         <v>84</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>299</v>
+        <v>372</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>319</v>
+        <v>373</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8500,13 +8452,13 @@
         <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>275</v>
+        <v>84</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>329</v>
+        <v>84</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>323</v>
+        <v>84</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -8524,13 +8476,13 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>318</v>
+        <v>371</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>84</v>
@@ -8539,19 +8491,19 @@
         <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>325</v>
+        <v>376</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>326</v>
+        <v>377</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>316</v>
+        <v>378</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>84</v>
+        <v>379</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>84</v>
@@ -8565,10 +8517,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8576,13 +8528,13 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>84</v>
@@ -8591,13 +8543,13 @@
         <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>114</v>
+        <v>381</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>331</v>
+        <v>382</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>332</v>
+        <v>383</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8624,13 +8576,13 @@
         <v>84</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>275</v>
+        <v>84</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>333</v>
+        <v>84</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>334</v>
+        <v>84</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8648,7 +8600,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8663,22 +8615,22 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>335</v>
+        <v>384</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>337</v>
+        <v>385</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>84</v>
+        <v>386</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
@@ -8689,10 +8641,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>338</v>
+        <v>387</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>338</v>
+        <v>387</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8709,23 +8661,21 @@
         <v>84</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>217</v>
+        <v>388</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>339</v>
+        <v>389</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8774,7 +8724,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>338</v>
+        <v>387</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8789,16 +8739,16 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>84</v>
+        <v>391</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>342</v>
+        <v>392</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>84</v>
+        <v>393</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>84</v>
@@ -8815,10 +8765,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>343</v>
+        <v>394</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>343</v>
+        <v>394</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8832,7 +8782,7 @@
         <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>84</v>
@@ -8841,15 +8791,17 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>344</v>
+        <v>283</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>345</v>
+        <v>395</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>396</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>397</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>84</v>
@@ -8874,13 +8826,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>84</v>
+        <v>287</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>84</v>
+        <v>398</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>84</v>
+        <v>399</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8898,7 +8850,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>343</v>
+        <v>394</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8913,13 +8865,13 @@
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>84</v>
+        <v>400</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>347</v>
+        <v>401</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>84</v>
@@ -8939,10 +8891,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>348</v>
+        <v>402</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>348</v>
+        <v>402</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8950,32 +8902,30 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>349</v>
+        <v>403</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>350</v>
+        <v>404</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>405</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -9000,11 +8950,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="Y49" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z49" t="s" s="2">
-        <v>354</v>
+        <v>84</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -9022,10 +8974,10 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>348</v>
+        <v>402</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>93</v>
@@ -9037,19 +8989,19 @@
         <v>106</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>355</v>
+        <v>84</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>356</v>
+        <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>357</v>
+        <v>406</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>358</v>
+        <v>407</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>359</v>
+        <v>84</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>84</v>
@@ -9063,10 +9015,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>360</v>
+        <v>408</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>360</v>
+        <v>408</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9074,31 +9026,31 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>361</v>
+        <v>283</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>362</v>
+        <v>409</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>363</v>
+        <v>410</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>364</v>
+        <v>411</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -9124,13 +9076,13 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>84</v>
+        <v>287</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>84</v>
+        <v>412</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>84</v>
+        <v>413</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -9148,13 +9100,13 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>360</v>
+        <v>408</v>
       </c>
       <c r="AG50" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>84</v>
@@ -9163,22 +9115,22 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>365</v>
+        <v>414</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>366</v>
+        <v>415</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>367</v>
+        <v>416</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>368</v>
+        <v>417</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>369</v>
+        <v>418</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>370</v>
+        <v>84</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
@@ -9189,10 +9141,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>371</v>
+        <v>419</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>371</v>
+        <v>419</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9206,7 +9158,7 @@
         <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>84</v>
@@ -9215,17 +9167,15 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>372</v>
+        <v>147</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>373</v>
+        <v>148</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>375</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>84</v>
@@ -9274,7 +9224,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>371</v>
+        <v>150</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -9286,25 +9236,25 @@
         <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>376</v>
+        <v>84</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>279</v>
+        <v>84</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>377</v>
+        <v>151</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>378</v>
+        <v>84</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>379</v>
+        <v>84</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>380</v>
+        <v>84</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -9315,14 +9265,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>381</v>
+        <v>420</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>381</v>
+        <v>420</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>84</v>
+        <v>176</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -9341,15 +9291,17 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>382</v>
+        <v>139</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>383</v>
+        <v>177</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -9386,19 +9338,19 @@
         <v>84</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>84</v>
+        <v>153</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>381</v>
+        <v>156</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9410,19 +9362,19 @@
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>385</v>
+        <v>84</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>386</v>
+        <v>151</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>378</v>
+        <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>84</v>
@@ -9439,10 +9391,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>387</v>
+        <v>421</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>387</v>
+        <v>421</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9453,10 +9405,10 @@
         <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>84</v>
@@ -9465,16 +9417,20 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>388</v>
+        <v>171</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>389</v>
+        <v>422</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>425</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>84</v>
       </c>
@@ -9522,13 +9478,13 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>387</v>
+        <v>426</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>84</v>
@@ -9537,19 +9493,19 @@
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>391</v>
+        <v>84</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>392</v>
+        <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>393</v>
+        <v>427</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>394</v>
+        <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>395</v>
+        <v>428</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>84</v>
@@ -9563,10 +9519,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>396</v>
+        <v>429</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>396</v>
+        <v>429</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9574,7 +9530,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>93</v>
@@ -9589,16 +9545,20 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>397</v>
+        <v>147</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>398</v>
+        <v>430</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>431</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
       </c>
@@ -9646,7 +9606,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>396</v>
+        <v>434</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9661,22 +9621,22 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>400</v>
+        <v>84</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>367</v>
+        <v>435</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>401</v>
+        <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>84</v>
+        <v>436</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>402</v>
+        <v>437</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
@@ -9687,10 +9647,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>403</v>
+        <v>438</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>403</v>
+        <v>438</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9701,7 +9661,7 @@
         <v>82</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>84</v>
@@ -9713,15 +9673,17 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>404</v>
+        <v>439</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>405</v>
+        <v>440</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>441</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>442</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9770,13 +9732,13 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>403</v>
+        <v>438</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>84</v>
@@ -9785,16 +9747,16 @@
         <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>407</v>
+        <v>443</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>84</v>
+        <v>278</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>408</v>
+        <v>444</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>84</v>
@@ -9811,10 +9773,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>410</v>
+        <v>445</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>410</v>
+        <v>445</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9825,7 +9787,7 @@
         <v>82</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>84</v>
@@ -9837,17 +9799,15 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>299</v>
+        <v>446</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>411</v>
+        <v>447</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>413</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -9872,13 +9832,13 @@
         <v>84</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>303</v>
+        <v>84</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>414</v>
+        <v>84</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>415</v>
+        <v>84</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>84</v>
@@ -9896,13 +9856,13 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>410</v>
+        <v>445</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>84</v>
@@ -9911,13 +9871,13 @@
         <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>416</v>
+        <v>449</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>417</v>
+        <v>450</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>84</v>
@@ -9937,10 +9897,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>418</v>
+        <v>451</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>418</v>
+        <v>451</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9951,7 +9911,7 @@
         <v>82</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>84</v>
@@ -9960,16 +9920,16 @@
         <v>84</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>419</v>
+        <v>108</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>420</v>
+        <v>452</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>421</v>
+        <v>453</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -10020,13 +9980,13 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>418</v>
+        <v>451</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>84</v>
@@ -10041,10 +10001,10 @@
         <v>84</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>422</v>
+        <v>450</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>423</v>
+        <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>84</v>
@@ -10061,10 +10021,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>424</v>
+        <v>454</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>424</v>
+        <v>454</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10084,20 +10044,18 @@
         <v>84</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>299</v>
+        <v>455</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>425</v>
+        <v>456</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>427</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -10122,13 +10080,13 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>303</v>
+        <v>84</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>428</v>
+        <v>84</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>429</v>
+        <v>84</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -10146,7 +10104,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>424</v>
+        <v>454</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -10161,19 +10119,19 @@
         <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>430</v>
+        <v>458</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>431</v>
+        <v>84</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>432</v>
+        <v>459</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>433</v>
+        <v>84</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>434</v>
+        <v>84</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>84</v>
@@ -10187,10 +10145,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>435</v>
+        <v>460</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>435</v>
+        <v>460</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10210,19 +10168,21 @@
         <v>84</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>147</v>
+        <v>262</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>148</v>
+        <v>461</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>149</v>
+        <v>462</v>
       </c>
       <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+      <c r="O59" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
       </c>
@@ -10270,7 +10230,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>150</v>
+        <v>460</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10282,16 +10242,16 @@
         <v>84</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>84</v>
+        <v>464</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>151</v>
+        <v>465</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>84</v>
@@ -10311,21 +10271,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>436</v>
+        <v>466</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>436</v>
+        <v>466</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>176</v>
+        <v>84</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>84</v>
@@ -10337,16 +10297,16 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>139</v>
+        <v>283</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>177</v>
+        <v>467</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>178</v>
+        <v>468</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>179</v>
+        <v>469</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -10372,43 +10332,43 @@
         <v>84</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>84</v>
+        <v>287</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>84</v>
+        <v>470</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>84</v>
+        <v>471</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>153</v>
+        <v>84</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>156</v>
+        <v>466</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>84</v>
@@ -10417,7 +10377,7 @@
         <v>84</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>151</v>
+        <v>472</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>84</v>
@@ -10437,10 +10397,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>437</v>
+        <v>473</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10460,23 +10420,19 @@
         <v>84</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>171</v>
+        <v>474</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>438</v>
+        <v>475</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>84</v>
       </c>
@@ -10524,7 +10480,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>442</v>
+        <v>473</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10539,19 +10495,19 @@
         <v>106</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>84</v>
+        <v>477</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>443</v>
+        <v>478</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>444</v>
+        <v>84</v>
       </c>
       <c r="AP61" t="s" s="2">
         <v>84</v>
@@ -10565,10 +10521,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>445</v>
+        <v>479</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>445</v>
+        <v>479</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10579,32 +10535,28 @@
         <v>82</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>147</v>
+        <v>480</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>446</v>
+        <v>481</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>84</v>
       </c>
@@ -10652,13 +10604,13 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>450</v>
+        <v>479</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>84</v>
@@ -10667,22 +10619,22 @@
         <v>106</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>84</v>
+        <v>483</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>84</v>
+        <v>484</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>451</v>
+        <v>485</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>452</v>
+        <v>84</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>453</v>
+        <v>84</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10693,10 +10645,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>454</v>
+        <v>486</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>454</v>
+        <v>486</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10710,7 +10662,7 @@
         <v>83</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>84</v>
@@ -10719,16 +10671,16 @@
         <v>84</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>455</v>
+        <v>487</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>456</v>
+        <v>488</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>457</v>
+        <v>489</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>458</v>
+        <v>490</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10778,7 +10730,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>454</v>
+        <v>486</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10793,16 +10745,16 @@
         <v>106</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>459</v>
+        <v>491</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>279</v>
+        <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>460</v>
+        <v>492</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>433</v>
+        <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>84</v>
@@ -10819,10 +10771,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>461</v>
+        <v>493</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>461</v>
+        <v>493</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10833,7 +10785,7 @@
         <v>82</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>84</v>
@@ -10842,16 +10794,16 @@
         <v>84</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>462</v>
+        <v>147</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>463</v>
+        <v>148</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>464</v>
+        <v>149</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -10902,28 +10854,28 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>461</v>
+        <v>150</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>465</v>
+        <v>84</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>466</v>
+        <v>151</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>84</v>
@@ -10943,14 +10895,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>467</v>
+        <v>494</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>467</v>
+        <v>494</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>84</v>
+        <v>176</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -10966,18 +10918,20 @@
         <v>84</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>468</v>
+        <v>177</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>84</v>
@@ -11014,19 +10968,19 @@
         <v>84</v>
       </c>
       <c r="AB65" t="s" s="2">
-        <v>84</v>
+        <v>153</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE65" t="s" s="2">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>467</v>
+        <v>156</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -11038,7 +10992,7 @@
         <v>84</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>84</v>
@@ -11047,7 +11001,7 @@
         <v>84</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>466</v>
+        <v>151</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>84</v>
@@ -11067,14 +11021,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>84</v>
+        <v>496</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -11087,22 +11041,26 @@
         <v>84</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="J66" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>471</v>
+        <v>139</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>472</v>
+        <v>497</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>498</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>259</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>84</v>
       </c>
@@ -11150,7 +11108,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>470</v>
+        <v>499</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -11162,16 +11120,16 @@
         <v>84</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>474</v>
+        <v>84</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>475</v>
+        <v>137</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>84</v>
@@ -11191,10 +11149,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>476</v>
+        <v>500</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>476</v>
+        <v>500</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11217,17 +11175,17 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>262</v>
+        <v>501</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>477</v>
+        <v>502</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>478</v>
+        <v>503</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>479</v>
+        <v>504</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
@@ -11276,7 +11234,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>476</v>
+        <v>505</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11291,19 +11249,19 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>480</v>
+        <v>84</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>84</v>
+        <v>507</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>84</v>
@@ -11317,10 +11275,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>482</v>
+        <v>508</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>482</v>
+        <v>508</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11334,27 +11292,27 @@
         <v>93</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>299</v>
+        <v>147</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>483</v>
+        <v>509</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>510</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" t="s" s="2">
+        <v>511</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
       </c>
@@ -11378,13 +11336,13 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>303</v>
+        <v>84</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>486</v>
+        <v>84</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>487</v>
+        <v>84</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>84</v>
@@ -11402,7 +11360,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>482</v>
+        <v>512</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11423,13 +11381,13 @@
         <v>84</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>84</v>
+        <v>513</v>
       </c>
       <c r="AP68" t="s" s="2">
         <v>84</v>
@@ -11443,10 +11401,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>489</v>
+        <v>514</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>489</v>
+        <v>514</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11466,19 +11424,23 @@
         <v>84</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>490</v>
+        <v>283</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>491</v>
+        <v>515</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>516</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>518</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
       </c>
@@ -11502,13 +11464,13 @@
         <v>84</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>84</v>
+        <v>287</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>84</v>
+        <v>519</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>84</v>
+        <v>520</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>84</v>
@@ -11526,7 +11488,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>489</v>
+        <v>521</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11541,19 +11503,19 @@
         <v>106</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>493</v>
+        <v>84</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>84</v>
+        <v>522</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>84</v>
@@ -11567,10 +11529,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>495</v>
+        <v>523</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>495</v>
+        <v>523</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11581,7 +11543,7 @@
         <v>82</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>84</v>
@@ -11590,16 +11552,16 @@
         <v>84</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>496</v>
+        <v>147</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>497</v>
+        <v>524</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>498</v>
+        <v>525</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11650,13 +11612,13 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>495</v>
+        <v>526</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>84</v>
@@ -11665,19 +11627,19 @@
         <v>106</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>499</v>
+        <v>84</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>500</v>
+        <v>84</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>84</v>
+        <v>522</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>84</v>
@@ -11691,10 +11653,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>502</v>
+        <v>527</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>502</v>
+        <v>527</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11705,30 +11667,32 @@
         <v>82</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J71" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="K71" t="s" s="2">
-        <v>503</v>
+        <v>528</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>504</v>
+        <v>529</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>505</v>
+        <v>530</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>531</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>532</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
       </c>
@@ -11776,13 +11740,13 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>502</v>
+        <v>533</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>84</v>
@@ -11791,13 +11755,13 @@
         <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>507</v>
+        <v>84</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>508</v>
+        <v>534</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>84</v>
@@ -11817,10 +11781,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>509</v>
+        <v>535</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>509</v>
+        <v>535</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11840,18 +11804,20 @@
         <v>84</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>147</v>
+        <v>536</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>148</v>
+        <v>537</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>538</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>539</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11876,13 +11842,13 @@
         <v>84</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>84</v>
+        <v>287</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>84</v>
+        <v>540</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>84</v>
+        <v>541</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>84</v>
@@ -11900,7 +11866,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>150</v>
+        <v>542</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11912,7 +11878,7 @@
         <v>84</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>84</v>
@@ -11921,13 +11887,13 @@
         <v>84</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>151</v>
+        <v>543</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>84</v>
+        <v>544</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>84</v>
@@ -11941,21 +11907,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>510</v>
+        <v>545</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>510</v>
+        <v>545</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>176</v>
+        <v>84</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>84</v>
@@ -11964,21 +11930,23 @@
         <v>84</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>139</v>
+        <v>283</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>177</v>
+        <v>546</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>178</v>
+        <v>547</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>548</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>549</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>84</v>
       </c>
@@ -12002,43 +11970,43 @@
         <v>84</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>84</v>
+        <v>287</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>84</v>
+        <v>550</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>84</v>
+        <v>551</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>153</v>
+        <v>84</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>156</v>
+        <v>552</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>84</v>
@@ -12047,13 +12015,13 @@
         <v>84</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>151</v>
+        <v>553</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>84</v>
+        <v>554</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>84</v>
@@ -12067,45 +12035,43 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>511</v>
+        <v>555</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>511</v>
+        <v>555</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>512</v>
+        <v>84</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>139</v>
+        <v>283</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>513</v>
+        <v>556</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>557</v>
+      </c>
+      <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>259</v>
+        <v>558</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>84</v>
@@ -12130,13 +12096,13 @@
         <v>84</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>84</v>
+        <v>287</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>84</v>
+        <v>559</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>84</v>
+        <v>560</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>84</v>
@@ -12154,19 +12120,19 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>515</v>
+        <v>561</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>84</v>
@@ -12175,13 +12141,13 @@
         <v>84</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>137</v>
+        <v>562</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>84</v>
+        <v>563</v>
       </c>
       <c r="AP74" t="s" s="2">
         <v>84</v>
@@ -12195,10 +12161,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>516</v>
+        <v>564</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>516</v>
+        <v>564</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12221,17 +12187,19 @@
         <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>517</v>
+        <v>283</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>518</v>
+        <v>565</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>566</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>567</v>
+      </c>
       <c r="O75" t="s" s="2">
-        <v>520</v>
+        <v>568</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>84</v>
@@ -12256,13 +12224,13 @@
         <v>84</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>84</v>
+        <v>287</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>84</v>
+        <v>569</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>84</v>
+        <v>570</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>84</v>
@@ -12280,7 +12248,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>521</v>
+        <v>571</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12301,13 +12269,13 @@
         <v>84</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>522</v>
+        <v>572</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>523</v>
+        <v>573</v>
       </c>
       <c r="AP75" t="s" s="2">
         <v>84</v>
@@ -12321,10 +12289,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>524</v>
+        <v>574</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>524</v>
+        <v>574</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12335,10 +12303,10 @@
         <v>82</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>84</v>
@@ -12347,18 +12315,16 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>147</v>
+        <v>575</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>525</v>
+        <v>576</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>526</v>
+        <v>577</v>
       </c>
       <c r="N76" s="2"/>
-      <c r="O76" t="s" s="2">
-        <v>527</v>
-      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>84</v>
       </c>
@@ -12406,13 +12372,13 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>528</v>
+        <v>578</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>84</v>
@@ -12427,13 +12393,13 @@
         <v>84</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>522</v>
+        <v>84</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>529</v>
+        <v>579</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>84</v>
@@ -12447,10 +12413,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>530</v>
+        <v>580</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>530</v>
+        <v>580</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12461,7 +12427,7 @@
         <v>82</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>84</v>
@@ -12470,23 +12436,19 @@
         <v>84</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>299</v>
+        <v>147</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>531</v>
+        <v>148</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>534</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>84</v>
       </c>
@@ -12510,13 +12472,13 @@
         <v>84</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>303</v>
+        <v>84</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>535</v>
+        <v>84</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>536</v>
+        <v>84</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>84</v>
@@ -12534,19 +12496,19 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>537</v>
+        <v>150</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>84</v>
@@ -12555,13 +12517,13 @@
         <v>84</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>522</v>
+        <v>151</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>538</v>
+        <v>84</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>84</v>
@@ -12575,21 +12537,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>539</v>
+        <v>581</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>539</v>
+        <v>581</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>84</v>
+        <v>176</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>84</v>
@@ -12598,18 +12560,20 @@
         <v>84</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>540</v>
+        <v>177</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>84</v>
@@ -12646,31 +12610,31 @@
         <v>84</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>84</v>
+        <v>153</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>542</v>
+        <v>156</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>84</v>
@@ -12679,13 +12643,13 @@
         <v>84</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>522</v>
+        <v>151</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>538</v>
+        <v>84</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>84</v>
@@ -12699,10 +12663,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>543</v>
+        <v>582</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>543</v>
+        <v>582</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12725,19 +12689,17 @@
         <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>544</v>
+        <v>283</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>545</v>
+        <v>583</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>547</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>548</v>
+        <v>585</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>84</v>
@@ -12762,13 +12724,13 @@
         <v>84</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>84</v>
+        <v>287</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>84</v>
+        <v>586</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>84</v>
+        <v>587</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>84</v>
@@ -12786,7 +12748,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>549</v>
+        <v>588</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12807,13 +12769,13 @@
         <v>84</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>550</v>
+        <v>84</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>84</v>
+        <v>589</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>84</v>
@@ -12827,10 +12789,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>551</v>
+        <v>590</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>551</v>
+        <v>590</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12853,18 +12815,20 @@
         <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>552</v>
+        <v>591</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>553</v>
+        <v>592</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>554</v>
+        <v>593</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="O80" s="2"/>
+        <v>594</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>595</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
       </c>
@@ -12888,13 +12852,13 @@
         <v>84</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>303</v>
+        <v>84</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>556</v>
+        <v>84</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>557</v>
+        <v>84</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>84</v>
@@ -12912,7 +12876,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>558</v>
+        <v>596</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12933,13 +12897,13 @@
         <v>84</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>560</v>
+        <v>597</v>
       </c>
       <c r="AP80" t="s" s="2">
         <v>84</v>
@@ -12953,10 +12917,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>561</v>
+        <v>598</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>561</v>
+        <v>598</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12979,19 +12943,19 @@
         <v>94</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>299</v>
+        <v>599</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>562</v>
+        <v>600</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>563</v>
+        <v>601</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>564</v>
+        <v>602</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>565</v>
+        <v>603</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>84</v>
@@ -13016,13 +12980,13 @@
         <v>84</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>303</v>
+        <v>84</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>566</v>
+        <v>84</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>567</v>
+        <v>84</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>84</v>
@@ -13040,7 +13004,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>568</v>
+        <v>604</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -13061,13 +13025,13 @@
         <v>84</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>569</v>
+        <v>605</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>570</v>
+        <v>606</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>84</v>
@@ -13081,10 +13045,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>571</v>
+        <v>607</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>571</v>
+        <v>607</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13107,17 +13071,19 @@
         <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>299</v>
+        <v>608</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>572</v>
+        <v>609</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>610</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>611</v>
+      </c>
       <c r="O82" t="s" s="2">
-        <v>574</v>
+        <v>612</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>84</v>
@@ -13142,13 +13108,13 @@
         <v>84</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>303</v>
+        <v>84</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>575</v>
+        <v>84</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>576</v>
+        <v>84</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>84</v>
@@ -13166,7 +13132,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>577</v>
+        <v>613</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -13187,13 +13153,13 @@
         <v>84</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>578</v>
+        <v>614</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>579</v>
+        <v>615</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>84</v>
@@ -13207,10 +13173,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>580</v>
+        <v>616</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>580</v>
+        <v>616</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13233,19 +13199,19 @@
         <v>94</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>299</v>
+        <v>617</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>581</v>
+        <v>618</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>582</v>
+        <v>619</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>583</v>
+        <v>620</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>584</v>
+        <v>621</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>84</v>
@@ -13270,13 +13236,13 @@
         <v>84</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>303</v>
+        <v>84</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>585</v>
+        <v>84</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>586</v>
+        <v>84</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>84</v>
@@ -13294,7 +13260,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>587</v>
+        <v>622</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13315,13 +13281,13 @@
         <v>84</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>588</v>
+        <v>623</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>589</v>
+        <v>84</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>84</v>
@@ -13335,10 +13301,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>590</v>
+        <v>624</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>590</v>
+        <v>624</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13349,7 +13315,7 @@
         <v>82</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>84</v>
@@ -13361,16 +13327,18 @@
         <v>94</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>591</v>
+        <v>617</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>592</v>
+        <v>625</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>593</v>
+        <v>626</v>
       </c>
       <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+      <c r="O84" t="s" s="2">
+        <v>627</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>84</v>
       </c>
@@ -13418,13 +13386,13 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>594</v>
+        <v>628</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>84</v>
@@ -13439,13 +13407,13 @@
         <v>84</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>84</v>
+        <v>623</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>595</v>
+        <v>84</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>84</v>
@@ -13459,10 +13427,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>596</v>
+        <v>629</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>596</v>
+        <v>629</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13485,13 +13453,13 @@
         <v>84</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>147</v>
+        <v>630</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>148</v>
+        <v>631</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>149</v>
+        <v>632</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13542,7 +13510,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>150</v>
+        <v>629</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13554,16 +13522,16 @@
         <v>84</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>84</v>
+        <v>633</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>151</v>
+        <v>634</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>84</v>
@@ -13583,21 +13551,21 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>597</v>
+        <v>635</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>597</v>
+        <v>635</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>176</v>
+        <v>84</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>84</v>
@@ -13609,17 +13577,15 @@
         <v>84</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>84</v>
@@ -13656,31 +13622,31 @@
         <v>84</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>153</v>
+        <v>84</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>84</v>
@@ -13709,21 +13675,21 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>598</v>
+        <v>636</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>598</v>
+        <v>636</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>84</v>
+        <v>176</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>84</v>
@@ -13732,21 +13698,21 @@
         <v>84</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>299</v>
+        <v>139</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>599</v>
+        <v>177</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" t="s" s="2">
-        <v>601</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>84</v>
       </c>
@@ -13770,13 +13736,13 @@
         <v>84</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>303</v>
+        <v>84</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>602</v>
+        <v>84</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>603</v>
+        <v>84</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>84</v>
@@ -13794,19 +13760,19 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>604</v>
+        <v>156</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>84</v>
@@ -13815,13 +13781,13 @@
         <v>84</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>84</v>
+        <v>151</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>605</v>
+        <v>84</v>
       </c>
       <c r="AP87" t="s" s="2">
         <v>84</v>
@@ -13835,45 +13801,45 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>606</v>
+        <v>637</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>606</v>
+        <v>637</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>84</v>
+        <v>496</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="J88" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>607</v>
+        <v>139</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>608</v>
+        <v>497</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>609</v>
+        <v>498</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>610</v>
+        <v>179</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>611</v>
+        <v>259</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>84</v>
@@ -13922,19 +13888,19 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>612</v>
+        <v>499</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>84</v>
@@ -13943,13 +13909,13 @@
         <v>84</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>588</v>
+        <v>137</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>613</v>
+        <v>84</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>84</v>
@@ -13963,10 +13929,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>614</v>
+        <v>638</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>614</v>
+        <v>638</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13986,23 +13952,21 @@
         <v>84</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>615</v>
+        <v>630</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>616</v>
+        <v>639</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>617</v>
+        <v>640</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>619</v>
-      </c>
+        <v>641</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>84</v>
       </c>
@@ -14050,7 +14014,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>620</v>
+        <v>638</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -14071,13 +14035,13 @@
         <v>84</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>621</v>
+        <v>642</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>622</v>
+        <v>84</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>84</v>
@@ -14091,10 +14055,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>623</v>
+        <v>643</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>623</v>
+        <v>643</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14114,23 +14078,19 @@
         <v>84</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>624</v>
+        <v>147</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>625</v>
+        <v>148</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>628</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>84</v>
       </c>
@@ -14178,7 +14138,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>629</v>
+        <v>150</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -14190,7 +14150,7 @@
         <v>84</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>84</v>
@@ -14199,13 +14159,13 @@
         <v>84</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>630</v>
+        <v>151</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>631</v>
+        <v>84</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>84</v>
@@ -14219,21 +14179,21 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>84</v>
+        <v>176</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>84</v>
@@ -14242,23 +14202,21 @@
         <v>84</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>633</v>
+        <v>139</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>634</v>
+        <v>177</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>635</v>
+        <v>178</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>637</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>84</v>
       </c>
@@ -14306,19 +14264,19 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>638</v>
+        <v>156</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>84</v>
@@ -14327,7 +14285,7 @@
         <v>84</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>639</v>
+        <v>151</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>84</v>
@@ -14347,43 +14305,45 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>640</v>
+        <v>645</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>84</v>
+        <v>496</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I92" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="J92" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>633</v>
+        <v>139</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>641</v>
+        <v>497</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>498</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O92" t="s" s="2">
-        <v>643</v>
+        <v>259</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>84</v>
@@ -14432,19 +14392,19 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>644</v>
+        <v>499</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>84</v>
@@ -14453,7 +14413,7 @@
         <v>84</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>639</v>
+        <v>137</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>84</v>
@@ -14473,10 +14433,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14499,7 +14459,7 @@
         <v>84</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>646</v>
+        <v>617</v>
       </c>
       <c r="L93" t="s" s="2">
         <v>647</v>
@@ -14556,7 +14516,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14574,10 +14534,10 @@
         <v>84</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM93" t="s" s="2">
         <v>649</v>
-      </c>
-      <c r="AM93" t="s" s="2">
-        <v>650</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>84</v>
@@ -14597,10 +14557,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14623,13 +14583,13 @@
         <v>84</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>147</v>
+        <v>651</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>148</v>
+        <v>652</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>149</v>
+        <v>653</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14680,7 +14640,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>150</v>
+        <v>650</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14692,7 +14652,7 @@
         <v>84</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>84</v>
@@ -14701,7 +14661,7 @@
         <v>84</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>151</v>
+        <v>654</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>84</v>
@@ -14721,21 +14681,21 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>176</v>
+        <v>84</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>84</v>
@@ -14747,17 +14707,15 @@
         <v>84</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>139</v>
+        <v>651</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>177</v>
+        <v>656</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>657</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>84</v>
@@ -14806,19 +14764,19 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>156</v>
+        <v>655</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>84</v>
@@ -14827,7 +14785,7 @@
         <v>84</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>151</v>
+        <v>654</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>84</v>
@@ -14847,45 +14805,45 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>512</v>
+        <v>84</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I96" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>139</v>
+        <v>659</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>513</v>
+        <v>660</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>514</v>
+        <v>661</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>179</v>
+        <v>662</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>259</v>
+        <v>663</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>84</v>
@@ -14934,28 +14892,28 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>515</v>
+        <v>658</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>84</v>
+        <v>664</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>137</v>
+        <v>665</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>84</v>
@@ -14975,10 +14933,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>654</v>
+        <v>666</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>654</v>
+        <v>666</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15001,17 +14959,15 @@
         <v>84</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>646</v>
+        <v>147</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>655</v>
+        <v>148</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>657</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>84</v>
@@ -15060,7 +15016,7 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>654</v>
+        <v>150</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -15072,7 +15028,7 @@
         <v>84</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>84</v>
@@ -15081,7 +15037,7 @@
         <v>84</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>658</v>
+        <v>151</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>84</v>
@@ -15101,21 +15057,21 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>84</v>
+        <v>176</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>84</v>
@@ -15127,15 +15083,17 @@
         <v>84</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>84</v>
@@ -15172,31 +15130,31 @@
         <v>84</v>
       </c>
       <c r="AB98" t="s" s="2">
-        <v>84</v>
+        <v>153</v>
       </c>
       <c r="AC98" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AD98" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE98" t="s" s="2">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>84</v>
@@ -15225,21 +15183,21 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>176</v>
+        <v>84</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>84</v>
@@ -15248,19 +15206,19 @@
         <v>84</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>139</v>
+        <v>372</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>177</v>
+        <v>669</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>178</v>
+        <v>670</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>179</v>
+        <v>671</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -15310,19 +15268,19 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>156</v>
+        <v>672</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>84</v>
+        <v>673</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>84</v>
@@ -15331,13 +15289,13 @@
         <v>84</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>151</v>
+        <v>674</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO99" t="s" s="2">
-        <v>84</v>
+        <v>675</v>
       </c>
       <c r="AP99" t="s" s="2">
         <v>84</v>
@@ -15351,50 +15309,50 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>661</v>
+        <v>676</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>661</v>
+        <v>676</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>512</v>
+        <v>84</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="J100" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>139</v>
+        <v>372</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>513</v>
+        <v>677</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>514</v>
+        <v>678</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>259</v>
-      </c>
+        <v>679</v>
+      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q100" s="2"/>
+      <c r="Q100" t="s" s="2">
+        <v>680</v>
+      </c>
       <c r="R100" t="s" s="2">
         <v>84</v>
       </c>
@@ -15438,19 +15396,19 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>515</v>
+        <v>681</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>84</v>
+        <v>673</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>84</v>
@@ -15459,16 +15417,16 @@
         <v>84</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>137</v>
+        <v>682</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO100" t="s" s="2">
-        <v>84</v>
+        <v>683</v>
       </c>
       <c r="AP100" t="s" s="2">
-        <v>84</v>
+        <v>684</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
@@ -15479,10 +15437,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>662</v>
+        <v>685</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>662</v>
+        <v>685</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15496,7 +15454,7 @@
         <v>93</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>84</v>
@@ -15505,15 +15463,17 @@
         <v>84</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>633</v>
+        <v>686</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>663</v>
+        <v>687</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>688</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>689</v>
+      </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>84</v>
@@ -15562,7 +15522,7 @@
         <v>84</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>662</v>
+        <v>685</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15580,22 +15540,22 @@
         <v>84</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>84</v>
+        <v>690</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>665</v>
+        <v>691</v>
       </c>
       <c r="AN101" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>84</v>
+        <v>692</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>84</v>
+        <v>693</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>84</v>
+        <v>694</v>
       </c>
       <c r="AR101" t="s" s="2">
         <v>84</v>
@@ -15603,10 +15563,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>666</v>
+        <v>695</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>666</v>
+        <v>695</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15629,13 +15589,13 @@
         <v>84</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>667</v>
+        <v>617</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>668</v>
+        <v>696</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>669</v>
+        <v>697</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15686,7 +15646,7 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>666</v>
+        <v>695</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15704,16 +15664,16 @@
         <v>84</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>84</v>
+        <v>698</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>670</v>
+        <v>699</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>84</v>
+        <v>700</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>84</v>
@@ -15727,10 +15687,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>671</v>
+        <v>701</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>671</v>
+        <v>701</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15753,13 +15713,13 @@
         <v>84</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>667</v>
+        <v>147</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>672</v>
+        <v>148</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>673</v>
+        <v>149</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15810,7 +15770,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>671</v>
+        <v>150</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15822,7 +15782,7 @@
         <v>84</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>84</v>
@@ -15831,7 +15791,7 @@
         <v>84</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>670</v>
+        <v>151</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>84</v>
@@ -15851,21 +15811,21 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>674</v>
+        <v>702</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>674</v>
+        <v>702</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>84</v>
+        <v>176</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>84</v>
@@ -15877,20 +15837,18 @@
         <v>84</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>675</v>
+        <v>139</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>676</v>
+        <v>177</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>677</v>
+        <v>178</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>679</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>84</v>
       </c>
@@ -15926,40 +15884,40 @@
         <v>84</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>84</v>
+        <v>153</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>84</v>
+        <v>154</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>84</v>
+        <v>155</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>674</v>
+        <v>156</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>680</v>
+        <v>84</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>681</v>
+        <v>151</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>84</v>
@@ -15979,10 +15937,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>682</v>
+        <v>703</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>682</v>
+        <v>703</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15996,25 +15954,29 @@
         <v>93</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>147</v>
+        <v>704</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>148</v>
+        <v>705</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
+        <v>706</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>708</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>84</v>
       </c>
@@ -16062,7 +16024,7 @@
         <v>84</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>150</v>
+        <v>709</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -16074,7 +16036,7 @@
         <v>84</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>84</v>
@@ -16083,68 +16045,70 @@
         <v>84</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>151</v>
+        <v>710</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>84</v>
+        <v>711</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>84</v>
+        <v>712</v>
       </c>
       <c r="AQ105" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR105" t="s" s="2">
-        <v>84</v>
+        <v>713</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>683</v>
+        <v>714</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>683</v>
+        <v>714</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>176</v>
+        <v>84</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I106" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>177</v>
+        <v>715</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O106" s="2"/>
+        <v>716</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" t="s" s="2">
+        <v>717</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q106" s="2"/>
+      <c r="Q106" t="s" s="2">
+        <v>718</v>
+      </c>
       <c r="R106" t="s" s="2">
         <v>84</v>
       </c>
@@ -16164,43 +16128,43 @@
         <v>84</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>84</v>
+        <v>275</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>84</v>
+        <v>719</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>84</v>
+        <v>720</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>153</v>
+        <v>84</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>156</v>
+        <v>721</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>84</v>
@@ -16209,13 +16173,13 @@
         <v>84</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>151</v>
+        <v>722</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO106" t="s" s="2">
-        <v>84</v>
+        <v>723</v>
       </c>
       <c r="AP106" t="s" s="2">
         <v>84</v>
@@ -16229,10 +16193,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>684</v>
+        <v>724</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>684</v>
+        <v>724</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16255,18 +16219,18 @@
         <v>94</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>388</v>
+        <v>147</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>685</v>
+        <v>725</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>687</v>
-      </c>
-      <c r="O107" s="2"/>
+        <v>726</v>
+      </c>
+      <c r="N107" s="2"/>
+      <c r="O107" t="s" s="2">
+        <v>727</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>84</v>
       </c>
@@ -16314,7 +16278,7 @@
         <v>84</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>688</v>
+        <v>728</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>82</v>
@@ -16323,7 +16287,7 @@
         <v>93</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>689</v>
+        <v>84</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>106</v>
@@ -16335,13 +16299,13 @@
         <v>84</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>690</v>
+        <v>729</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO107" t="s" s="2">
-        <v>691</v>
+        <v>730</v>
       </c>
       <c r="AP107" t="s" s="2">
         <v>84</v>
@@ -16355,10 +16319,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>692</v>
+        <v>731</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>692</v>
+        <v>731</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16372,7 +16336,7 @@
         <v>93</v>
       </c>
       <c r="H108" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="I108" t="s" s="2">
         <v>84</v>
@@ -16381,24 +16345,22 @@
         <v>94</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>388</v>
+        <v>108</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>693</v>
+        <v>732</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="O108" s="2"/>
+        <v>733</v>
+      </c>
+      <c r="N108" s="2"/>
+      <c r="O108" t="s" s="2">
+        <v>734</v>
+      </c>
       <c r="P108" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q108" t="s" s="2">
-        <v>696</v>
-      </c>
+      <c r="Q108" s="2"/>
       <c r="R108" t="s" s="2">
         <v>84</v>
       </c>
@@ -16442,7 +16404,7 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>697</v>
+        <v>735</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -16451,7 +16413,7 @@
         <v>93</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>689</v>
+        <v>736</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>106</v>
@@ -16463,16 +16425,16 @@
         <v>84</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>698</v>
+        <v>737</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>699</v>
+        <v>730</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>700</v>
+        <v>84</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>84</v>
@@ -16483,10 +16445,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>701</v>
+        <v>738</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>701</v>
+        <v>738</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16500,27 +16462,29 @@
         <v>93</v>
       </c>
       <c r="H109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J109" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J109" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="K109" t="s" s="2">
-        <v>702</v>
+        <v>114</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>703</v>
+        <v>739</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>704</v>
+        <v>740</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="O109" s="2"/>
+        <v>741</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>742</v>
+      </c>
       <c r="P109" t="s" s="2">
         <v>84</v>
       </c>
@@ -16568,7 +16532,7 @@
         <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>701</v>
+        <v>743</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>82</v>
@@ -16586,22 +16550,22 @@
         <v>84</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>706</v>
+        <v>84</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>707</v>
+        <v>744</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>708</v>
+        <v>730</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>709</v>
+        <v>84</v>
       </c>
       <c r="AQ109" t="s" s="2">
-        <v>710</v>
+        <v>84</v>
       </c>
       <c r="AR109" t="s" s="2">
         <v>84</v>
@@ -16609,10 +16573,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>711</v>
+        <v>745</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>711</v>
+        <v>745</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16626,7 +16590,7 @@
         <v>93</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>84</v>
@@ -16635,15 +16599,17 @@
         <v>84</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>633</v>
+        <v>651</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>712</v>
+        <v>746</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="N110" s="2"/>
+        <v>747</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>748</v>
+      </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>84</v>
@@ -16692,7 +16658,7 @@
         <v>84</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>711</v>
+        <v>745</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>82</v>
@@ -16710,33 +16676,33 @@
         <v>84</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>714</v>
+        <v>749</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>715</v>
+        <v>750</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>716</v>
+        <v>84</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>84</v>
+        <v>751</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR110" t="s" s="2">
-        <v>84</v>
+        <v>752</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>717</v>
+        <v>753</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>717</v>
+        <v>753</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16759,13 +16725,13 @@
         <v>84</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>147</v>
+        <v>754</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>148</v>
+        <v>755</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>149</v>
+        <v>756</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16816,7 +16782,7 @@
         <v>84</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>150</v>
+        <v>753</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>82</v>
@@ -16828,7 +16794,7 @@
         <v>84</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>84</v>
@@ -16837,10 +16803,10 @@
         <v>84</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>151</v>
+        <v>757</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>84</v>
+        <v>407</v>
       </c>
       <c r="AO111" t="s" s="2">
         <v>84</v>
@@ -16857,21 +16823,21 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>718</v>
+        <v>758</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>718</v>
+        <v>758</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>176</v>
+        <v>84</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>84</v>
@@ -16883,17 +16849,15 @@
         <v>84</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>139</v>
+        <v>630</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>177</v>
+        <v>759</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N112" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>760</v>
+      </c>
+      <c r="N112" s="2"/>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>84</v>
@@ -16930,40 +16894,40 @@
         <v>84</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>153</v>
+        <v>84</v>
       </c>
       <c r="AC112" t="s" s="2">
-        <v>154</v>
+        <v>84</v>
       </c>
       <c r="AD112" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>156</v>
+        <v>758</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>143</v>
+        <v>106</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>84</v>
+        <v>761</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>151</v>
+        <v>762</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>84</v>
@@ -16983,10 +16947,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>719</v>
+        <v>763</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>719</v>
+        <v>763</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17000,29 +16964,25 @@
         <v>93</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J113" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>720</v>
+        <v>147</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>721</v>
+        <v>148</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>724</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>84</v>
       </c>
@@ -17070,7 +17030,7 @@
         <v>84</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>725</v>
+        <v>150</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>82</v>
@@ -17082,7 +17042,7 @@
         <v>84</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>84</v>
@@ -17091,70 +17051,68 @@
         <v>84</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>726</v>
+        <v>151</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>727</v>
+        <v>84</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>728</v>
+        <v>84</v>
       </c>
       <c r="AQ113" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR113" t="s" s="2">
-        <v>729</v>
+        <v>84</v>
       </c>
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>730</v>
+        <v>764</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>730</v>
+        <v>764</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
-        <v>84</v>
+        <v>176</v>
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I114" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="J114" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>731</v>
+        <v>177</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="N114" s="2"/>
-      <c r="O114" t="s" s="2">
-        <v>733</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="Q114" t="s" s="2">
-        <v>734</v>
-      </c>
+      <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
         <v>84</v>
       </c>
@@ -17174,13 +17132,13 @@
         <v>84</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>275</v>
+        <v>84</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>735</v>
+        <v>84</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>736</v>
+        <v>84</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>84</v>
@@ -17198,19 +17156,19 @@
         <v>84</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>737</v>
+        <v>156</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>84</v>
@@ -17219,13 +17177,13 @@
         <v>84</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>738</v>
+        <v>151</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>739</v>
+        <v>84</v>
       </c>
       <c r="AP114" t="s" s="2">
         <v>84</v>
@@ -17239,43 +17197,45 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>740</v>
+        <v>765</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>740</v>
+        <v>765</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>84</v>
+        <v>496</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I115" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="J115" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>741</v>
+        <v>497</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="N115" s="2"/>
+        <v>498</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O115" t="s" s="2">
-        <v>743</v>
+        <v>259</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>84</v>
@@ -17324,19 +17284,19 @@
         <v>84</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>744</v>
+        <v>499</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="AK115" t="s" s="2">
         <v>84</v>
@@ -17345,13 +17305,13 @@
         <v>84</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>745</v>
+        <v>137</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>746</v>
+        <v>84</v>
       </c>
       <c r="AP115" t="s" s="2">
         <v>84</v>
@@ -17365,10 +17325,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>747</v>
+        <v>766</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>747</v>
+        <v>766</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17376,7 +17336,7 @@
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G116" t="s" s="2">
         <v>93</v>
@@ -17388,21 +17348,21 @@
         <v>84</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>108</v>
+        <v>536</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>748</v>
+        <v>767</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" t="s" s="2">
-        <v>750</v>
-      </c>
+        <v>768</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>84</v>
       </c>
@@ -17426,13 +17386,13 @@
         <v>84</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>84</v>
+        <v>287</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>84</v>
+        <v>770</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>84</v>
+        <v>771</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>84</v>
@@ -17450,16 +17410,16 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>751</v>
+        <v>766</v>
       </c>
       <c r="AG116" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AH116" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>752</v>
+        <v>84</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>106</v>
@@ -17468,16 +17428,16 @@
         <v>84</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>84</v>
+        <v>761</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>753</v>
+        <v>772</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>746</v>
+        <v>773</v>
       </c>
       <c r="AP116" t="s" s="2">
         <v>84</v>
@@ -17491,10 +17451,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>754</v>
+        <v>774</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>754</v>
+        <v>774</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17514,23 +17474,19 @@
         <v>84</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>114</v>
+        <v>283</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>755</v>
+        <v>775</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>756</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>757</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>758</v>
-      </c>
+        <v>776</v>
+      </c>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>84</v>
       </c>
@@ -17554,13 +17510,13 @@
         <v>84</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>84</v>
+        <v>287</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>84</v>
+        <v>777</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>84</v>
+        <v>778</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>84</v>
@@ -17578,7 +17534,7 @@
         <v>84</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>759</v>
+        <v>774</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>82</v>
@@ -17596,16 +17552,16 @@
         <v>84</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>84</v>
+        <v>779</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>760</v>
+        <v>780</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>746</v>
+        <v>781</v>
       </c>
       <c r="AP117" t="s" s="2">
         <v>84</v>
@@ -17619,10 +17575,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>761</v>
+        <v>782</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>761</v>
+        <v>782</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17636,7 +17592,7 @@
         <v>93</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>84</v>
@@ -17645,17 +17601,15 @@
         <v>84</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>667</v>
+        <v>783</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>762</v>
+        <v>784</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>763</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>764</v>
-      </c>
+        <v>785</v>
+      </c>
+      <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
         <v>84</v>
@@ -17704,7 +17658,7 @@
         <v>84</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>761</v>
+        <v>782</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>82</v>
@@ -17719,13 +17673,13 @@
         <v>106</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>84</v>
+        <v>786</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>765</v>
+        <v>779</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>766</v>
+        <v>787</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>84</v>
@@ -17734,32 +17688,32 @@
         <v>84</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>767</v>
+        <v>84</v>
       </c>
       <c r="AQ118" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR118" t="s" s="2">
-        <v>768</v>
+        <v>84</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>769</v>
+        <v>788</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>769</v>
+        <v>788</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>84</v>
+        <v>789</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>84</v>
@@ -17771,15 +17725,17 @@
         <v>84</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>770</v>
+        <v>790</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>771</v>
+        <v>791</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>772</v>
-      </c>
-      <c r="N119" s="2"/>
+        <v>792</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>793</v>
+      </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>84</v>
@@ -17828,13 +17784,13 @@
         <v>84</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>769</v>
+        <v>788</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>84</v>
@@ -17849,10 +17805,10 @@
         <v>84</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>773</v>
+        <v>794</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>423</v>
+        <v>84</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>84</v>
@@ -17869,10 +17825,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>774</v>
+        <v>795</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>774</v>
+        <v>795</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17883,7 +17839,7 @@
         <v>82</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>84</v>
@@ -17895,15 +17851,17 @@
         <v>84</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>646</v>
+        <v>796</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>775</v>
+        <v>797</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>776</v>
-      </c>
-      <c r="N120" s="2"/>
+        <v>798</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>799</v>
+      </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>84</v>
@@ -17952,13 +17910,13 @@
         <v>84</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>774</v>
+        <v>795</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>84</v>
@@ -17967,13 +17925,13 @@
         <v>106</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>84</v>
+        <v>800</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>777</v>
+        <v>84</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>778</v>
+        <v>801</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>84</v>
@@ -17988,1015 +17946,11 @@
         <v>84</v>
       </c>
       <c r="AR120" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="121" hidden="true">
-      <c r="A121" t="s" s="2">
-        <v>779</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>779</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E121" s="2"/>
-      <c r="F121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="L121" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
-      <c r="P121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR121" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="122" hidden="true">
-      <c r="A122" t="s" s="2">
-        <v>780</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>780</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>176</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O122" s="2"/>
-      <c r="P122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR122" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="123" hidden="true">
-      <c r="A123" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>781</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O123" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="P123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR123" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="124" hidden="true">
-      <c r="A124" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E124" s="2"/>
-      <c r="F124" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>783</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>785</v>
-      </c>
-      <c r="O124" s="2"/>
-      <c r="P124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>786</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>787</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>782</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>777</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>788</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO124" t="s" s="2">
-        <v>789</v>
-      </c>
-      <c r="AP124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR124" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="125" hidden="true">
-      <c r="A125" t="s" s="2">
-        <v>790</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>790</v>
-      </c>
-      <c r="C125" s="2"/>
-      <c r="D125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E125" s="2"/>
-      <c r="F125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G125" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="L125" t="s" s="2">
-        <v>791</v>
-      </c>
-      <c r="M125" t="s" s="2">
-        <v>792</v>
-      </c>
-      <c r="N125" s="2"/>
-      <c r="O125" s="2"/>
-      <c r="P125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q125" s="2"/>
-      <c r="R125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>793</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>794</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>790</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL125" t="s" s="2">
-        <v>795</v>
-      </c>
-      <c r="AM125" t="s" s="2">
-        <v>796</v>
-      </c>
-      <c r="AN125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO125" t="s" s="2">
-        <v>797</v>
-      </c>
-      <c r="AP125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR125" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="126" hidden="true">
-      <c r="A126" t="s" s="2">
-        <v>798</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>798</v>
-      </c>
-      <c r="C126" s="2"/>
-      <c r="D126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E126" s="2"/>
-      <c r="F126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G126" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K126" t="s" s="2">
-        <v>799</v>
-      </c>
-      <c r="L126" t="s" s="2">
-        <v>800</v>
-      </c>
-      <c r="M126" t="s" s="2">
-        <v>801</v>
-      </c>
-      <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
-      <c r="P126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q126" s="2"/>
-      <c r="R126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>798</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK126" t="s" s="2">
-        <v>802</v>
-      </c>
-      <c r="AL126" t="s" s="2">
-        <v>795</v>
-      </c>
-      <c r="AM126" t="s" s="2">
-        <v>803</v>
-      </c>
-      <c r="AN126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR126" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="127" hidden="true">
-      <c r="A127" t="s" s="2">
-        <v>804</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>804</v>
-      </c>
-      <c r="C127" s="2"/>
-      <c r="D127" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="E127" s="2"/>
-      <c r="F127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G127" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K127" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="L127" t="s" s="2">
-        <v>807</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>808</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>809</v>
-      </c>
-      <c r="O127" s="2"/>
-      <c r="P127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q127" s="2"/>
-      <c r="R127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>804</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM127" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="AN127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR127" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="128" hidden="true">
-      <c r="A128" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="C128" s="2"/>
-      <c r="D128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E128" s="2"/>
-      <c r="F128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G128" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K128" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="L128" t="s" s="2">
-        <v>813</v>
-      </c>
-      <c r="M128" t="s" s="2">
-        <v>814</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="O128" s="2"/>
-      <c r="P128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q128" s="2"/>
-      <c r="R128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ128" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK128" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="AL128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM128" t="s" s="2">
-        <v>817</v>
-      </c>
-      <c r="AN128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR128" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR128">
+  <autoFilter ref="A1:AR120">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -19006,7 +17960,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI127">
+  <conditionalFormatting sqref="A2:AI119">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5171" uniqueCount="821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5171" uniqueCount="822">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -999,6 +999,9 @@
 This element is labeled as a modifier because the intent alters when and how the resource is actually applicable.</t>
   </si>
   <si>
+    <t>order</t>
+  </si>
+  <si>
     <t>The kind of medication order.</t>
   </si>
   <si>
@@ -1014,7 +1017,7 @@
     <t>FiveWs.class</t>
   </si>
   <si>
-    <t>801: fixed value = order</t>
+    <t>801: fixed value = #order</t>
   </si>
   <si>
     <t>MedicationRequest.category</t>
@@ -8367,7 +8370,7 @@
         <v>84</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>84</v>
+        <v>316</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>84</v>
@@ -8385,10 +8388,10 @@
         <v>295</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>84</v>
@@ -8421,22 +8424,22 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -8447,10 +8450,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8476,13 +8479,13 @@
         <v>303</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8511,16 +8514,16 @@
         <v>307</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
@@ -8530,7 +8533,7 @@
         <v>143</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8548,13 +8551,13 @@
         <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>84</v>
@@ -8571,13 +8574,13 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>84</v>
@@ -8602,13 +8605,13 @@
         <v>303</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8637,10 +8640,10 @@
         <v>295</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8658,7 +8661,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8676,13 +8679,13 @@
         <v>84</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>84</v>
@@ -8699,10 +8702,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8728,10 +8731,10 @@
         <v>114</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8761,10 +8764,10 @@
         <v>295</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -8782,7 +8785,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8797,16 +8800,16 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>84</v>
@@ -8823,10 +8826,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8852,13 +8855,13 @@
         <v>221</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8908,7 +8911,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8929,7 +8932,7 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>84</v>
@@ -8949,10 +8952,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8975,13 +8978,13 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -9032,7 +9035,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -9053,7 +9056,7 @@
         <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>84</v>
@@ -9073,10 +9076,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9099,16 +9102,16 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -9134,11 +9137,11 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -9156,7 +9159,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>93</v>
@@ -9171,19 +9174,19 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>84</v>
@@ -9197,10 +9200,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9223,16 +9226,16 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -9282,7 +9285,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>93</v>
@@ -9297,22 +9300,22 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -9323,10 +9326,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9349,16 +9352,16 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -9408,7 +9411,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9423,22 +9426,22 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>298</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -9449,10 +9452,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9475,13 +9478,13 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -9532,7 +9535,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9547,16 +9550,16 @@
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>84</v>
@@ -9573,10 +9576,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9602,10 +9605,10 @@
         <v>237</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -9656,7 +9659,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9671,19 +9674,19 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>84</v>
@@ -9697,10 +9700,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9723,13 +9726,13 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9780,7 +9783,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9795,22 +9798,22 @@
         <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9821,10 +9824,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9847,13 +9850,13 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9904,7 +9907,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9919,16 +9922,16 @@
         <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>84</v>
@@ -9945,10 +9948,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9974,13 +9977,13 @@
         <v>303</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -10009,10 +10012,10 @@
         <v>307</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
@@ -10030,7 +10033,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -10045,13 +10048,13 @@
         <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>84</v>
@@ -10071,10 +10074,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10097,13 +10100,13 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -10154,7 +10157,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -10175,10 +10178,10 @@
         <v>84</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>84</v>
@@ -10195,10 +10198,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10224,13 +10227,13 @@
         <v>303</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -10259,10 +10262,10 @@
         <v>307</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -10280,7 +10283,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10295,19 +10298,19 @@
         <v>106</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>84</v>
@@ -10321,10 +10324,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10445,10 +10448,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10571,10 +10574,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10600,16 +10603,16 @@
         <v>172</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -10658,7 +10661,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10679,13 +10682,13 @@
         <v>84</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>84</v>
@@ -10699,10 +10702,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10728,16 +10731,16 @@
         <v>154</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10786,7 +10789,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10807,16 +10810,16 @@
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10827,10 +10830,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10853,16 +10856,16 @@
         <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10912,7 +10915,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10927,16 +10930,16 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>298</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>84</v>
@@ -10953,10 +10956,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10979,13 +10982,13 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -11036,7 +11039,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -11051,13 +11054,13 @@
         <v>106</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>84</v>
@@ -11077,10 +11080,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11106,10 +11109,10 @@
         <v>108</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -11160,7 +11163,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -11181,7 +11184,7 @@
         <v>84</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>84</v>
@@ -11201,10 +11204,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11227,13 +11230,13 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -11284,7 +11287,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11299,13 +11302,13 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>84</v>
@@ -11325,10 +11328,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11354,14 +11357,14 @@
         <v>282</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
@@ -11410,7 +11413,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11425,13 +11428,13 @@
         <v>106</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>84</v>
@@ -11451,10 +11454,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11480,13 +11483,13 @@
         <v>303</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11515,10 +11518,10 @@
         <v>307</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>84</v>
@@ -11536,7 +11539,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11557,7 +11560,7 @@
         <v>84</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>84</v>
@@ -11577,10 +11580,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11603,13 +11606,13 @@
         <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11660,7 +11663,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11675,13 +11678,13 @@
         <v>106</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>84</v>
@@ -11701,10 +11704,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11727,13 +11730,13 @@
         <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11784,7 +11787,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11799,13 +11802,13 @@
         <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>84</v>
@@ -11825,10 +11828,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11851,16 +11854,16 @@
         <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11910,7 +11913,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11925,13 +11928,13 @@
         <v>106</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>84</v>
@@ -11951,10 +11954,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12075,10 +12078,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12201,14 +12204,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -12230,10 +12233,10 @@
         <v>139</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>183</v>
@@ -12288,7 +12291,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12329,10 +12332,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12355,17 +12358,17 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>84</v>
@@ -12414,7 +12417,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12435,13 +12438,13 @@
         <v>84</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>84</v>
@@ -12455,10 +12458,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12484,14 +12487,14 @@
         <v>154</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12540,7 +12543,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12561,13 +12564,13 @@
         <v>84</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>84</v>
@@ -12581,10 +12584,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12610,16 +12613,16 @@
         <v>303</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
@@ -12647,10 +12650,10 @@
         <v>307</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>84</v>
@@ -12668,7 +12671,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12689,13 +12692,13 @@
         <v>84</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>84</v>
@@ -12709,10 +12712,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12738,10 +12741,10 @@
         <v>154</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12792,7 +12795,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12813,13 +12816,13 @@
         <v>84</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>84</v>
@@ -12833,10 +12836,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12859,19 +12862,19 @@
         <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
@@ -12920,7 +12923,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12941,7 +12944,7 @@
         <v>84</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>84</v>
@@ -12961,10 +12964,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12987,16 +12990,16 @@
         <v>94</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -13025,10 +13028,10 @@
         <v>307</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>84</v>
@@ -13046,7 +13049,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -13067,13 +13070,13 @@
         <v>84</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>84</v>
@@ -13087,10 +13090,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13116,16 +13119,16 @@
         <v>303</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>84</v>
@@ -13153,10 +13156,10 @@
         <v>307</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>84</v>
@@ -13174,7 +13177,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -13195,13 +13198,13 @@
         <v>84</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>84</v>
@@ -13215,10 +13218,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13244,14 +13247,14 @@
         <v>303</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>84</v>
@@ -13279,10 +13282,10 @@
         <v>307</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>84</v>
@@ -13300,7 +13303,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13321,13 +13324,13 @@
         <v>84</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>84</v>
@@ -13341,10 +13344,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13370,16 +13373,16 @@
         <v>303</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>84</v>
@@ -13407,10 +13410,10 @@
         <v>307</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>84</v>
@@ -13428,7 +13431,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13449,13 +13452,13 @@
         <v>84</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>84</v>
@@ -13469,10 +13472,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13495,13 +13498,13 @@
         <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13552,7 +13555,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13579,7 +13582,7 @@
         <v>84</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>84</v>
@@ -13593,10 +13596,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13717,10 +13720,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13843,10 +13846,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13872,14 +13875,14 @@
         <v>303</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>84</v>
@@ -13907,10 +13910,10 @@
         <v>307</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>84</v>
@@ -13928,7 +13931,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13955,7 +13958,7 @@
         <v>84</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>84</v>
@@ -13969,10 +13972,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13995,19 +13998,19 @@
         <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>84</v>
@@ -14056,7 +14059,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -14077,13 +14080,13 @@
         <v>84</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>84</v>
@@ -14097,10 +14100,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14123,19 +14126,19 @@
         <v>94</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>84</v>
@@ -14184,7 +14187,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -14205,13 +14208,13 @@
         <v>84</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>84</v>
@@ -14225,10 +14228,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14251,19 +14254,19 @@
         <v>94</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>84</v>
@@ -14312,7 +14315,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14333,13 +14336,13 @@
         <v>84</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>84</v>
@@ -14353,10 +14356,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14379,19 +14382,19 @@
         <v>94</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>84</v>
@@ -14440,7 +14443,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14461,7 +14464,7 @@
         <v>84</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>84</v>
@@ -14481,10 +14484,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14507,17 +14510,17 @@
         <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14566,7 +14569,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14587,7 +14590,7 @@
         <v>84</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>84</v>
@@ -14607,10 +14610,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14633,13 +14636,13 @@
         <v>84</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14690,7 +14693,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14708,10 +14711,10 @@
         <v>84</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>84</v>
@@ -14731,10 +14734,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14855,10 +14858,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14981,14 +14984,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -15010,10 +15013,10 @@
         <v>139</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>183</v>
@@ -15068,7 +15071,7 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -15109,10 +15112,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15135,16 +15138,16 @@
         <v>84</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -15194,7 +15197,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -15215,7 +15218,7 @@
         <v>84</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>84</v>
@@ -15235,10 +15238,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15359,10 +15362,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15485,14 +15488,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -15514,10 +15517,10 @@
         <v>139</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>183</v>
@@ -15572,7 +15575,7 @@
         <v>84</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15613,10 +15616,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15639,13 +15642,13 @@
         <v>84</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15696,7 +15699,7 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15717,7 +15720,7 @@
         <v>84</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>84</v>
@@ -15737,10 +15740,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15763,13 +15766,13 @@
         <v>84</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15820,7 +15823,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15841,7 +15844,7 @@
         <v>84</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>84</v>
@@ -15861,10 +15864,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15887,13 +15890,13 @@
         <v>84</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15944,7 +15947,7 @@
         <v>84</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15965,7 +15968,7 @@
         <v>84</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>84</v>
@@ -15985,10 +15988,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16011,19 +16014,19 @@
         <v>84</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>84</v>
@@ -16072,7 +16075,7 @@
         <v>84</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -16090,10 +16093,10 @@
         <v>84</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>84</v>
@@ -16113,10 +16116,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16237,10 +16240,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16363,10 +16366,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16392,13 +16395,13 @@
         <v>237</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -16448,7 +16451,7 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -16457,7 +16460,7 @@
         <v>93</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>106</v>
@@ -16469,13 +16472,13 @@
         <v>84</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>84</v>
@@ -16489,10 +16492,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16518,20 +16521,20 @@
         <v>237</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q109" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="R109" t="s" s="2">
         <v>84</v>
@@ -16576,7 +16579,7 @@
         <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>82</v>
@@ -16585,7 +16588,7 @@
         <v>93</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>106</v>
@@ -16597,16 +16600,16 @@
         <v>84</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>84</v>
@@ -16617,10 +16620,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16643,16 +16646,16 @@
         <v>84</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -16702,7 +16705,7 @@
         <v>84</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>82</v>
@@ -16720,22 +16723,22 @@
         <v>84</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AQ110" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AR110" t="s" s="2">
         <v>84</v>
@@ -16743,10 +16746,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16769,13 +16772,13 @@
         <v>84</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16826,7 +16829,7 @@
         <v>84</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>82</v>
@@ -16844,16 +16847,16 @@
         <v>84</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>84</v>
@@ -16867,10 +16870,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16991,10 +16994,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17117,10 +17120,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17143,19 +17146,19 @@
         <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>84</v>
@@ -17204,7 +17207,7 @@
         <v>84</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>82</v>
@@ -17225,30 +17228,30 @@
         <v>84</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR114" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17274,20 +17277,20 @@
         <v>114</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q115" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="R115" t="s" s="2">
         <v>84</v>
@@ -17311,10 +17314,10 @@
         <v>295</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>84</v>
@@ -17332,7 +17335,7 @@
         <v>84</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>82</v>
@@ -17353,13 +17356,13 @@
         <v>84</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AP115" t="s" s="2">
         <v>84</v>
@@ -17373,10 +17376,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17402,14 +17405,14 @@
         <v>154</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>84</v>
@@ -17458,7 +17461,7 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>82</v>
@@ -17479,13 +17482,13 @@
         <v>84</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AP116" t="s" s="2">
         <v>84</v>
@@ -17499,10 +17502,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17528,14 +17531,14 @@
         <v>108</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>84</v>
@@ -17584,7 +17587,7 @@
         <v>84</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>82</v>
@@ -17593,7 +17596,7 @@
         <v>93</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>106</v>
@@ -17605,13 +17608,13 @@
         <v>84</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AP117" t="s" s="2">
         <v>84</v>
@@ -17625,10 +17628,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17654,16 +17657,16 @@
         <v>114</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>84</v>
@@ -17712,7 +17715,7 @@
         <v>84</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>82</v>
@@ -17733,13 +17736,13 @@
         <v>84</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AP118" t="s" s="2">
         <v>84</v>
@@ -17753,10 +17756,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17779,16 +17782,16 @@
         <v>84</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -17838,7 +17841,7 @@
         <v>84</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>82</v>
@@ -17856,10 +17859,10 @@
         <v>84</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>84</v>
@@ -17868,21 +17871,21 @@
         <v>84</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AQ119" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR119" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17905,13 +17908,13 @@
         <v>84</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -17962,7 +17965,7 @@
         <v>84</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>82</v>
@@ -17983,10 +17986,10 @@
         <v>84</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>84</v>
@@ -18003,10 +18006,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18029,13 +18032,13 @@
         <v>84</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -18086,7 +18089,7 @@
         <v>84</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>82</v>
@@ -18104,10 +18107,10 @@
         <v>84</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>84</v>
@@ -18127,10 +18130,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18251,10 +18254,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18377,14 +18380,14 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
@@ -18406,10 +18409,10 @@
         <v>139</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N124" t="s" s="2">
         <v>183</v>
@@ -18464,7 +18467,7 @@
         <v>84</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>82</v>
@@ -18505,10 +18508,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18531,16 +18534,16 @@
         <v>84</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -18569,10 +18572,10 @@
         <v>307</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>84</v>
@@ -18590,7 +18593,7 @@
         <v>84</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>93</v>
@@ -18608,16 +18611,16 @@
         <v>84</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="AP125" t="s" s="2">
         <v>84</v>
@@ -18631,10 +18634,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18660,10 +18663,10 @@
         <v>303</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -18693,10 +18696,10 @@
         <v>307</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>84</v>
@@ -18714,7 +18717,7 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>82</v>
@@ -18732,16 +18735,16 @@
         <v>84</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AP126" t="s" s="2">
         <v>84</v>
@@ -18755,10 +18758,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18781,13 +18784,13 @@
         <v>84</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -18838,7 +18841,7 @@
         <v>84</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>82</v>
@@ -18853,13 +18856,13 @@
         <v>106</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>84</v>
@@ -18879,14 +18882,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -18905,16 +18908,16 @@
         <v>84</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -18964,7 +18967,7 @@
         <v>84</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>82</v>
@@ -18985,7 +18988,7 @@
         <v>84</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>84</v>
@@ -19005,10 +19008,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19031,16 +19034,16 @@
         <v>84</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -19090,7 +19093,7 @@
         <v>84</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
@@ -19105,13 +19108,13 @@
         <v>106</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5171" uniqueCount="822">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5171" uniqueCount="823">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -481,10 +481,7 @@
 </t>
   </si>
   <si>
-    <t>Optional Extensions Element</t>
-  </si>
-  <si>
-    <t>Optional Extension Element - found in all resources.</t>
+    <t>Extension medicationrequest-pharmacyOrderStatus</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -736,6 +733,9 @@
 </t>
   </si>
   <si>
+    <t>Extension medicationrequest-cancelDate</t>
+  </si>
+  <si>
     <t>MedicationRequest.extension:medicationrequest-cancelDate.id</t>
   </si>
   <si>
@@ -769,6 +769,9 @@
   <si>
     <t xml:space="preserve">Extension {http://va.gov/fhir/StructureDefinition/medicationrequest-includeIndicationInSig}
 </t>
+  </si>
+  <si>
+    <t>Extension medicationrequest-includeIndicationInSig</t>
   </si>
   <si>
     <t>MedicationRequest.extension:medicationrequest-includeIndicationInSig.id</t>
@@ -4099,10 +4102,10 @@
         <v>148</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -4162,7 +4165,7 @@
         <v>83</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>145</v>
@@ -4174,7 +4177,7 @@
         <v>84</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="AN10" t="s" s="2">
         <v>84</v>
@@ -4194,10 +4197,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>152</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>153</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -4220,13 +4223,13 @@
         <v>84</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -4277,28 +4280,28 @@
         <v>84</v>
       </c>
       <c r="AF11" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH11" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AG11" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH11" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM11" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>84</v>
@@ -4318,10 +4321,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -4392,7 +4395,7 @@
         <v>142</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>84</v>
@@ -4401,7 +4404,7 @@
         <v>143</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>82</v>
@@ -4442,10 +4445,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -4471,13 +4474,13 @@
         <v>108</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -4485,49 +4488,49 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="S13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="T13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="U13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="V13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="W13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="X13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Y13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="Z13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AA13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="S13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>93</v>
@@ -4568,10 +4571,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4594,13 +4597,13 @@
         <v>84</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L14" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="L14" t="s" s="2">
+      <c r="M14" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4651,7 +4654,7 @@
         <v>84</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>82</v>
@@ -4692,10 +4695,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>176</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4718,13 +4721,13 @@
         <v>84</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4775,28 +4778,28 @@
         <v>84</v>
       </c>
       <c r="AF15" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG15" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH15" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AG15" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH15" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>84</v>
@@ -4816,14 +4819,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>178</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4845,13 +4848,13 @@
         <v>139</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M16" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4892,7 +4895,7 @@
         <v>142</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>84</v>
@@ -4901,7 +4904,7 @@
         <v>143</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>82</v>
@@ -4922,7 +4925,7 @@
         <v>84</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>84</v>
@@ -4942,10 +4945,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B17" t="s" s="2">
         <v>184</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>185</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4971,16 +4974,16 @@
         <v>108</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>188</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>189</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>84</v>
@@ -5029,7 +5032,7 @@
         <v>84</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -5050,13 +5053,13 @@
         <v>84</v>
       </c>
       <c r="AM17" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AN17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO17" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>84</v>
@@ -5070,10 +5073,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="B18" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -5096,16 +5099,16 @@
         <v>94</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>195</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>197</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -5155,7 +5158,7 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -5176,13 +5179,13 @@
         <v>84</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO18" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>200</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>84</v>
@@ -5196,10 +5199,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="B19" t="s" s="2">
         <v>201</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>202</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -5225,14 +5228,14 @@
         <v>114</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>84</v>
@@ -5281,7 +5284,7 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -5302,19 +5305,19 @@
         <v>84</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AN19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO19" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="AN19" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO19" t="s" s="2">
+      <c r="AP19" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="AP19" t="s" s="2">
+      <c r="AQ19" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AQ19" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="AR19" t="s" s="2">
         <v>84</v>
@@ -5322,10 +5325,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="B20" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>212</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -5348,17 +5351,17 @@
         <v>94</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L20" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M20" t="s" s="2">
         <v>213</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>214</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -5407,7 +5410,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -5428,13 +5431,13 @@
         <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>84</v>
@@ -5448,10 +5451,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5474,19 +5477,19 @@
         <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L21" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="M21" t="s" s="2">
+      <c r="N21" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="N21" t="s" s="2">
+      <c r="O21" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>225</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>84</v>
@@ -5535,7 +5538,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -5556,13 +5559,13 @@
         <v>84</v>
       </c>
       <c r="AM21" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>84</v>
@@ -5576,13 +5579,13 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>138</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>84</v>
@@ -5604,13 +5607,13 @@
         <v>84</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="L22" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5670,7 +5673,7 @@
         <v>83</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>145</v>
@@ -5682,7 +5685,7 @@
         <v>84</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>84</v>
@@ -5705,7 +5708,7 @@
         <v>232</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5728,13 +5731,13 @@
         <v>84</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5785,28 +5788,28 @@
         <v>84</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AG23" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>84</v>
@@ -5829,7 +5832,7 @@
         <v>233</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5900,7 +5903,7 @@
         <v>142</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>84</v>
@@ -5909,7 +5912,7 @@
         <v>143</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>82</v>
@@ -5953,7 +5956,7 @@
         <v>234</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5979,13 +5982,13 @@
         <v>108</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -6035,7 +6038,7 @@
         <v>84</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>93</v>
@@ -6079,7 +6082,7 @@
         <v>236</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -6105,10 +6108,10 @@
         <v>237</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -6159,7 +6162,7 @@
         <v>84</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>82</v>
@@ -6231,10 +6234,10 @@
         <v>242</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>150</v>
+        <v>243</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -6294,7 +6297,7 @@
         <v>83</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>145</v>
@@ -6306,7 +6309,7 @@
         <v>84</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>84</v>
@@ -6326,10 +6329,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6352,13 +6355,13 @@
         <v>84</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -6409,28 +6412,28 @@
         <v>84</v>
       </c>
       <c r="AF28" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM28" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AG28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>84</v>
@@ -6450,10 +6453,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6524,7 +6527,7 @@
         <v>142</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>84</v>
@@ -6533,7 +6536,7 @@
         <v>143</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -6574,10 +6577,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6603,13 +6606,13 @@
         <v>108</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -6617,7 +6620,7 @@
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>84</v>
@@ -6659,7 +6662,7 @@
         <v>84</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>93</v>
@@ -6700,10 +6703,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6726,13 +6729,13 @@
         <v>84</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>173</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>174</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -6783,7 +6786,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -6813,7 +6816,7 @@
         <v>84</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -6824,10 +6827,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6850,13 +6853,13 @@
         <v>84</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6907,7 +6910,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6948,10 +6951,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -7029,7 +7032,7 @@
         <v>143</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -7070,13 +7073,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>84</v>
@@ -7098,16 +7101,16 @@
         <v>84</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -7157,7 +7160,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -7166,7 +7169,7 @@
         <v>83</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>145</v>
@@ -7198,10 +7201,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7224,13 +7227,13 @@
         <v>84</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -7281,28 +7284,28 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM35" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AG35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH35" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>84</v>
@@ -7322,10 +7325,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7396,7 +7399,7 @@
         <v>142</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>84</v>
@@ -7405,7 +7408,7 @@
         <v>143</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -7446,10 +7449,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7475,13 +7478,13 @@
         <v>108</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -7489,7 +7492,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>84</v>
@@ -7531,7 +7534,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>93</v>
@@ -7572,10 +7575,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7598,13 +7601,13 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7616,7 +7619,7 @@
         <v>84</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>84</v>
@@ -7655,7 +7658,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7696,10 +7699,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7722,13 +7725,13 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7779,7 +7782,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7820,14 +7823,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7849,16 +7852,16 @@
         <v>139</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7907,7 +7910,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7948,10 +7951,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7974,16 +7977,16 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -8033,7 +8036,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -8048,19 +8051,19 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>84</v>
@@ -8074,10 +8077,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8103,13 +8106,13 @@
         <v>114</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -8135,11 +8138,11 @@
         <v>84</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>84</v>
@@ -8157,7 +8160,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>93</v>
@@ -8172,25 +8175,25 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>84</v>
@@ -8198,10 +8201,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8224,16 +8227,16 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -8259,13 +8262,13 @@
         <v>84</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>84</v>
@@ -8283,7 +8286,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -8298,13 +8301,13 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>84</v>
@@ -8324,10 +8327,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8353,13 +8356,13 @@
         <v>114</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -8370,7 +8373,7 @@
         <v>84</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>84</v>
@@ -8385,13 +8388,13 @@
         <v>84</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>84</v>
@@ -8409,7 +8412,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>93</v>
@@ -8424,22 +8427,22 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
@@ -8450,10 +8453,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8476,16 +8479,16 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8511,19 +8514,19 @@
         <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
@@ -8533,7 +8536,7 @@
         <v>143</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8551,13 +8554,13 @@
         <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>84</v>
@@ -8574,13 +8577,13 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>84</v>
@@ -8602,16 +8605,16 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8637,13 +8640,13 @@
         <v>84</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8661,7 +8664,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8679,13 +8682,13 @@
         <v>84</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>84</v>
@@ -8702,10 +8705,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8731,10 +8734,10 @@
         <v>114</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8761,13 +8764,13 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -8785,7 +8788,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8800,16 +8803,16 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>84</v>
@@ -8826,10 +8829,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8852,16 +8855,16 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8911,7 +8914,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8932,7 +8935,7 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>84</v>
@@ -8952,10 +8955,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8978,13 +8981,13 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -9035,7 +9038,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -9056,7 +9059,7 @@
         <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>84</v>
@@ -9076,10 +9079,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9102,16 +9105,16 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -9137,11 +9140,11 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -9159,7 +9162,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>93</v>
@@ -9174,19 +9177,19 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>84</v>
@@ -9200,10 +9203,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9226,16 +9229,16 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -9285,7 +9288,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>93</v>
@@ -9300,22 +9303,22 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
@@ -9326,10 +9329,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9352,16 +9355,16 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -9411,7 +9414,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9426,22 +9429,22 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -9452,10 +9455,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9478,13 +9481,13 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -9535,7 +9538,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9550,16 +9553,16 @@
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>84</v>
@@ -9576,10 +9579,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9605,10 +9608,10 @@
         <v>237</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -9659,7 +9662,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9674,19 +9677,19 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>84</v>
@@ -9700,10 +9703,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9726,13 +9729,13 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9783,7 +9786,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9798,22 +9801,22 @@
         <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9824,10 +9827,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9850,13 +9853,13 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9907,7 +9910,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9922,16 +9925,16 @@
         <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>84</v>
@@ -9948,10 +9951,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9974,16 +9977,16 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -10009,13 +10012,13 @@
         <v>84</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
@@ -10033,7 +10036,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -10048,13 +10051,13 @@
         <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>84</v>
@@ -10074,10 +10077,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10100,13 +10103,13 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -10157,7 +10160,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -10178,10 +10181,10 @@
         <v>84</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>84</v>
@@ -10198,10 +10201,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10224,16 +10227,16 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -10259,13 +10262,13 @@
         <v>84</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -10283,7 +10286,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10298,19 +10301,19 @@
         <v>106</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>84</v>
@@ -10324,10 +10327,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10350,13 +10353,13 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -10407,28 +10410,28 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>84</v>
@@ -10448,14 +10451,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -10477,13 +10480,13 @@
         <v>139</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M61" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M61" t="s" s="2">
+      <c r="N61" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -10524,7 +10527,7 @@
         <v>142</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>84</v>
@@ -10533,7 +10536,7 @@
         <v>143</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10554,7 +10557,7 @@
         <v>84</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>84</v>
@@ -10574,10 +10577,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10600,19 +10603,19 @@
         <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -10661,7 +10664,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10682,13 +10685,13 @@
         <v>84</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AP62" t="s" s="2">
         <v>84</v>
@@ -10702,10 +10705,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10728,19 +10731,19 @@
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10789,7 +10792,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10810,16 +10813,16 @@
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10830,10 +10833,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10856,16 +10859,16 @@
         <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10915,7 +10918,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10930,16 +10933,16 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>84</v>
@@ -10956,10 +10959,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10982,13 +10985,13 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -11039,7 +11042,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -11054,13 +11057,13 @@
         <v>106</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>84</v>
@@ -11080,10 +11083,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11109,10 +11112,10 @@
         <v>108</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -11163,7 +11166,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -11184,7 +11187,7 @@
         <v>84</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>84</v>
@@ -11204,10 +11207,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11230,13 +11233,13 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -11287,7 +11290,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11302,13 +11305,13 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>84</v>
@@ -11328,10 +11331,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11354,17 +11357,17 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
@@ -11413,7 +11416,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11428,13 +11431,13 @@
         <v>106</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>84</v>
@@ -11454,10 +11457,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11480,16 +11483,16 @@
         <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11515,13 +11518,13 @@
         <v>84</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>84</v>
@@ -11539,7 +11542,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11560,7 +11563,7 @@
         <v>84</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>84</v>
@@ -11580,10 +11583,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11606,13 +11609,13 @@
         <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11663,7 +11666,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11678,13 +11681,13 @@
         <v>106</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>84</v>
@@ -11704,10 +11707,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11730,13 +11733,13 @@
         <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11787,7 +11790,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11802,13 +11805,13 @@
         <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>84</v>
@@ -11828,10 +11831,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11854,16 +11857,16 @@
         <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11913,7 +11916,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11928,13 +11931,13 @@
         <v>106</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>84</v>
@@ -11954,10 +11957,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11980,13 +11983,13 @@
         <v>84</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="M73" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -12037,28 +12040,28 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AG73" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH73" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM73" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>84</v>
@@ -12078,14 +12081,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -12107,13 +12110,13 @@
         <v>139</v>
       </c>
       <c r="L74" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -12154,7 +12157,7 @@
         <v>142</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>84</v>
@@ -12163,7 +12166,7 @@
         <v>143</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -12184,7 +12187,7 @@
         <v>84</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>84</v>
@@ -12204,14 +12207,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -12233,16 +12236,16 @@
         <v>139</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>84</v>
@@ -12291,7 +12294,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12332,10 +12335,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12358,17 +12361,17 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>84</v>
@@ -12417,7 +12420,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12438,13 +12441,13 @@
         <v>84</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AP76" t="s" s="2">
         <v>84</v>
@@ -12458,10 +12461,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12484,17 +12487,17 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12543,7 +12546,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12564,13 +12567,13 @@
         <v>84</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>84</v>
@@ -12584,10 +12587,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12610,19 +12613,19 @@
         <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
@@ -12647,13 +12650,13 @@
         <v>84</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>84</v>
@@ -12671,7 +12674,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12692,13 +12695,13 @@
         <v>84</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>84</v>
@@ -12712,10 +12715,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12738,13 +12741,13 @@
         <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12795,7 +12798,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12816,13 +12819,13 @@
         <v>84</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>84</v>
@@ -12836,10 +12839,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12862,19 +12865,19 @@
         <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
@@ -12923,7 +12926,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12944,7 +12947,7 @@
         <v>84</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>84</v>
@@ -12964,10 +12967,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12990,16 +12993,16 @@
         <v>94</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -13025,13 +13028,13 @@
         <v>84</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>84</v>
@@ -13049,7 +13052,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -13070,13 +13073,13 @@
         <v>84</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AP81" t="s" s="2">
         <v>84</v>
@@ -13090,10 +13093,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13116,19 +13119,19 @@
         <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>84</v>
@@ -13153,13 +13156,13 @@
         <v>84</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>84</v>
@@ -13177,7 +13180,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -13198,13 +13201,13 @@
         <v>84</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>84</v>
@@ -13218,10 +13221,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13244,17 +13247,17 @@
         <v>94</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>84</v>
@@ -13279,13 +13282,13 @@
         <v>84</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>84</v>
@@ -13303,7 +13306,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13324,13 +13327,13 @@
         <v>84</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>84</v>
@@ -13344,10 +13347,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13370,19 +13373,19 @@
         <v>94</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>84</v>
@@ -13407,13 +13410,13 @@
         <v>84</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>84</v>
@@ -13431,7 +13434,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13452,13 +13455,13 @@
         <v>84</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>84</v>
@@ -13472,10 +13475,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13498,13 +13501,13 @@
         <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13555,7 +13558,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13582,7 +13585,7 @@
         <v>84</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>84</v>
@@ -13596,10 +13599,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13622,13 +13625,13 @@
         <v>84</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -13679,28 +13682,28 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM86" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ86" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>84</v>
@@ -13720,14 +13723,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -13749,13 +13752,13 @@
         <v>139</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13796,7 +13799,7 @@
         <v>142</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>84</v>
@@ -13805,7 +13808,7 @@
         <v>143</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13826,7 +13829,7 @@
         <v>84</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>84</v>
@@ -13846,10 +13849,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13872,17 +13875,17 @@
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>84</v>
@@ -13907,13 +13910,13 @@
         <v>84</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>84</v>
@@ -13931,7 +13934,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13958,7 +13961,7 @@
         <v>84</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>84</v>
@@ -13972,10 +13975,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13998,19 +14001,19 @@
         <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>84</v>
@@ -14059,7 +14062,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -14080,13 +14083,13 @@
         <v>84</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AP89" t="s" s="2">
         <v>84</v>
@@ -14100,10 +14103,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14126,19 +14129,19 @@
         <v>94</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>84</v>
@@ -14187,7 +14190,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -14208,13 +14211,13 @@
         <v>84</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AN90" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>84</v>
@@ -14228,10 +14231,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14254,19 +14257,19 @@
         <v>94</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>84</v>
@@ -14315,7 +14318,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14336,13 +14339,13 @@
         <v>84</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>84</v>
@@ -14356,10 +14359,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14382,19 +14385,19 @@
         <v>94</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>84</v>
@@ -14443,7 +14446,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14464,7 +14467,7 @@
         <v>84</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>84</v>
@@ -14484,10 +14487,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14510,17 +14513,17 @@
         <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14569,7 +14572,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14590,7 +14593,7 @@
         <v>84</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>84</v>
@@ -14610,10 +14613,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14636,13 +14639,13 @@
         <v>84</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14693,7 +14696,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14711,10 +14714,10 @@
         <v>84</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>84</v>
@@ -14734,10 +14737,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14760,13 +14763,13 @@
         <v>84</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L95" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="L95" t="s" s="2">
+      <c r="M95" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -14817,28 +14820,28 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM95" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>84</v>
@@ -14858,14 +14861,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -14887,13 +14890,13 @@
         <v>139</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14943,7 +14946,7 @@
         <v>84</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>82</v>
@@ -14964,7 +14967,7 @@
         <v>84</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>84</v>
@@ -14984,14 +14987,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -15013,16 +15016,16 @@
         <v>139</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>84</v>
@@ -15071,7 +15074,7 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -15112,10 +15115,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15138,16 +15141,16 @@
         <v>84</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -15197,7 +15200,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -15218,7 +15221,7 @@
         <v>84</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>84</v>
@@ -15238,10 +15241,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15264,13 +15267,13 @@
         <v>84</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="M99" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -15321,28 +15324,28 @@
         <v>84</v>
       </c>
       <c r="AF99" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM99" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>84</v>
@@ -15362,14 +15365,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -15391,13 +15394,13 @@
         <v>139</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -15447,7 +15450,7 @@
         <v>84</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>82</v>
@@ -15468,7 +15471,7 @@
         <v>84</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>84</v>
@@ -15488,14 +15491,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -15517,16 +15520,16 @@
         <v>139</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>84</v>
@@ -15575,7 +15578,7 @@
         <v>84</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15616,10 +15619,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15642,13 +15645,13 @@
         <v>84</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15699,7 +15702,7 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15720,7 +15723,7 @@
         <v>84</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="AN102" t="s" s="2">
         <v>84</v>
@@ -15740,10 +15743,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15766,13 +15769,13 @@
         <v>84</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15823,7 +15826,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15844,7 +15847,7 @@
         <v>84</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>84</v>
@@ -15864,10 +15867,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15890,13 +15893,13 @@
         <v>84</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15947,7 +15950,7 @@
         <v>84</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15968,7 +15971,7 @@
         <v>84</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="AN104" t="s" s="2">
         <v>84</v>
@@ -15988,10 +15991,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16014,19 +16017,19 @@
         <v>84</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>84</v>
@@ -16075,7 +16078,7 @@
         <v>84</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -16093,10 +16096,10 @@
         <v>84</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>84</v>
@@ -16116,10 +16119,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16142,13 +16145,13 @@
         <v>84</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L106" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="L106" t="s" s="2">
+      <c r="M106" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -16199,28 +16202,28 @@
         <v>84</v>
       </c>
       <c r="AF106" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM106" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>84</v>
@@ -16240,14 +16243,14 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -16269,13 +16272,13 @@
         <v>139</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -16316,7 +16319,7 @@
         <v>142</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>84</v>
@@ -16325,7 +16328,7 @@
         <v>143</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>82</v>
@@ -16346,7 +16349,7 @@
         <v>84</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>84</v>
@@ -16366,10 +16369,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16395,13 +16398,13 @@
         <v>237</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -16451,7 +16454,7 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -16460,7 +16463,7 @@
         <v>93</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>106</v>
@@ -16472,13 +16475,13 @@
         <v>84</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO108" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AP108" t="s" s="2">
         <v>84</v>
@@ -16492,10 +16495,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16521,20 +16524,20 @@
         <v>237</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q109" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="R109" t="s" s="2">
         <v>84</v>
@@ -16579,7 +16582,7 @@
         <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>82</v>
@@ -16588,7 +16591,7 @@
         <v>93</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>106</v>
@@ -16600,16 +16603,16 @@
         <v>84</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>84</v>
@@ -16620,10 +16623,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16646,16 +16649,16 @@
         <v>84</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -16705,7 +16708,7 @@
         <v>84</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>82</v>
@@ -16723,22 +16726,22 @@
         <v>84</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AQ110" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AR110" t="s" s="2">
         <v>84</v>
@@ -16746,10 +16749,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16772,13 +16775,13 @@
         <v>84</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16829,7 +16832,7 @@
         <v>84</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>82</v>
@@ -16847,16 +16850,16 @@
         <v>84</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>84</v>
@@ -16870,10 +16873,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16896,13 +16899,13 @@
         <v>84</v>
       </c>
       <c r="K112" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L112" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="L112" t="s" s="2">
+      <c r="M112" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -16953,28 +16956,28 @@
         <v>84</v>
       </c>
       <c r="AF112" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM112" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>84</v>
@@ -16994,14 +16997,14 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
@@ -17023,13 +17026,13 @@
         <v>139</v>
       </c>
       <c r="L113" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M113" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M113" t="s" s="2">
+      <c r="N113" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -17070,7 +17073,7 @@
         <v>142</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>84</v>
@@ -17079,7 +17082,7 @@
         <v>143</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>82</v>
@@ -17100,7 +17103,7 @@
         <v>84</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AN113" t="s" s="2">
         <v>84</v>
@@ -17120,10 +17123,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17146,19 +17149,19 @@
         <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>84</v>
@@ -17207,7 +17210,7 @@
         <v>84</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>82</v>
@@ -17228,30 +17231,30 @@
         <v>84</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR114" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17277,20 +17280,20 @@
         <v>114</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q115" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="R115" t="s" s="2">
         <v>84</v>
@@ -17311,13 +17314,13 @@
         <v>84</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>84</v>
@@ -17335,7 +17338,7 @@
         <v>84</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>82</v>
@@ -17356,13 +17359,13 @@
         <v>84</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AN115" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO115" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AP115" t="s" s="2">
         <v>84</v>
@@ -17376,10 +17379,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17402,17 +17405,17 @@
         <v>94</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>84</v>
@@ -17461,7 +17464,7 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>82</v>
@@ -17482,13 +17485,13 @@
         <v>84</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AN116" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO116" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AP116" t="s" s="2">
         <v>84</v>
@@ -17502,10 +17505,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17531,14 +17534,14 @@
         <v>108</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>84</v>
@@ -17587,7 +17590,7 @@
         <v>84</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>82</v>
@@ -17596,7 +17599,7 @@
         <v>93</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>106</v>
@@ -17608,13 +17611,13 @@
         <v>84</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AN117" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO117" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AP117" t="s" s="2">
         <v>84</v>
@@ -17628,10 +17631,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17657,16 +17660,16 @@
         <v>114</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>84</v>
@@ -17715,7 +17718,7 @@
         <v>84</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>82</v>
@@ -17736,13 +17739,13 @@
         <v>84</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO118" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AP118" t="s" s="2">
         <v>84</v>
@@ -17756,10 +17759,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17782,16 +17785,16 @@
         <v>84</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -17841,7 +17844,7 @@
         <v>84</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>82</v>
@@ -17859,10 +17862,10 @@
         <v>84</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>84</v>
@@ -17871,21 +17874,21 @@
         <v>84</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AQ119" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR119" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17908,13 +17911,13 @@
         <v>84</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -17965,7 +17968,7 @@
         <v>84</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>82</v>
@@ -17986,10 +17989,10 @@
         <v>84</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>84</v>
@@ -18006,10 +18009,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18032,13 +18035,13 @@
         <v>84</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -18089,7 +18092,7 @@
         <v>84</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>82</v>
@@ -18107,10 +18110,10 @@
         <v>84</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AM121" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AN121" t="s" s="2">
         <v>84</v>
@@ -18130,10 +18133,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18156,13 +18159,13 @@
         <v>84</v>
       </c>
       <c r="K122" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="L122" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="L122" t="s" s="2">
+      <c r="M122" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -18213,28 +18216,28 @@
         <v>84</v>
       </c>
       <c r="AF122" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM122" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>84</v>
@@ -18254,14 +18257,14 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -18283,13 +18286,13 @@
         <v>139</v>
       </c>
       <c r="L123" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M123" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M123" t="s" s="2">
+      <c r="N123" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -18339,7 +18342,7 @@
         <v>84</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>82</v>
@@ -18360,7 +18363,7 @@
         <v>84</v>
       </c>
       <c r="AM123" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AN123" t="s" s="2">
         <v>84</v>
@@ -18380,14 +18383,14 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
@@ -18409,16 +18412,16 @@
         <v>139</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>84</v>
@@ -18467,7 +18470,7 @@
         <v>84</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>82</v>
@@ -18508,10 +18511,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18534,16 +18537,16 @@
         <v>84</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -18569,13 +18572,13 @@
         <v>84</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>84</v>
@@ -18593,7 +18596,7 @@
         <v>84</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>93</v>
@@ -18611,16 +18614,16 @@
         <v>84</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="AN125" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AP125" t="s" s="2">
         <v>84</v>
@@ -18634,10 +18637,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18660,13 +18663,13 @@
         <v>84</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -18693,13 +18696,13 @@
         <v>84</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>84</v>
@@ -18717,7 +18720,7 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>82</v>
@@ -18735,16 +18738,16 @@
         <v>84</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AM126" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AN126" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AP126" t="s" s="2">
         <v>84</v>
@@ -18758,10 +18761,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18784,13 +18787,13 @@
         <v>84</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -18841,7 +18844,7 @@
         <v>84</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>82</v>
@@ -18856,13 +18859,13 @@
         <v>106</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AN127" t="s" s="2">
         <v>84</v>
@@ -18882,14 +18885,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -18908,16 +18911,16 @@
         <v>84</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -18967,7 +18970,7 @@
         <v>84</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>82</v>
@@ -18988,7 +18991,7 @@
         <v>84</v>
       </c>
       <c r="AM128" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="AN128" t="s" s="2">
         <v>84</v>
@@ -19008,10 +19011,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19034,16 +19037,16 @@
         <v>84</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -19093,7 +19096,7 @@
         <v>84</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
@@ -19108,13 +19111,13 @@
         <v>106</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AN129" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -237,6 +237,15 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
+    <t>Mapping: Virtual Patient Record (VPR)</t>
+  </si>
+  <si>
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
@@ -250,15 +259,6 @@
   </si>
   <si>
     <t>Mapping: HL7 v2 Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
   </si>
   <si>
     <t>Prescription
@@ -656,16 +656,16 @@
     <t>Coding.code</t>
   </si>
   <si>
+    <t>1707: source value from PRESCRIPTION - MAIL/WINDOW/PARK (#52-11)</t>
+  </si>
+  <si>
+    <t>RxOut.RxOutpat.RxStatus</t>
+  </si>
+  <si>
     <t>./code</t>
   </si>
   <si>
     <t>C*E.1</t>
-  </si>
-  <si>
-    <t>1707: source value from PRESCRIPTION - MAIL/WINDOW/PARK (#52-11)</t>
-  </si>
-  <si>
-    <t>RxOut.RxOutpat.RxStatus</t>
   </si>
   <si>
     <t>MedicationRequest.extension:medicationrequest-pharmacyOrderStatus.value[x].display</t>
@@ -940,6 +940,9 @@
     <t>http://va.gov/fhir/ValueSet/VSVFOutMedRequestStatus</t>
   </si>
   <si>
+    <t>799: terminologyMaps using VF_OutMedRequestStatus on PRESCRIPTION - STATUS (#52-100)</t>
+  </si>
+  <si>
     <t>Request.status</t>
   </si>
   <si>
@@ -950,9 +953,6 @@
   </si>
   <si>
     <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>799: terminologyMaps using VF_OutMedRequestStatus on PRESCRIPTION - STATUS (#52-100)</t>
   </si>
   <si>
     <t>MedicationRequest.statusReason</t>
@@ -1011,6 +1011,9 @@
     <t>http://hl7.org/fhir/ValueSet/medicationrequest-intent</t>
   </si>
   <si>
+    <t>801: fixed value = #order</t>
+  </si>
+  <si>
     <t>Request.intent</t>
   </si>
   <si>
@@ -1018,9 +1021,6 @@
   </si>
   <si>
     <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>801: fixed value = #order</t>
   </si>
   <si>
     <t>MedicationRequest.category</t>
@@ -1178,6 +1178,9 @@
     <t>The subject on a medication request is mandatory.  For the secondary use case where the actual subject is not provided, there still must be an anonymized subject specified.</t>
   </si>
   <si>
+    <t>806: reference from PRESCRIPTION - PATIENT (#52-2)</t>
+  </si>
+  <si>
     <t>Request.subject</t>
   </si>
   <si>
@@ -1195,9 +1198,6 @@
     <t>PID-3-Patient ID List</t>
   </si>
   <si>
-    <t>806: reference from PRESCRIPTION - PATIENT (#52-2)</t>
-  </si>
-  <si>
     <t>MedicationRequest.encounter</t>
   </si>
   <si>
@@ -1214,6 +1214,9 @@
     <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter."    If there is a need to link to episodes of care they will be handled with an extension.</t>
   </si>
   <si>
+    <t>1724: reference</t>
+  </si>
+  <si>
     <t>Request.context</t>
   </si>
   <si>
@@ -1224,9 +1227,6 @@
   </si>
   <si>
     <t>PV1-19-Visit Number</t>
-  </si>
-  <si>
-    <t>1724: reference</t>
   </si>
   <si>
     <t>MedicationRequest.supportingInformation</t>
@@ -1285,13 +1285,13 @@
     <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
   </si>
   <si>
+    <t>808: reference from PRESCRIPTION - PROVIDER (#52-4)</t>
+  </si>
+  <si>
     <t>Request.requester</t>
   </si>
   <si>
     <t>FiveWs.author</t>
-  </si>
-  <si>
-    <t>808: reference from PRESCRIPTION - PROVIDER (#52-4)</t>
   </si>
   <si>
     <t>MedicationRequest.performer</t>
@@ -1440,13 +1440,13 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
+    <t>1705: source value from PRESCRIPTION - INDICATION FOR USE (#52-128)</t>
+  </si>
+  <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>1705: source value from PRESCRIPTION - INDICATION FOR USE (#52-128)</t>
   </si>
   <si>
     <t>MedicationRequest.reasonReference</t>
@@ -2203,13 +2203,13 @@
     <t>Period.end</t>
   </si>
   <si>
+    <t>815: source value from PRESCRIPTION - EXPIRATION DATE (#52-26)</t>
+  </si>
+  <si>
     <t>./high</t>
   </si>
   <si>
     <t>DR.2</t>
-  </si>
-  <si>
-    <t>815: source value from PRESCRIPTION - EXPIRATION DATE (#52-26)</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.numberOfRepeatsAllowed</t>
@@ -2228,6 +2228,12 @@
     <t>If displaying "number of authorized fills", add 1 to this number.</t>
   </si>
   <si>
+    <t>816: source value from PRESCRIPTION - # OF REFILLS (#52-9)</t>
+  </si>
+  <si>
+    <t>RxOut.RxOutpat.MaxRefills</t>
+  </si>
+  <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Quantity</t>
   </si>
   <si>
@@ -2235,12 +2241,6 @@
   </si>
   <si>
     <t>RXE-12-Number of Refills</t>
-  </si>
-  <si>
-    <t>816: source value from PRESCRIPTION - # OF REFILLS (#52-9)</t>
-  </si>
-  <si>
-    <t>RxOut.RxOutpat.MaxRefills</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.quantity</t>
@@ -2289,16 +2289,16 @@
     <t>Quantity.value</t>
   </si>
   <si>
+    <t>1669: source value from PRESCRIPTION - QTY (#52-7)</t>
+  </si>
+  <si>
+    <t>Pharmacy: quantity</t>
+  </si>
+  <si>
     <t>PQ.value, CO.value, MO.value, IVL.high or IVL.low depending on the value</t>
   </si>
   <si>
     <t>SN.2  / CQ - N/A</t>
-  </si>
-  <si>
-    <t>1669: source value from PRESCRIPTION - QTY (#52-7)</t>
-  </si>
-  <si>
-    <t>Pharmacy: quantity</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.quantity.comparator</t>
@@ -2407,16 +2407,16 @@
     <t>In some situations, this attribute may be used instead of quantity to identify the amount supplied by how long it is expected to last, rather than the physical quantity issued, e.g. 90 days supply of medication (based on an ordered dosage). When possible, it is always better to specify quantity, as this tends to be more precise. expectedSupplyDuration will always be an estimate that can be influenced by external factors.</t>
   </si>
   <si>
+    <t>1670: source value from PRESCRIPTION - DAYS SUPPLY (#52-8)</t>
+  </si>
+  <si>
+    <t>Pharmacy: daysSupply</t>
+  </si>
+  <si>
     <t>Message/Body/NewRx/MedicationPrescribed/Substitutions</t>
   </si>
   <si>
     <t>expectedUseTime</t>
-  </si>
-  <si>
-    <t>1670: source value from PRESCRIPTION - DAYS SUPPLY (#52-8)</t>
-  </si>
-  <si>
-    <t>Pharmacy: daysSupply</t>
   </si>
   <si>
     <t>MedicationRequest.dispenseRequest.performer</t>
@@ -2923,14 +2923,14 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="128.41796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="88.6875" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="43.94140625" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="128.41796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3169,22 +3169,22 @@
         <v>88</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM2" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN2" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AP2" t="s" s="2">
         <v>91</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP2" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ2" t="s" s="2">
         <v>84</v>
@@ -3295,7 +3295,7 @@
         <v>84</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="AL3" t="s" s="2">
         <v>84</v>
@@ -3310,7 +3310,7 @@
         <v>84</v>
       </c>
       <c r="AP3" t="s" s="2">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="AQ3" t="s" s="2">
         <v>84</v>
@@ -3803,16 +3803,16 @@
         <v>84</v>
       </c>
       <c r="AM7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP7" t="s" s="2">
         <v>129</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO7" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP7" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ7" t="s" s="2">
         <v>84</v>
@@ -3929,16 +3929,16 @@
         <v>84</v>
       </c>
       <c r="AM8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP8" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO8" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP8" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ8" t="s" s="2">
         <v>84</v>
@@ -4301,16 +4301,16 @@
         <v>84</v>
       </c>
       <c r="AM11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO11" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP11" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ11" t="s" s="2">
         <v>84</v>
@@ -4551,16 +4551,16 @@
         <v>84</v>
       </c>
       <c r="AM13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO13" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP13" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO13" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP13" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ13" t="s" s="2">
         <v>84</v>
@@ -4675,16 +4675,16 @@
         <v>84</v>
       </c>
       <c r="AM14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO14" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP14" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO14" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP14" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ14" t="s" s="2">
         <v>84</v>
@@ -4799,16 +4799,16 @@
         <v>84</v>
       </c>
       <c r="AM15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO15" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP15" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO15" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP15" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ15" t="s" s="2">
         <v>84</v>
@@ -4925,16 +4925,16 @@
         <v>84</v>
       </c>
       <c r="AM16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO16" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP16" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP16" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ16" t="s" s="2">
         <v>84</v>
@@ -5053,22 +5053,22 @@
         <v>84</v>
       </c>
       <c r="AM17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP17" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="AN17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO17" t="s" s="2">
+      <c r="AQ17" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR17" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="AP17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ17" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR17" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -5179,22 +5179,22 @@
         <v>84</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP18" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="AN18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO18" t="s" s="2">
+      <c r="AQ18" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR18" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AP18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ18" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR18" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="19" hidden="true">
@@ -5299,28 +5299,28 @@
         <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>84</v>
+        <v>206</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>84</v>
+        <v>207</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>206</v>
+        <v>84</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>207</v>
+        <v>84</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>208</v>
       </c>
       <c r="AQ19" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR19" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="AR19" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="20" hidden="true">
@@ -5431,22 +5431,22 @@
         <v>84</v>
       </c>
       <c r="AM20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP20" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AN20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO20" t="s" s="2">
+      <c r="AQ20" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR20" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ20" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR20" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -5559,22 +5559,22 @@
         <v>84</v>
       </c>
       <c r="AM21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP21" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="AN21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO21" t="s" s="2">
+      <c r="AQ21" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR21" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ21" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR21" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="22" hidden="true">
@@ -5809,16 +5809,16 @@
         <v>84</v>
       </c>
       <c r="AM23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP23" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ23" t="s" s="2">
         <v>84</v>
@@ -6059,16 +6059,16 @@
         <v>84</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP25" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP25" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ25" t="s" s="2">
         <v>84</v>
@@ -6177,25 +6177,25 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>84</v>
+        <v>238</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>84</v>
+        <v>239</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP26" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>238</v>
-      </c>
       <c r="AQ26" t="s" s="2">
-        <v>239</v>
+        <v>84</v>
       </c>
       <c r="AR26" t="s" s="2">
         <v>84</v>
@@ -6433,16 +6433,16 @@
         <v>84</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP28" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ28" t="s" s="2">
         <v>84</v>
@@ -6683,16 +6683,16 @@
         <v>84</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP30" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO30" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP30" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ30" t="s" s="2">
         <v>84</v>
@@ -6801,22 +6801,22 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>84</v>
+        <v>249</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO31" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP31" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP31" t="s" s="2">
-        <v>249</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -7181,22 +7181,22 @@
         <v>84</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP34" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AN34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO34" t="s" s="2">
+      <c r="AQ34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR34" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR34" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="35" hidden="true">
@@ -7305,16 +7305,16 @@
         <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO35" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP35" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -7555,16 +7555,16 @@
         <v>84</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -7679,16 +7679,16 @@
         <v>84</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP38" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ38" t="s" s="2">
         <v>84</v>
@@ -7931,16 +7931,16 @@
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP40" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP40" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ40" t="s" s="2">
         <v>84</v>
@@ -8051,28 +8051,28 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AQ41" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="AO41" t="s" s="2">
+      <c r="AR41" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ41" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR41" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="42" hidden="true">
@@ -8178,22 +8178,22 @@
         <v>298</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AO42" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="AN42" t="s" s="2">
+      <c r="AP42" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="AO42" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP42" t="s" s="2">
+      <c r="AQ42" t="s" s="2">
         <v>302</v>
-      </c>
-      <c r="AQ42" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>84</v>
@@ -8301,22 +8301,22 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>311</v>
       </c>
-      <c r="AL43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -8433,19 +8433,19 @@
         <v>84</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="AN44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP44" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="AO44" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP44" t="s" s="2">
+      <c r="AQ44" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="AQ44" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>84</v>
@@ -8554,22 +8554,22 @@
         <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO45" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AM45" t="s" s="2">
+      <c r="AP45" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AN45" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP45" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AQ45" t="s" s="2">
-        <v>84</v>
+        <v>323</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>84</v>
@@ -8682,22 +8682,22 @@
         <v>84</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AP46" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AN46" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP46" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AQ46" t="s" s="2">
-        <v>84</v>
+        <v>323</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>84</v>
@@ -8803,25 +8803,25 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AL47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP47" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AN47" t="s" s="2">
+      <c r="AQ47" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP47" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ47" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>84</v>
@@ -8935,16 +8935,16 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP48" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO48" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP48" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -9059,16 +9059,16 @@
         <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO49" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP49" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO49" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP49" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -9177,28 +9177,28 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
         <v>362</v>
       </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AP50" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AN50" t="s" s="2">
+      <c r="AQ50" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AO50" t="s" s="2">
+      <c r="AR50" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ50" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR50" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="51" hidden="true">
@@ -9306,25 +9306,25 @@
         <v>371</v>
       </c>
       <c r="AL51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AM51" t="s" s="2">
+      <c r="AO51" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="AN51" t="s" s="2">
+      <c r="AP51" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="AO51" t="s" s="2">
+      <c r="AQ51" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="AP51" t="s" s="2">
+      <c r="AR51" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="AQ51" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR51" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="52" hidden="true">
@@ -9432,25 +9432,25 @@
         <v>382</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>299</v>
+        <v>84</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AP52" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="AO52" t="s" s="2">
+      <c r="AQ52" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AP52" t="s" s="2">
+      <c r="AR52" t="s" s="2">
         <v>386</v>
-      </c>
-      <c r="AQ52" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR52" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="53" hidden="true">
@@ -9553,25 +9553,25 @@
         <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AL53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AO53" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP53" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AN53" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP53" t="s" s="2">
-        <v>84</v>
-      </c>
       <c r="AQ53" t="s" s="2">
-        <v>84</v>
+        <v>385</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>84</v>
@@ -9677,28 +9677,28 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN54" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AL54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AP54" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AQ54" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AO54" t="s" s="2">
+      <c r="AR54" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AP54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ54" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR54" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="55" hidden="true">
@@ -9807,7 +9807,7 @@
         <v>84</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>373</v>
+        <v>84</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>406</v>
@@ -9816,10 +9816,10 @@
         <v>84</v>
       </c>
       <c r="AP55" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AQ55" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AQ55" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>84</v>
@@ -9925,25 +9925,25 @@
         <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>412</v>
       </c>
-      <c r="AL56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP56" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AQ56" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP56" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ56" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>84</v>
@@ -10051,22 +10051,22 @@
         <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AL57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP57" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP57" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -10181,19 +10181,19 @@
         <v>84</v>
       </c>
       <c r="AM58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AQ58" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ58" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>84</v>
@@ -10301,28 +10301,28 @@
         <v>106</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="AL59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AP59" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AQ59" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="AO59" t="s" s="2">
+      <c r="AR59" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR59" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="60" hidden="true">
@@ -10431,16 +10431,16 @@
         <v>84</v>
       </c>
       <c r="AM60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -10557,16 +10557,16 @@
         <v>84</v>
       </c>
       <c r="AM61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO61" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP61" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -10685,22 +10685,22 @@
         <v>84</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP62" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="AN62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO62" t="s" s="2">
+      <c r="AQ62" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR62" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AP62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ62" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR62" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="63" hidden="true">
@@ -10807,28 +10807,28 @@
         <v>106</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>84</v>
+        <v>456</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>456</v>
+        <v>84</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP63" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="AP63" t="s" s="2">
+      <c r="AQ63" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR63" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="AQ63" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR63" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="64" hidden="true">
@@ -10933,25 +10933,25 @@
         <v>106</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>464</v>
       </c>
-      <c r="AL64" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AM64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AP64" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AQ64" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="AO64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ64" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>84</v>
@@ -11057,22 +11057,22 @@
         <v>106</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="AL65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM65" t="s" s="2">
+      <c r="AO65" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP65" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO65" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -11187,16 +11187,16 @@
         <v>84</v>
       </c>
       <c r="AM66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP66" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -11305,22 +11305,22 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN67" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="AL67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP67" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP67" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -11431,22 +11431,22 @@
         <v>106</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN68" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="AL68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
@@ -11563,16 +11563,16 @@
         <v>84</v>
       </c>
       <c r="AM69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP69" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP69" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -11681,22 +11681,22 @@
         <v>106</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN70" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="AL70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11805,22 +11805,22 @@
         <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="AL71" t="s" s="2">
+      <c r="AO71" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="AM71" t="s" s="2">
+      <c r="AP71" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP71" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
@@ -11931,22 +11931,22 @@
         <v>106</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN72" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="AL72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -12061,16 +12061,16 @@
         <v>84</v>
       </c>
       <c r="AM73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP73" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
@@ -12187,16 +12187,16 @@
         <v>84</v>
       </c>
       <c r="AM74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
@@ -12315,16 +12315,16 @@
         <v>84</v>
       </c>
       <c r="AM75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP75" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
@@ -12441,22 +12441,22 @@
         <v>84</v>
       </c>
       <c r="AM76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="AN76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO76" t="s" s="2">
+      <c r="AQ76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR76" t="s" s="2">
         <v>528</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ76" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR76" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="77" hidden="true">
@@ -12567,22 +12567,22 @@
         <v>84</v>
       </c>
       <c r="AM77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP77" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="AN77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO77" t="s" s="2">
+      <c r="AQ77" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR77" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="AP77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ77" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR77" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="78" hidden="true">
@@ -12695,22 +12695,22 @@
         <v>84</v>
       </c>
       <c r="AM78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP78" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="AN78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO78" t="s" s="2">
+      <c r="AQ78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR78" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="AP78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ78" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR78" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="79" hidden="true">
@@ -12819,22 +12819,22 @@
         <v>84</v>
       </c>
       <c r="AM79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP79" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="AN79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO79" t="s" s="2">
+      <c r="AQ79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR79" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="AP79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ79" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR79" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="80" hidden="true">
@@ -12947,16 +12947,16 @@
         <v>84</v>
       </c>
       <c r="AM80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP80" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO80" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP80" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>
@@ -13073,22 +13073,22 @@
         <v>84</v>
       </c>
       <c r="AM81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP81" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="AN81" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO81" t="s" s="2">
+      <c r="AQ81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR81" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="AP81" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ81" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR81" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="82" hidden="true">
@@ -13201,22 +13201,22 @@
         <v>84</v>
       </c>
       <c r="AM82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP82" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="AN82" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO82" t="s" s="2">
+      <c r="AQ82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR82" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ82" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR82" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="83" hidden="true">
@@ -13327,22 +13327,22 @@
         <v>84</v>
       </c>
       <c r="AM83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP83" t="s" s="2">
         <v>583</v>
       </c>
-      <c r="AN83" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO83" t="s" s="2">
+      <c r="AQ83" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR83" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ83" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR83" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="84" hidden="true">
@@ -13455,22 +13455,22 @@
         <v>84</v>
       </c>
       <c r="AM84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP84" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="AN84" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO84" t="s" s="2">
+      <c r="AQ84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR84" t="s" s="2">
         <v>594</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ84" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR84" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="85" hidden="true">
@@ -13585,16 +13585,16 @@
         <v>84</v>
       </c>
       <c r="AO85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ85" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR85" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="AP85" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ85" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR85" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="86" hidden="true">
@@ -13703,16 +13703,16 @@
         <v>84</v>
       </c>
       <c r="AM86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP86" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP86" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -13829,16 +13829,16 @@
         <v>84</v>
       </c>
       <c r="AM87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP87" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP87" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -13961,16 +13961,16 @@
         <v>84</v>
       </c>
       <c r="AO88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ88" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR88" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="AP88" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ88" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR88" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="89" hidden="true">
@@ -14083,22 +14083,22 @@
         <v>84</v>
       </c>
       <c r="AM89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP89" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="AN89" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO89" t="s" s="2">
+      <c r="AQ89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR89" t="s" s="2">
         <v>618</v>
-      </c>
-      <c r="AP89" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ89" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR89" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="90" hidden="true">
@@ -14211,22 +14211,22 @@
         <v>84</v>
       </c>
       <c r="AM90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP90" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="AN90" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO90" t="s" s="2">
+      <c r="AQ90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR90" t="s" s="2">
         <v>627</v>
-      </c>
-      <c r="AP90" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ90" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR90" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="91" hidden="true">
@@ -14339,22 +14339,22 @@
         <v>84</v>
       </c>
       <c r="AM91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP91" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="AN91" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO91" t="s" s="2">
+      <c r="AQ91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR91" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="AP91" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ91" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR91" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="92" hidden="true">
@@ -14467,16 +14467,16 @@
         <v>84</v>
       </c>
       <c r="AM92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP92" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP92" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>84</v>
@@ -14593,16 +14593,16 @@
         <v>84</v>
       </c>
       <c r="AM93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP93" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>
@@ -14714,19 +14714,19 @@
         <v>84</v>
       </c>
       <c r="AL94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO94" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="AM94" t="s" s="2">
+      <c r="AP94" t="s" s="2">
         <v>655</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP94" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
@@ -14841,16 +14841,16 @@
         <v>84</v>
       </c>
       <c r="AM95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP95" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
@@ -14967,16 +14967,16 @@
         <v>84</v>
       </c>
       <c r="AM96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP96" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ96" t="s" s="2">
         <v>84</v>
@@ -15095,16 +15095,16 @@
         <v>84</v>
       </c>
       <c r="AM97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP97" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ97" t="s" s="2">
         <v>84</v>
@@ -15221,16 +15221,16 @@
         <v>84</v>
       </c>
       <c r="AM98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP98" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>84</v>
@@ -15345,16 +15345,16 @@
         <v>84</v>
       </c>
       <c r="AM99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP99" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ99" t="s" s="2">
         <v>84</v>
@@ -15471,16 +15471,16 @@
         <v>84</v>
       </c>
       <c r="AM100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP100" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP100" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ100" t="s" s="2">
         <v>84</v>
@@ -15599,16 +15599,16 @@
         <v>84</v>
       </c>
       <c r="AM101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP101" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>84</v>
@@ -15723,16 +15723,16 @@
         <v>84</v>
       </c>
       <c r="AM102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP102" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ102" t="s" s="2">
         <v>84</v>
@@ -15847,16 +15847,16 @@
         <v>84</v>
       </c>
       <c r="AM103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP103" t="s" s="2">
         <v>675</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
@@ -15971,16 +15971,16 @@
         <v>84</v>
       </c>
       <c r="AM104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP104" t="s" s="2">
         <v>675</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP104" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ104" t="s" s="2">
         <v>84</v>
@@ -16096,19 +16096,19 @@
         <v>84</v>
       </c>
       <c r="AL105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO105" t="s" s="2">
         <v>685</v>
       </c>
-      <c r="AM105" t="s" s="2">
+      <c r="AP105" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP105" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ105" t="s" s="2">
         <v>84</v>
@@ -16223,16 +16223,16 @@
         <v>84</v>
       </c>
       <c r="AM106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP106" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP106" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ106" t="s" s="2">
         <v>84</v>
@@ -16349,16 +16349,16 @@
         <v>84</v>
       </c>
       <c r="AM107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP107" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP107" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ107" t="s" s="2">
         <v>84</v>
@@ -16475,22 +16475,22 @@
         <v>84</v>
       </c>
       <c r="AM108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP108" t="s" s="2">
         <v>695</v>
       </c>
-      <c r="AN108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO108" t="s" s="2">
+      <c r="AQ108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR108" t="s" s="2">
         <v>696</v>
-      </c>
-      <c r="AP108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ108" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR108" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="109" hidden="true">
@@ -16597,28 +16597,28 @@
         <v>106</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>84</v>
+        <v>703</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>703</v>
+        <v>84</v>
       </c>
       <c r="AN109" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP109" t="s" s="2">
         <v>704</v>
       </c>
-      <c r="AP109" t="s" s="2">
+      <c r="AQ109" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR109" t="s" s="2">
         <v>705</v>
-      </c>
-      <c r="AQ109" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR109" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="110" hidden="true">
@@ -16723,13 +16723,13 @@
         <v>106</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>84</v>
+        <v>711</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>712</v>
+        <v>84</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>84</v>
@@ -16741,10 +16741,10 @@
         <v>714</v>
       </c>
       <c r="AQ110" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR110" t="s" s="2">
         <v>715</v>
-      </c>
-      <c r="AR110" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="111" hidden="true">
@@ -16850,25 +16850,25 @@
         <v>84</v>
       </c>
       <c r="AL111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO111" t="s" s="2">
         <v>719</v>
       </c>
-      <c r="AM111" t="s" s="2">
+      <c r="AP111" t="s" s="2">
         <v>720</v>
       </c>
-      <c r="AN111" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO111" t="s" s="2">
+      <c r="AQ111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR111" t="s" s="2">
         <v>721</v>
-      </c>
-      <c r="AP111" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ111" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR111" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="112" hidden="true">
@@ -16977,16 +16977,16 @@
         <v>84</v>
       </c>
       <c r="AM112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP112" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO112" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP112" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>84</v>
@@ -17103,16 +17103,16 @@
         <v>84</v>
       </c>
       <c r="AM113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP113" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO113" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP113" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ113" t="s" s="2">
         <v>84</v>
@@ -17225,19 +17225,19 @@
         <v>106</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>84</v>
+        <v>731</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>732</v>
+        <v>84</v>
       </c>
       <c r="AP114" t="s" s="2">
         <v>733</v>
@@ -17359,22 +17359,22 @@
         <v>84</v>
       </c>
       <c r="AM115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP115" t="s" s="2">
         <v>743</v>
       </c>
-      <c r="AN115" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO115" t="s" s="2">
+      <c r="AQ115" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR115" t="s" s="2">
         <v>744</v>
-      </c>
-      <c r="AP115" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ115" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR115" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="116" hidden="true">
@@ -17485,22 +17485,22 @@
         <v>84</v>
       </c>
       <c r="AM116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP116" t="s" s="2">
         <v>750</v>
       </c>
-      <c r="AN116" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO116" t="s" s="2">
+      <c r="AQ116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR116" t="s" s="2">
         <v>751</v>
-      </c>
-      <c r="AP116" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ116" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR116" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="117" hidden="true">
@@ -17611,22 +17611,22 @@
         <v>84</v>
       </c>
       <c r="AM117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP117" t="s" s="2">
         <v>758</v>
       </c>
-      <c r="AN117" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO117" t="s" s="2">
+      <c r="AQ117" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR117" t="s" s="2">
         <v>751</v>
-      </c>
-      <c r="AP117" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ117" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR117" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="118" hidden="true">
@@ -17739,22 +17739,22 @@
         <v>84</v>
       </c>
       <c r="AM118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP118" t="s" s="2">
         <v>765</v>
       </c>
-      <c r="AN118" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO118" t="s" s="2">
+      <c r="AQ118" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR118" t="s" s="2">
         <v>751</v>
-      </c>
-      <c r="AP118" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ118" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR118" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="119" hidden="true">
@@ -17859,10 +17859,10 @@
         <v>106</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>84</v>
+        <v>770</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>770</v>
+        <v>84</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>771</v>
@@ -17871,16 +17871,16 @@
         <v>84</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>84</v>
+        <v>772</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AQ119" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR119" t="s" s="2">
-        <v>773</v>
+        <v>84</v>
       </c>
     </row>
     <row r="120" hidden="true">
@@ -17989,19 +17989,19 @@
         <v>84</v>
       </c>
       <c r="AM120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP120" t="s" s="2">
         <v>778</v>
       </c>
-      <c r="AN120" t="s" s="2">
+      <c r="AQ120" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="AO120" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP120" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ120" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AR120" t="s" s="2">
         <v>84</v>
@@ -18110,19 +18110,19 @@
         <v>84</v>
       </c>
       <c r="AL121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO121" t="s" s="2">
         <v>782</v>
       </c>
-      <c r="AM121" t="s" s="2">
+      <c r="AP121" t="s" s="2">
         <v>783</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO121" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP121" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ121" t="s" s="2">
         <v>84</v>
@@ -18237,16 +18237,16 @@
         <v>84</v>
       </c>
       <c r="AM122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP122" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO122" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP122" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>84</v>
@@ -18363,16 +18363,16 @@
         <v>84</v>
       </c>
       <c r="AM123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP123" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO123" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP123" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ123" t="s" s="2">
         <v>84</v>
@@ -18491,16 +18491,16 @@
         <v>84</v>
       </c>
       <c r="AM124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP124" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP124" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ124" t="s" s="2">
         <v>84</v>
@@ -18614,25 +18614,25 @@
         <v>84</v>
       </c>
       <c r="AL125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO125" t="s" s="2">
         <v>782</v>
       </c>
-      <c r="AM125" t="s" s="2">
+      <c r="AP125" t="s" s="2">
         <v>793</v>
       </c>
-      <c r="AN125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO125" t="s" s="2">
+      <c r="AQ125" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR125" t="s" s="2">
         <v>794</v>
-      </c>
-      <c r="AP125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ125" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR125" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="126" hidden="true">
@@ -18738,25 +18738,25 @@
         <v>84</v>
       </c>
       <c r="AL126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO126" t="s" s="2">
         <v>800</v>
       </c>
-      <c r="AM126" t="s" s="2">
+      <c r="AP126" t="s" s="2">
         <v>801</v>
       </c>
-      <c r="AN126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO126" t="s" s="2">
+      <c r="AQ126" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AR126" t="s" s="2">
         <v>802</v>
-      </c>
-      <c r="AP126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ126" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR126" t="s" s="2">
-        <v>84</v>
       </c>
     </row>
     <row r="127" hidden="true">
@@ -18859,22 +18859,22 @@
         <v>106</v>
       </c>
       <c r="AK127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM127" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN127" t="s" s="2">
         <v>807</v>
       </c>
-      <c r="AL127" t="s" s="2">
+      <c r="AO127" t="s" s="2">
         <v>800</v>
       </c>
-      <c r="AM127" t="s" s="2">
+      <c r="AP127" t="s" s="2">
         <v>808</v>
-      </c>
-      <c r="AN127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO127" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP127" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>84</v>
@@ -18991,16 +18991,16 @@
         <v>84</v>
       </c>
       <c r="AM128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AO128" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP128" t="s" s="2">
         <v>815</v>
-      </c>
-      <c r="AN128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO128" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP128" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ128" t="s" s="2">
         <v>84</v>
@@ -19111,22 +19111,22 @@
         <v>106</v>
       </c>
       <c r="AK129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AN129" t="s" s="2">
         <v>821</v>
       </c>
-      <c r="AL129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM129" t="s" s="2">
+      <c r="AO129" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP129" t="s" s="2">
         <v>822</v>
-      </c>
-      <c r="AN129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO129" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP129" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="AQ129" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -322,7 +322,7 @@
     <t>Resource.id</t>
   </si>
   <si>
-    <t>798: transform using ID_generation</t>
+    <t>798: transform using ID_generation()</t>
   </si>
   <si>
     <t>MedicationRequest.meta</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file PRESCRIPTION (#52) to us-core-medicationrequest</t>
+    <t>This StructureDefinition contains the maps for VistA file PRESCRIPTION (52) to us-core-medicationrequest</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -656,7 +656,7 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1707: source value from PRESCRIPTION - MAIL/WINDOW/PARK (#52-11)</t>
+    <t>1707: source value from PRESCRIPTION - MAIL/WINDOW/PARK (52-11)</t>
   </si>
   <si>
     <t>RxOut.RxOutpat.RxStatus</t>
@@ -755,7 +755,7 @@
 </t>
   </si>
   <si>
-    <t>1704: source value from PRESCRIPTION - CANCEL DATE (#52-26.1)</t>
+    <t>1704: source value from PRESCRIPTION - CANCEL DATE (52-26.1)</t>
   </si>
   <si>
     <t>RxOut.RxOutpat.CancelDate</t>
@@ -789,7 +789,7 @@
     <t>MedicationRequest.extension:medicationrequest-includeIndicationInSig.value[x]</t>
   </si>
   <si>
-    <t>1706: transform using VF_Boolean on PRESCRIPTION - INDICATION FOR USE FLAG (#51-129)</t>
+    <t>1706: transform using VF_Boolean on MEDICATION INSTRUCTION - INDICATION FOR USE FLAG (51-129)</t>
   </si>
   <si>
     <t>MedicationRequest.extension:medicationrequest-includeIndicationInSig.value[x].id</t>
@@ -940,7 +940,7 @@
     <t>http://va.gov/fhir/ValueSet/VSVFOutMedRequestStatus</t>
   </si>
   <si>
-    <t>799: terminologyMaps using VF_OutMedRequestStatus on PRESCRIPTION - STATUS (#52-100)</t>
+    <t>799: terminologyMaps using VF_OutMedRequestStatus on PRESCRIPTION - STATUS (52-100)</t>
   </si>
   <si>
     <t>Request.status</t>
@@ -1178,7 +1178,7 @@
     <t>The subject on a medication request is mandatory.  For the secondary use case where the actual subject is not provided, there still must be an anonymized subject specified.</t>
   </si>
   <si>
-    <t>806: reference from PRESCRIPTION - PATIENT (#52-2)</t>
+    <t>806: reference from PRESCRIPTION - PATIENT (52-2)</t>
   </si>
   <si>
     <t>Request.subject</t>
@@ -1285,7 +1285,7 @@
     <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
   </si>
   <si>
-    <t>808: reference from PRESCRIPTION - PROVIDER (#52-4)</t>
+    <t>808: reference from PRESCRIPTION - PROVIDER (52-4)</t>
   </si>
   <si>
     <t>Request.requester</t>
@@ -1440,7 +1440,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>1705: source value from PRESCRIPTION - INDICATION FOR USE (#52-128)</t>
+    <t>1705: source value from PRESCRIPTION - INDICATION FOR USE (52-128)</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
@@ -2203,7 +2203,7 @@
     <t>Period.end</t>
   </si>
   <si>
-    <t>815: source value from PRESCRIPTION - EXPIRATION DATE (#52-26)</t>
+    <t>815: source value from PRESCRIPTION - EXPIRATION DATE (52-26)</t>
   </si>
   <si>
     <t>./high</t>
@@ -2228,7 +2228,7 @@
     <t>If displaying "number of authorized fills", add 1 to this number.</t>
   </si>
   <si>
-    <t>816: source value from PRESCRIPTION - # OF REFILLS (#52-9)</t>
+    <t>816: source value from PRESCRIPTION - # OF REFILLS (52-9)</t>
   </si>
   <si>
     <t>RxOut.RxOutpat.MaxRefills</t>
@@ -2289,7 +2289,7 @@
     <t>Quantity.value</t>
   </si>
   <si>
-    <t>1669: source value from PRESCRIPTION - QTY (#52-7)</t>
+    <t>1669: source value from PRESCRIPTION - QTY (52-7)</t>
   </si>
   <si>
     <t>Pharmacy: quantity</t>
@@ -2407,7 +2407,7 @@
     <t>In some situations, this attribute may be used instead of quantity to identify the amount supplied by how long it is expected to last, rather than the physical quantity issued, e.g. 90 days supply of medication (based on an ordered dosage). When possible, it is always better to specify quantity, as this tends to be more precise. expectedSupplyDuration will always be an estimate that can be influenced by external factors.</t>
   </si>
   <si>
-    <t>1670: source value from PRESCRIPTION - DAYS SUPPLY (#52-8)</t>
+    <t>1670: source value from PRESCRIPTION - DAYS SUPPLY (52-8)</t>
   </si>
   <si>
     <t>Pharmacy: daysSupply</t>
@@ -2923,7 +2923,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="96.140625" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5171" uniqueCount="823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5171" uniqueCount="824">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -789,7 +789,7 @@
     <t>MedicationRequest.extension:medicationrequest-includeIndicationInSig.value[x]</t>
   </si>
   <si>
-    <t>1706: transform using VF_Boolean on MEDICATION INSTRUCTION - INDICATION FOR USE FLAG (51-129)</t>
+    <t>1706: transform using VF_Boolean on PRESCRIPTION - INDICATION FOR USE FLAG (52-129)</t>
   </si>
   <si>
     <t>MedicationRequest.extension:medicationrequest-includeIndicationInSig.value[x].id</t>
@@ -854,10 +854,14 @@
 </t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ConceptMap/CMVFBoolean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
   </si>
   <si>
     <t>MedicationRequest.extension:medicationrequest-includeIndicationInSig.value[x].value</t>
@@ -2923,7 +2927,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="96.140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="43.94140625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
@@ -7169,7 +7173,7 @@
         <v>83</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>145</v>
@@ -7227,7 +7231,7 @@
         <v>84</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>153</v>
+        <v>95</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>154</v>
@@ -7293,7 +7297,7 @@
         <v>93</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>84</v>
@@ -7667,7 +7671,7 @@
         <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>84</v>
+        <v>272</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -7699,10 +7703,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7728,10 +7732,10 @@
         <v>220</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -7782,7 +7786,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7823,10 +7827,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7852,16 +7856,16 @@
         <v>139</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7910,7 +7914,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7951,10 +7955,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7977,16 +7981,16 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -8036,7 +8040,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -8060,27 +8064,27 @@
         <v>84</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8106,13 +8110,13 @@
         <v>114</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -8138,11 +8142,11 @@
         <v>84</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>84</v>
@@ -8160,7 +8164,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>93</v>
@@ -8175,7 +8179,7 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>207</v>
@@ -8184,16 +8188,16 @@
         <v>84</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>84</v>
@@ -8201,10 +8205,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8227,16 +8231,16 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -8262,13 +8266,13 @@
         <v>84</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>84</v>
@@ -8286,7 +8290,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -8310,13 +8314,13 @@
         <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -8327,10 +8331,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8356,13 +8360,13 @@
         <v>114</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -8373,7 +8377,7 @@
         <v>84</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>84</v>
@@ -8388,13 +8392,13 @@
         <v>84</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>84</v>
@@ -8412,7 +8416,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>93</v>
@@ -8427,7 +8431,7 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>84</v>
@@ -8436,16 +8440,16 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>84</v>
@@ -8453,10 +8457,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8479,16 +8483,16 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8514,19 +8518,19 @@
         <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
@@ -8536,7 +8540,7 @@
         <v>143</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8563,13 +8567,13 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>84</v>
@@ -8577,13 +8581,13 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>84</v>
@@ -8605,16 +8609,16 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8640,13 +8644,13 @@
         <v>84</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8664,7 +8668,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8691,13 +8695,13 @@
         <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>84</v>
@@ -8705,10 +8709,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8734,10 +8738,10 @@
         <v>114</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8764,13 +8768,13 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -8788,7 +8792,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8812,16 +8816,16 @@
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>84</v>
@@ -8829,10 +8833,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8858,13 +8862,13 @@
         <v>220</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8914,7 +8918,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8944,7 +8948,7 @@
         <v>84</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -8955,10 +8959,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8981,13 +8985,13 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -9038,7 +9042,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -9068,7 +9072,7 @@
         <v>84</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -9079,10 +9083,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9105,16 +9109,16 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -9140,11 +9144,11 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
@@ -9162,7 +9166,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>93</v>
@@ -9186,27 +9190,27 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9229,16 +9233,16 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -9288,7 +9292,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>93</v>
@@ -9303,7 +9307,7 @@
         <v>106</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>84</v>
@@ -9312,27 +9316,27 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9355,16 +9359,16 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -9414,7 +9418,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -9429,7 +9433,7 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>84</v>
@@ -9438,27 +9442,27 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9481,13 +9485,13 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -9538,7 +9542,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -9562,16 +9566,16 @@
         <v>84</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>84</v>
@@ -9579,10 +9583,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9608,10 +9612,10 @@
         <v>237</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -9662,7 +9666,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9686,27 +9690,27 @@
         <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9729,13 +9733,13 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -9786,7 +9790,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9801,7 +9805,7 @@
         <v>106</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>84</v>
@@ -9810,16 +9814,16 @@
         <v>84</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>84</v>
@@ -9827,10 +9831,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9853,13 +9857,13 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9910,7 +9914,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9934,16 +9938,16 @@
         <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>84</v>
@@ -9951,10 +9955,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9977,16 +9981,16 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -10012,13 +10016,13 @@
         <v>84</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
@@ -10036,7 +10040,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -10060,13 +10064,13 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -10077,10 +10081,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10103,13 +10107,13 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -10160,7 +10164,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -10190,10 +10194,10 @@
         <v>84</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>84</v>
@@ -10201,10 +10205,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10227,16 +10231,16 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -10262,13 +10266,13 @@
         <v>84</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -10286,7 +10290,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10310,27 +10314,27 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10451,10 +10455,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10577,10 +10581,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10606,16 +10610,16 @@
         <v>171</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -10664,7 +10668,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10694,21 +10698,21 @@
         <v>84</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10734,16 +10738,16 @@
         <v>153</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10792,7 +10796,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10807,7 +10811,7 @@
         <v>106</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>84</v>
@@ -10822,21 +10826,21 @@
         <v>84</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR63" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10859,16 +10863,16 @@
         <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10918,7 +10922,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10942,16 +10946,16 @@
         <v>84</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>84</v>
@@ -10959,10 +10963,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10985,13 +10989,13 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -11042,7 +11046,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -11066,13 +11070,13 @@
         <v>84</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -11083,10 +11087,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11112,10 +11116,10 @@
         <v>108</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -11166,7 +11170,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -11196,7 +11200,7 @@
         <v>84</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -11207,10 +11211,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11233,13 +11237,13 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -11290,7 +11294,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11314,13 +11318,13 @@
         <v>84</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -11331,10 +11335,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11357,17 +11361,17 @@
         <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
@@ -11416,7 +11420,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11440,13 +11444,13 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AQ68" t="s" s="2">
         <v>84</v>
@@ -11457,10 +11461,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11483,16 +11487,16 @@
         <v>84</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11518,13 +11522,13 @@
         <v>84</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>84</v>
@@ -11542,7 +11546,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11572,7 +11576,7 @@
         <v>84</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -11583,10 +11587,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11609,13 +11613,13 @@
         <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11666,7 +11670,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11690,13 +11694,13 @@
         <v>84</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11707,10 +11711,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11733,13 +11737,13 @@
         <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11790,7 +11794,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11814,13 +11818,13 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
@@ -11831,10 +11835,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11857,16 +11861,16 @@
         <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11916,7 +11920,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11940,13 +11944,13 @@
         <v>84</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11957,10 +11961,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12081,10 +12085,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12207,14 +12211,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -12236,16 +12240,16 @@
         <v>139</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>84</v>
@@ -12294,7 +12298,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12335,10 +12339,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12361,17 +12365,17 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>84</v>
@@ -12420,7 +12424,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12450,21 +12454,21 @@
         <v>84</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR76" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12490,14 +12494,14 @@
         <v>153</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12546,7 +12550,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12576,21 +12580,21 @@
         <v>84</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12613,19 +12617,19 @@
         <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>84</v>
@@ -12650,13 +12654,13 @@
         <v>84</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>84</v>
@@ -12674,7 +12678,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12704,21 +12708,21 @@
         <v>84</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR78" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12744,10 +12748,10 @@
         <v>153</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -12798,7 +12802,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12828,21 +12832,21 @@
         <v>84</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12865,19 +12869,19 @@
         <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
@@ -12926,7 +12930,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -12956,7 +12960,7 @@
         <v>84</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>
@@ -12967,10 +12971,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12993,16 +12997,16 @@
         <v>94</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -13028,13 +13032,13 @@
         <v>84</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>84</v>
@@ -13052,7 +13056,7 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -13082,21 +13086,21 @@
         <v>84</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR81" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13119,19 +13123,19 @@
         <v>94</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>84</v>
@@ -13156,13 +13160,13 @@
         <v>84</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>84</v>
@@ -13180,7 +13184,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -13210,21 +13214,21 @@
         <v>84</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13247,17 +13251,17 @@
         <v>94</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>84</v>
@@ -13282,13 +13286,13 @@
         <v>84</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>84</v>
@@ -13306,7 +13310,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13336,21 +13340,21 @@
         <v>84</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13373,19 +13377,19 @@
         <v>94</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>84</v>
@@ -13410,13 +13414,13 @@
         <v>84</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>84</v>
@@ -13434,7 +13438,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13464,21 +13468,21 @@
         <v>84</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR84" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13501,13 +13505,13 @@
         <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -13558,7 +13562,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13594,15 +13598,15 @@
         <v>84</v>
       </c>
       <c r="AR85" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13723,10 +13727,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13849,10 +13853,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13875,17 +13879,17 @@
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>84</v>
@@ -13910,13 +13914,13 @@
         <v>84</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>84</v>
@@ -13934,7 +13938,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13970,15 +13974,15 @@
         <v>84</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14001,19 +14005,19 @@
         <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>84</v>
@@ -14062,7 +14066,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -14092,21 +14096,21 @@
         <v>84</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14129,19 +14133,19 @@
         <v>94</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>84</v>
@@ -14190,7 +14194,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -14220,21 +14224,21 @@
         <v>84</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14257,19 +14261,19 @@
         <v>94</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>84</v>
@@ -14318,7 +14322,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14348,21 +14352,21 @@
         <v>84</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14385,19 +14389,19 @@
         <v>94</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>84</v>
@@ -14446,7 +14450,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14476,7 +14480,7 @@
         <v>84</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>84</v>
@@ -14487,10 +14491,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14513,17 +14517,17 @@
         <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14572,7 +14576,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14602,7 +14606,7 @@
         <v>84</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>
@@ -14613,10 +14617,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14639,13 +14643,13 @@
         <v>84</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -14696,7 +14700,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14723,10 +14727,10 @@
         <v>84</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
@@ -14737,10 +14741,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14861,10 +14865,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14987,14 +14991,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -15016,16 +15020,16 @@
         <v>139</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>84</v>
@@ -15074,7 +15078,7 @@
         <v>84</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>82</v>
@@ -15115,10 +15119,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15141,16 +15145,16 @@
         <v>84</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -15200,7 +15204,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -15230,7 +15234,7 @@
         <v>84</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>84</v>
@@ -15241,10 +15245,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15365,10 +15369,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15491,14 +15495,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -15520,16 +15524,16 @@
         <v>139</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>84</v>
@@ -15578,7 +15582,7 @@
         <v>84</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15619,10 +15623,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15645,13 +15649,13 @@
         <v>84</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -15702,7 +15706,7 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -15732,7 +15736,7 @@
         <v>84</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AQ102" t="s" s="2">
         <v>84</v>
@@ -15743,10 +15747,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15769,13 +15773,13 @@
         <v>84</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -15826,7 +15830,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -15856,7 +15860,7 @@
         <v>84</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
@@ -15867,10 +15871,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15893,13 +15897,13 @@
         <v>84</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -15950,7 +15954,7 @@
         <v>84</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -15980,7 +15984,7 @@
         <v>84</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="AQ104" t="s" s="2">
         <v>84</v>
@@ -15991,10 +15995,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16017,19 +16021,19 @@
         <v>84</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>84</v>
@@ -16078,7 +16082,7 @@
         <v>84</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -16105,10 +16109,10 @@
         <v>84</v>
       </c>
       <c r="AO105" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="AQ105" t="s" s="2">
         <v>84</v>
@@ -16119,10 +16123,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16243,10 +16247,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16369,10 +16373,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16398,13 +16402,13 @@
         <v>237</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -16454,7 +16458,7 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -16463,7 +16467,7 @@
         <v>93</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>106</v>
@@ -16484,21 +16488,21 @@
         <v>84</v>
       </c>
       <c r="AP108" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AQ108" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR108" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16524,20 +16528,20 @@
         <v>237</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q109" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="R109" t="s" s="2">
         <v>84</v>
@@ -16582,7 +16586,7 @@
         <v>84</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>82</v>
@@ -16591,13 +16595,13 @@
         <v>93</v>
       </c>
       <c r="AI109" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AJ109" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="AL109" t="s" s="2">
         <v>84</v>
@@ -16612,21 +16616,21 @@
         <v>84</v>
       </c>
       <c r="AP109" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AQ109" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR109" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -16649,16 +16653,16 @@
         <v>84</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -16708,7 +16712,7 @@
         <v>84</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>82</v>
@@ -16723,10 +16727,10 @@
         <v>106</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>84</v>
@@ -16735,24 +16739,24 @@
         <v>84</v>
       </c>
       <c r="AO110" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="AP110" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AQ110" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR110" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16775,13 +16779,13 @@
         <v>84</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16832,7 +16836,7 @@
         <v>84</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>82</v>
@@ -16859,24 +16863,24 @@
         <v>84</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR111" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -16997,10 +17001,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17123,10 +17127,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17149,19 +17153,19 @@
         <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>84</v>
@@ -17210,7 +17214,7 @@
         <v>84</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>82</v>
@@ -17225,13 +17229,13 @@
         <v>106</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>84</v>
@@ -17240,21 +17244,21 @@
         <v>84</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AQ114" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR114" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17280,20 +17284,20 @@
         <v>114</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q115" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="R115" t="s" s="2">
         <v>84</v>
@@ -17314,13 +17318,13 @@
         <v>84</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>84</v>
@@ -17338,7 +17342,7 @@
         <v>84</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>82</v>
@@ -17368,21 +17372,21 @@
         <v>84</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AQ115" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR115" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17408,14 +17412,14 @@
         <v>153</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>84</v>
@@ -17464,7 +17468,7 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>82</v>
@@ -17494,21 +17498,21 @@
         <v>84</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AQ116" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR116" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17534,14 +17538,14 @@
         <v>108</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>84</v>
@@ -17590,7 +17594,7 @@
         <v>84</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>82</v>
@@ -17599,7 +17603,7 @@
         <v>93</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>106</v>
@@ -17620,21 +17624,21 @@
         <v>84</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="AQ117" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR117" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17660,16 +17664,16 @@
         <v>114</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>84</v>
@@ -17718,7 +17722,7 @@
         <v>84</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>82</v>
@@ -17748,21 +17752,21 @@
         <v>84</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AQ118" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR118" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17785,16 +17789,16 @@
         <v>84</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -17844,7 +17848,7 @@
         <v>84</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>82</v>
@@ -17859,22 +17863,22 @@
         <v>106</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="AP119" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="AQ119" t="s" s="2">
         <v>84</v>
@@ -17885,10 +17889,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17911,13 +17915,13 @@
         <v>84</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -17968,7 +17972,7 @@
         <v>84</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>82</v>
@@ -17998,10 +18002,10 @@
         <v>84</v>
       </c>
       <c r="AP120" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AQ120" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AR120" t="s" s="2">
         <v>84</v>
@@ -18009,10 +18013,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18035,13 +18039,13 @@
         <v>84</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -18092,7 +18096,7 @@
         <v>84</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>82</v>
@@ -18119,10 +18123,10 @@
         <v>84</v>
       </c>
       <c r="AO121" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AP121" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="AQ121" t="s" s="2">
         <v>84</v>
@@ -18133,10 +18137,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18257,10 +18261,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18383,14 +18387,14 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
@@ -18412,16 +18416,16 @@
         <v>139</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N124" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>84</v>
@@ -18470,7 +18474,7 @@
         <v>84</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>82</v>
@@ -18511,10 +18515,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18537,16 +18541,16 @@
         <v>84</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
@@ -18572,13 +18576,13 @@
         <v>84</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>84</v>
@@ -18596,7 +18600,7 @@
         <v>84</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>93</v>
@@ -18623,24 +18627,24 @@
         <v>84</v>
       </c>
       <c r="AO125" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AQ125" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR125" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18663,13 +18667,13 @@
         <v>84</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -18696,13 +18700,13 @@
         <v>84</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>84</v>
@@ -18720,7 +18724,7 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>82</v>
@@ -18747,24 +18751,24 @@
         <v>84</v>
       </c>
       <c r="AO126" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="AQ126" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR126" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18787,13 +18791,13 @@
         <v>84</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -18844,7 +18848,7 @@
         <v>84</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>82</v>
@@ -18868,13 +18872,13 @@
         <v>84</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="AO127" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>84</v>
@@ -18885,14 +18889,14 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -18911,16 +18915,16 @@
         <v>84</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
@@ -18970,7 +18974,7 @@
         <v>84</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>82</v>
@@ -19000,7 +19004,7 @@
         <v>84</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="AQ128" t="s" s="2">
         <v>84</v>
@@ -19011,10 +19015,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19037,16 +19041,16 @@
         <v>84</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
@@ -19096,7 +19100,7 @@
         <v>84</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
@@ -19120,13 +19124,13 @@
         <v>84</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="AQ129" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -914,7 +914,7 @@
     <t>This is a business identifier, not a resource identifier.</t>
   </si>
   <si>
-    <t>1664: source value from PRESCRIPTION - Rx (52-.01)</t>
+    <t>1664: source value from PRESCRIPTION - RX # (52-.01)</t>
   </si>
   <si>
     <t>RxOut.RxOutpat.RxNumber</t>
@@ -1265,7 +1265,7 @@
     <t>MedicationRequest.medication[x].coding.code</t>
   </si>
   <si>
-    <t>805: transform using null on PRESCRIPTION - DRUG &gt; DRUG - NDF &gt; VA GENERIC - CODING SYSTEM &gt; CODING SYSTEM - CODE (52-6 &gt; 50-20 &gt; 50.6-5 &gt; 50.65-.02)</t>
+    <t>805: transform using null on PRESCRIPTION - DRUG &gt; DRUG - NATIONAL DRUG FILE ENTRY &gt; VA GENERIC - CODING SYSTEM &gt; CODING SYSTEM - CODE (52-6 &gt; 50-20 &gt; 50.6-5 &gt; 50.65-.02)</t>
   </si>
   <si>
     <t>RxOut.RxOutpat.LocalDrugIEN,RxOut.RxOutpat.NationalDrugIEN,RxOut.RxOutpatFill.LocalDrugIEN,RxOut.RxOutpatFill.NationalDrugIEN</t>
@@ -1304,7 +1304,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>803: source value from PRESCRIPTION - DRUG &gt; DRUG - PSNDF &gt; VA PRODUCT - NAME (52-6 &gt; 50-22 &gt; 50.68-5)</t>
+    <t>803: source value from PRESCRIPTION - DRUG &gt; DRUG - DRUG - PSNDF VA PRODUCT NAME ENTRY &gt; VA PRODUCT - VA PRINT NAME (52-6 &gt; 50-22 &gt; 50.68-5)</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>
@@ -1992,7 +1992,7 @@
     <t>MedicationRequest.dosageInstruction.route.coding.code</t>
   </si>
   <si>
-    <t>1665: source value from PRESCRIPTION - ROUTE &gt; MEDICATION INSTRUCTIONS - ROUTE (52-113 &gt; 52.0113-6)</t>
+    <t>1665: source value from PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - ROUTE (52-113 &gt; 52.0113-6)</t>
   </si>
   <si>
     <t>RxOut.RxOutpatMedInstructions.MedRoute</t>
@@ -3192,7 +3192,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="152.84375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="175.39453125" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="249.89453125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1304,7 +1304,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>803: source value from PRESCRIPTION - DRUG &gt; DRUG - DRUG - PSNDF VA PRODUCT NAME ENTRY &gt; VA PRODUCT - VA PRINT NAME (52-6 &gt; 50-22 &gt; 50.68-5)</t>
+    <t>803: source value from PRESCRIPTION - DRUG &gt; DRUG - PSNDF VA PRODUCT NAME ENTRY &gt; VA PRODUCT - VA PRINT NAME (52-6 &gt; 50-22 &gt; 50.68-5)</t>
   </si>
   <si>
     <t>./originalText[mediaType/code="text/plain"]/data</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6613" uniqueCount="910">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6615" uniqueCount="925">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -605,7 +605,13 @@
     <t>Need to be unambiguous about the source of the definition of the symbol.</t>
   </si>
   <si>
+    <t>http://va.gov/terminology/vistaDefinedTerms/52-100</t>
+  </si>
+  <si>
     <t>Coding.system</t>
+  </si>
+  <si>
+    <t>1707-1: fixed value = http://va.gov/terminology/vistaDefinedTerms/52-100</t>
   </si>
   <si>
     <t>./codeSystem</t>
@@ -1253,6 +1259,12 @@
     <t>MedicationRequest.medication[x].coding.system</t>
   </si>
   <si>
+    <t>http://www.nlm.nih.gov/research/umls/rxnorm</t>
+  </si>
+  <si>
+    <t>805-1: fixed value = http://www.nlm.nih.gov/research/umls/rxnorm</t>
+  </si>
+  <si>
     <t>MedicationRequest.medication[x]:medicationCodeableConcept.coding.version</t>
   </si>
   <si>
@@ -1432,7 +1444,7 @@
     <t>MedicationRequest.requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner|http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient|http://hl7.org/fhir/us/core/StructureDefinition/us-core-organization|http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitionerrole|http://hl7.org/fhir/us/core/StructureDefinition/us-core-relatedperson|Device)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-practitioner)
 </t>
   </si>
   <si>
@@ -1986,6 +1998,12 @@
     <t>MedicationRequest.dosageInstruction.route.coding.system</t>
   </si>
   <si>
+    <t>http://va.gov/terminology/vistaDefinedTerms/53.1-3</t>
+  </si>
+  <si>
+    <t>1665-1: fixed value = http://va.gov/terminology/vistaDefinedTerms/53.1-3</t>
+  </si>
+  <si>
     <t>MedicationRequest.dosageInstruction.route.coding.version</t>
   </si>
   <si>
@@ -2062,25 +2080,55 @@
     <t>MedicationRequest.dosageInstruction.doseAndRate.extension</t>
   </si>
   <si>
+    <t>MedicationRequest.dosageInstruction.doseAndRate.extension:originalText</t>
+  </si>
+  <si>
+    <t>originalText</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {originalText}
+</t>
+  </si>
+  <si>
+    <t>Original Text that represents the data as seen/selected/uttered originally</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept (resource/element) as seen/selected/uttered by the user who entered the data and/or which represents the full intended meaning of the user. This can be provided either directly as text, or as a url that is a reference to a portion of the narrative of a resource ([DomainResource.text](http://hl7.org/fhir/R4/narrative.html) or [Composition.section.text](http://hl7.org/fhir/R4/composition-definitions.html#Composition.section.text)). When it a url, the value should end with a #{id} where the id identifies a specific portion of the referenced content (via an XHTML id attribute).</t>
+  </si>
+  <si>
+    <t>The data in the element does not always capture the correct meaning with all the nuances of the original text. In these cases, the text is used to capture the full meaning of the source. This is commonly used to provide "what did the user actually see/type". Note that this extension has the same definition as CodeableConcept.text and SHALL NOT be used on CodeableConcept with type = string in place of CodeableConcept.text but MAY be used with type url. If present on a CodeableConcept with type url as well as CodeableConcept.text, then the CodeableConcept.text SHALL match the referenced narrative. 
+It's also possible to link to the resource narrative using the [narrativeLink extension](StructureDefinition-narrativeLink.html) which does not claim that the data is derived from the text.</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.doseAndRate.extension:originalText.id</t>
+  </si>
+  <si>
     <t>MedicationRequest.dosageInstruction.doseAndRate.extension.id</t>
   </si>
   <si>
+    <t>MedicationRequest.dosageInstruction.doseAndRate.extension:originalText.extension</t>
+  </si>
+  <si>
     <t>MedicationRequest.dosageInstruction.doseAndRate.extension.extension</t>
   </si>
   <si>
+    <t>MedicationRequest.dosageInstruction.doseAndRate.extension:originalText.url</t>
+  </si>
+  <si>
     <t>MedicationRequest.dosageInstruction.doseAndRate.extension.url</t>
   </si>
   <si>
+    <t>http://hl7.org/fhir/StructureDefinition/originalText</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dosageInstruction.doseAndRate.extension:originalText.value[x]</t>
+  </si>
+  <si>
     <t>MedicationRequest.dosageInstruction.doseAndRate.extension.value[x]</t>
   </si>
   <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dosageInstruction.doseAndRate.extension.value[x]:valueString</t>
-  </si>
-  <si>
-    <t>valueString</t>
+    <t>string
+url</t>
   </si>
   <si>
     <t>841: source value from PRESCRIPTION - MEDICATION INSTRUCTIONS &gt; MEDICATION INSTRUCTIONS - DOSAGE ORDERED (52-113 &gt; 52.0113-.01) case not a number</t>
@@ -5231,7 +5279,7 @@
         <v>93</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>84</v>
@@ -5262,7 +5310,7 @@
         <v>84</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>84</v>
+        <v>189</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>84</v>
@@ -5301,7 +5349,7 @@
         <v>84</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>82</v>
@@ -5316,7 +5364,7 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>84</v>
+        <v>191</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>84</v>
@@ -5331,21 +5379,21 @@
         <v>84</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AQ17" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR17" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -5371,13 +5419,13 @@
         <v>153</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -5427,7 +5475,7 @@
         <v>84</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>82</v>
@@ -5457,21 +5505,21 @@
         <v>84</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AQ18" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR18" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -5497,14 +5545,14 @@
         <v>114</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>84</v>
@@ -5553,7 +5601,7 @@
         <v>84</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>82</v>
@@ -5568,10 +5616,10 @@
         <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>84</v>
@@ -5583,21 +5631,21 @@
         <v>84</v>
       </c>
       <c r="AP19" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AQ19" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR19" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -5623,14 +5671,14 @@
         <v>153</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>84</v>
@@ -5679,7 +5727,7 @@
         <v>84</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>82</v>
@@ -5709,21 +5757,21 @@
         <v>84</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AQ20" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR20" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5746,19 +5794,19 @@
         <v>94</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>84</v>
@@ -5807,7 +5855,7 @@
         <v>84</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>82</v>
@@ -5837,24 +5885,24 @@
         <v>84</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AQ21" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR21" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>138</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>84</v>
@@ -5876,13 +5924,13 @@
         <v>84</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>140</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -5974,7 +6022,7 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>152</v>
@@ -6098,7 +6146,7 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>159</v>
@@ -6222,7 +6270,7 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>163</v>
@@ -6265,7 +6313,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>84</v>
@@ -6348,7 +6396,7 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>170</v>
@@ -6374,7 +6422,7 @@
         <v>84</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L26" t="s" s="2">
         <v>172</v>
@@ -6446,10 +6494,10 @@
         <v>106</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>84</v>
@@ -6472,13 +6520,13 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>138</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>84</v>
@@ -6500,13 +6548,13 @@
         <v>84</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>140</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -6598,7 +6646,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>152</v>
@@ -6722,7 +6770,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>159</v>
@@ -6846,7 +6894,7 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>163</v>
@@ -6889,7 +6937,7 @@
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>84</v>
@@ -6972,7 +7020,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>170</v>
@@ -6998,7 +7046,7 @@
         <v>84</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>172</v>
@@ -7070,10 +7118,10 @@
         <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>84</v>
@@ -7096,7 +7144,7 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>176</v>
@@ -7125,10 +7173,10 @@
         <v>153</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -7220,7 +7268,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>178</v>
@@ -7342,13 +7390,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>178</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>84</v>
@@ -7370,16 +7418,16 @@
         <v>84</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -7470,10 +7518,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7594,10 +7642,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7718,10 +7766,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7761,7 +7809,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>84</v>
@@ -7844,10 +7892,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7870,13 +7918,13 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>172</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -7888,7 +7936,7 @@
         <v>84</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>84</v>
@@ -7936,7 +7984,7 @@
         <v>93</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>106</v>
@@ -7968,10 +8016,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7994,13 +8042,13 @@
         <v>84</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -8051,7 +8099,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -8092,10 +8140,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -8121,16 +8169,16 @@
         <v>139</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -8179,7 +8227,7 @@
         <v>84</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -8220,10 +8268,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -8246,16 +8294,16 @@
         <v>84</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -8305,7 +8353,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -8320,36 +8368,36 @@
         <v>106</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8375,13 +8423,13 @@
         <v>114</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -8407,11 +8455,11 @@
         <v>84</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>84</v>
@@ -8429,7 +8477,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>93</v>
@@ -8444,25 +8492,25 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>84</v>
@@ -8470,10 +8518,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8496,16 +8544,16 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -8531,13 +8579,13 @@
         <v>84</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>84</v>
@@ -8555,7 +8603,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -8579,13 +8627,13 @@
         <v>84</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AQ43" t="s" s="2">
         <v>84</v>
@@ -8596,10 +8644,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8625,13 +8673,13 @@
         <v>114</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -8642,7 +8690,7 @@
         <v>84</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>84</v>
@@ -8657,13 +8705,13 @@
         <v>84</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>84</v>
@@ -8681,7 +8729,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>93</v>
@@ -8696,7 +8744,7 @@
         <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>84</v>
@@ -8705,16 +8753,16 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>84</v>
@@ -8722,10 +8770,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8748,16 +8796,16 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8768,7 +8816,7 @@
         <v>84</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>84</v>
@@ -8783,19 +8831,19 @@
         <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AC45" s="2"/>
       <c r="AD45" t="s" s="2">
@@ -8805,7 +8853,7 @@
         <v>143</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8820,7 +8868,7 @@
         <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>84</v>
@@ -8832,13 +8880,13 @@
         <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>84</v>
@@ -8846,13 +8894,13 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D46" t="s" s="2">
         <v>84</v>
@@ -8874,16 +8922,16 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -8909,13 +8957,13 @@
         <v>84</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8933,7 +8981,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8960,13 +9008,13 @@
         <v>84</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>84</v>
@@ -8974,10 +9022,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -9003,10 +9051,10 @@
         <v>114</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -9033,13 +9081,13 @@
         <v>84</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>84</v>
@@ -9057,7 +9105,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -9081,16 +9129,16 @@
         <v>84</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>84</v>
@@ -9098,10 +9146,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -9124,16 +9172,16 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -9183,7 +9231,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -9213,7 +9261,7 @@
         <v>84</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
@@ -9224,10 +9272,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9250,13 +9298,13 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -9307,7 +9355,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -9337,7 +9385,7 @@
         <v>84</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -9348,10 +9396,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9374,16 +9422,16 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -9409,17 +9457,17 @@
         <v>84</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AC50" s="2"/>
       <c r="AD50" t="s" s="2">
@@ -9429,7 +9477,7 @@
         <v>143</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>93</v>
@@ -9453,30 +9501,30 @@
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>84</v>
@@ -9498,16 +9546,16 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -9533,11 +9581,11 @@
         <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -9555,7 +9603,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>93</v>
@@ -9579,27 +9627,27 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9720,10 +9768,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9846,10 +9894,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9875,16 +9923,16 @@
         <v>171</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>84</v>
@@ -9933,7 +9981,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
@@ -9963,21 +10011,21 @@
         <v>84</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -10098,10 +10146,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -10224,10 +10272,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10241,7 +10289,7 @@
         <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>84</v>
@@ -10272,7 +10320,7 @@
         <v>84</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>84</v>
+        <v>396</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>84</v>
@@ -10311,7 +10359,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -10326,7 +10374,7 @@
         <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>84</v>
+        <v>397</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>84</v>
@@ -10341,21 +10389,21 @@
         <v>84</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR57" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10381,13 +10429,13 @@
         <v>153</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -10437,7 +10485,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -10467,21 +10515,21 @@
         <v>84</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10507,14 +10555,14 @@
         <v>114</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -10563,7 +10611,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -10578,10 +10626,10 @@
         <v>106</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>84</v>
@@ -10593,21 +10641,21 @@
         <v>84</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR59" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10633,14 +10681,14 @@
         <v>153</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -10689,7 +10737,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -10719,21 +10767,21 @@
         <v>84</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR60" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10756,19 +10804,19 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>84</v>
@@ -10817,7 +10865,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10847,21 +10895,21 @@
         <v>84</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR61" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10887,16 +10935,16 @@
         <v>153</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -10945,7 +10993,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10960,10 +11008,10 @@
         <v>106</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>84</v>
@@ -10975,21 +11023,21 @@
         <v>84</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR62" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -11012,16 +11060,16 @@
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -11071,7 +11119,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>93</v>
@@ -11086,36 +11134,36 @@
         <v>106</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="AR63" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -11138,16 +11186,16 @@
         <v>84</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -11197,7 +11245,7 @@
         <v>84</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -11221,27 +11269,27 @@
         <v>84</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AR64" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11264,13 +11312,13 @@
         <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -11321,7 +11369,7 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
@@ -11345,16 +11393,16 @@
         <v>84</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>84</v>
@@ -11362,10 +11410,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11388,13 +11436,13 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -11445,7 +11493,7 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
@@ -11460,36 +11508,36 @@
         <v>106</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="AR66" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11512,13 +11560,13 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -11569,7 +11617,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -11584,25 +11632,25 @@
         <v>106</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>84</v>
@@ -11610,10 +11658,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11636,13 +11684,13 @@
         <v>84</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -11693,7 +11741,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>82</v>
@@ -11717,16 +11765,16 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>84</v>
@@ -11734,10 +11782,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11760,16 +11808,16 @@
         <v>94</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -11795,31 +11843,31 @@
         <v>84</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11843,13 +11891,13 @@
         <v>84</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
@@ -11860,10 +11908,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11886,13 +11934,13 @@
         <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -11943,7 +11991,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11973,10 +12021,10 @@
         <v>84</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>84</v>
@@ -11984,10 +12032,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -12010,16 +12058,16 @@
         <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -12045,31 +12093,31 @@
         <v>84</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -12093,27 +12141,27 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12234,10 +12282,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12360,10 +12408,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12389,16 +12437,16 @@
         <v>171</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>84</v>
@@ -12447,7 +12495,7 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>82</v>
@@ -12477,21 +12525,21 @@
         <v>84</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AQ74" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR74" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12517,16 +12565,16 @@
         <v>153</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>84</v>
@@ -12575,7 +12623,7 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
@@ -12590,10 +12638,10 @@
         <v>106</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>84</v>
@@ -12605,21 +12653,21 @@
         <v>84</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12642,16 +12690,16 @@
         <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -12701,7 +12749,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12725,16 +12773,16 @@
         <v>84</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>84</v>
@@ -12742,10 +12790,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12768,13 +12816,13 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -12825,7 +12873,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>82</v>
@@ -12849,13 +12897,13 @@
         <v>84</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="AQ77" t="s" s="2">
         <v>84</v>
@@ -12866,10 +12914,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12895,10 +12943,10 @@
         <v>108</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -12949,7 +12997,7 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
@@ -12979,7 +13027,7 @@
         <v>84</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>
@@ -12990,10 +13038,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -13016,13 +13064,13 @@
         <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -13073,7 +13121,7 @@
         <v>84</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -13097,13 +13145,13 @@
         <v>84</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
@@ -13114,10 +13162,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -13140,17 +13188,17 @@
         <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
@@ -13199,7 +13247,7 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
@@ -13223,13 +13271,13 @@
         <v>84</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>
@@ -13240,10 +13288,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13266,16 +13314,16 @@
         <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -13301,31 +13349,31 @@
         <v>84</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Y81" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF81" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
@@ -13355,7 +13403,7 @@
         <v>84</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AQ81" t="s" s="2">
         <v>84</v>
@@ -13366,10 +13414,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13392,13 +13440,13 @@
         <v>84</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -13449,7 +13497,7 @@
         <v>84</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -13473,13 +13521,13 @@
         <v>84</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
@@ -13490,10 +13538,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13516,13 +13564,13 @@
         <v>84</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -13573,7 +13621,7 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>82</v>
@@ -13597,13 +13645,13 @@
         <v>84</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
@@ -13614,10 +13662,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13640,16 +13688,16 @@
         <v>84</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -13699,7 +13747,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13723,13 +13771,13 @@
         <v>84</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -13740,10 +13788,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13864,10 +13912,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13990,14 +14038,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -14019,16 +14067,16 @@
         <v>139</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>84</v>
@@ -14077,7 +14125,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -14118,10 +14166,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -14144,17 +14192,17 @@
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>84</v>
@@ -14203,7 +14251,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -14233,21 +14281,21 @@
         <v>84</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14273,14 +14321,14 @@
         <v>153</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>84</v>
@@ -14329,7 +14377,7 @@
         <v>84</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -14344,7 +14392,7 @@
         <v>106</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>84</v>
@@ -14359,21 +14407,21 @@
         <v>84</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14396,19 +14444,19 @@
         <v>94</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>84</v>
@@ -14433,13 +14481,13 @@
         <v>84</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>84</v>
@@ -14457,7 +14505,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -14487,21 +14535,21 @@
         <v>84</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14527,10 +14575,10 @@
         <v>153</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -14581,7 +14629,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -14596,10 +14644,10 @@
         <v>106</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>84</v>
@@ -14611,21 +14659,21 @@
         <v>84</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR91" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14648,19 +14696,19 @@
         <v>94</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>84</v>
@@ -14709,7 +14757,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14739,7 +14787,7 @@
         <v>84</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>84</v>
@@ -14750,10 +14798,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14776,16 +14824,16 @@
         <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -14811,13 +14859,13 @@
         <v>84</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>84</v>
@@ -14835,7 +14883,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14865,21 +14913,21 @@
         <v>84</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14902,19 +14950,19 @@
         <v>94</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>84</v>
@@ -14939,13 +14987,13 @@
         <v>84</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>84</v>
@@ -14963,7 +15011,7 @@
         <v>84</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>82</v>
@@ -14993,21 +15041,21 @@
         <v>84</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="AQ94" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR94" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -15030,17 +15078,17 @@
         <v>94</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>84</v>
@@ -15065,13 +15113,13 @@
         <v>84</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>84</v>
@@ -15089,7 +15137,7 @@
         <v>84</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>82</v>
@@ -15119,21 +15167,21 @@
         <v>84</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="AQ95" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR95" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15254,10 +15302,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15380,10 +15428,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15409,16 +15457,16 @@
         <v>171</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>84</v>
@@ -15467,7 +15515,7 @@
         <v>84</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>82</v>
@@ -15497,21 +15545,21 @@
         <v>84</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AQ98" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR98" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15632,10 +15680,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15758,10 +15806,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15775,7 +15823,7 @@
         <v>93</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>84</v>
@@ -15806,7 +15854,7 @@
         <v>84</v>
       </c>
       <c r="S101" t="s" s="2">
-        <v>84</v>
+        <v>636</v>
       </c>
       <c r="T101" t="s" s="2">
         <v>84</v>
@@ -15845,7 +15893,7 @@
         <v>84</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>82</v>
@@ -15860,7 +15908,7 @@
         <v>106</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>84</v>
+        <v>637</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>84</v>
@@ -15875,21 +15923,21 @@
         <v>84</v>
       </c>
       <c r="AP101" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AQ101" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR101" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15915,13 +15963,13 @@
         <v>153</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -15971,7 +16019,7 @@
         <v>84</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>82</v>
@@ -16001,21 +16049,21 @@
         <v>84</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AQ102" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR102" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -16041,14 +16089,14 @@
         <v>114</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>84</v>
@@ -16097,7 +16145,7 @@
         <v>84</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>82</v>
@@ -16112,10 +16160,10 @@
         <v>106</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>84</v>
@@ -16127,21 +16175,21 @@
         <v>84</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AQ103" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR103" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -16167,14 +16215,14 @@
         <v>153</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>84</v>
@@ -16223,7 +16271,7 @@
         <v>84</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>82</v>
@@ -16253,21 +16301,21 @@
         <v>84</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AQ104" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR104" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16290,19 +16338,19 @@
         <v>94</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>84</v>
@@ -16351,7 +16399,7 @@
         <v>84</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>82</v>
@@ -16381,21 +16429,21 @@
         <v>84</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AQ105" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR105" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16421,16 +16469,16 @@
         <v>153</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>84</v>
@@ -16479,7 +16527,7 @@
         <v>84</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>82</v>
@@ -16509,21 +16557,21 @@
         <v>84</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="AQ106" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR106" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16546,19 +16594,19 @@
         <v>94</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>84</v>
@@ -16583,13 +16631,13 @@
         <v>84</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>84</v>
@@ -16607,7 +16655,7 @@
         <v>84</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>646</v>
+        <v>652</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>82</v>
@@ -16637,21 +16685,21 @@
         <v>84</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="AQ107" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR107" t="s" s="2">
-        <v>648</v>
+        <v>654</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16674,13 +16722,13 @@
         <v>94</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -16731,7 +16779,7 @@
         <v>84</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>82</v>
@@ -16767,15 +16815,15 @@
         <v>84</v>
       </c>
       <c r="AR108" t="s" s="2">
-        <v>654</v>
+        <v>660</v>
       </c>
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16896,10 +16944,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -17022,12 +17070,14 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="C111" s="2"/>
+        <v>662</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>664</v>
+      </c>
       <c r="D111" t="s" s="2">
         <v>84</v>
       </c>
@@ -17048,15 +17098,17 @@
         <v>84</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>153</v>
+        <v>665</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>154</v>
+        <v>666</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N111" s="2"/>
+        <v>667</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>668</v>
+      </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>84</v>
@@ -17105,19 +17157,19 @@
         <v>84</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>84</v>
@@ -17135,7 +17187,7 @@
         <v>84</v>
       </c>
       <c r="AP111" t="s" s="2">
-        <v>157</v>
+        <v>84</v>
       </c>
       <c r="AQ111" t="s" s="2">
         <v>84</v>
@@ -17146,10 +17198,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>658</v>
+        <v>669</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>658</v>
+        <v>670</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -17160,7 +17212,7 @@
         <v>82</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>84</v>
@@ -17172,13 +17224,13 @@
         <v>84</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -17217,31 +17269,31 @@
         <v>84</v>
       </c>
       <c r="AB112" t="s" s="2">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="AC112" t="s" s="2">
-        <v>160</v>
+        <v>84</v>
       </c>
       <c r="AD112" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE112" t="s" s="2">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AI112" t="s" s="2">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="AK112" t="s" s="2">
         <v>84</v>
@@ -17259,7 +17311,7 @@
         <v>84</v>
       </c>
       <c r="AP112" t="s" s="2">
-        <v>84</v>
+        <v>157</v>
       </c>
       <c r="AQ112" t="s" s="2">
         <v>84</v>
@@ -17270,10 +17322,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>659</v>
+        <v>671</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>659</v>
+        <v>672</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17281,10 +17333,10 @@
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>84</v>
@@ -17296,17 +17348,15 @@
         <v>84</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>166</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>84</v>
@@ -17343,31 +17393,31 @@
         <v>84</v>
       </c>
       <c r="AB113" t="s" s="2">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="AC113" t="s" s="2">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="AD113" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE113" t="s" s="2">
-        <v>84</v>
+        <v>143</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>84</v>
+        <v>145</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>84</v>
@@ -17385,7 +17435,7 @@
         <v>84</v>
       </c>
       <c r="AP113" t="s" s="2">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="AQ113" t="s" s="2">
         <v>84</v>
@@ -17396,10 +17446,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>660</v>
+        <v>673</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>660</v>
+        <v>674</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17407,7 +17457,7 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G114" t="s" s="2">
         <v>93</v>
@@ -17422,22 +17472,24 @@
         <v>84</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>153</v>
+        <v>108</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="N114" s="2"/>
+        <v>165</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>84</v>
+        <v>675</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>84</v>
@@ -17467,20 +17519,22 @@
         <v>84</v>
       </c>
       <c r="AB114" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AC114" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD114" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE114" t="s" s="2">
-        <v>661</v>
+        <v>84</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="AH114" t="s" s="2">
         <v>93</v>
@@ -17489,7 +17543,7 @@
         <v>84</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK114" t="s" s="2">
         <v>84</v>
@@ -17518,20 +17572,18 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>662</v>
+        <v>676</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="C115" t="s" s="2">
-        <v>663</v>
-      </c>
+        <v>677</v>
+      </c>
+      <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
         <v>84</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="G115" t="s" s="2">
         <v>93</v>
@@ -17546,13 +17598,13 @@
         <v>84</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>153</v>
+        <v>678</v>
       </c>
       <c r="L115" t="s" s="2">
         <v>172</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>173</v>
+        <v>273</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -17612,16 +17664,16 @@
         <v>93</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>84</v>
+        <v>275</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>664</v>
+        <v>679</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>665</v>
+        <v>680</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>84</v>
@@ -17644,10 +17696,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>666</v>
+        <v>681</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>666</v>
+        <v>681</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17670,17 +17722,17 @@
         <v>94</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>667</v>
+        <v>682</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>668</v>
+        <v>683</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>669</v>
+        <v>684</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>84</v>
@@ -17705,13 +17757,13 @@
         <v>84</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>670</v>
+        <v>685</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>671</v>
+        <v>686</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>84</v>
@@ -17729,7 +17781,7 @@
         <v>84</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>672</v>
+        <v>687</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>82</v>
@@ -17765,15 +17817,15 @@
         <v>84</v>
       </c>
       <c r="AR116" t="s" s="2">
-        <v>673</v>
+        <v>688</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>674</v>
+        <v>689</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>674</v>
+        <v>689</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17796,19 +17848,19 @@
         <v>94</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>675</v>
+        <v>690</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>676</v>
+        <v>691</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>677</v>
+        <v>692</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>678</v>
+        <v>693</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>679</v>
+        <v>694</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>84</v>
@@ -17845,7 +17897,7 @@
         <v>84</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AC117" s="2"/>
       <c r="AD117" t="s" s="2">
@@ -17855,7 +17907,7 @@
         <v>143</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>680</v>
+        <v>695</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>82</v>
@@ -17885,24 +17937,24 @@
         <v>84</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="AQ117" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR117" t="s" s="2">
-        <v>681</v>
+        <v>696</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>682</v>
+        <v>697</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>674</v>
+        <v>689</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>683</v>
+        <v>698</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>84</v>
@@ -17924,19 +17976,19 @@
         <v>84</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>684</v>
+        <v>699</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>685</v>
+        <v>700</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>686</v>
+        <v>701</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>687</v>
+        <v>702</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>679</v>
+        <v>694</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>84</v>
@@ -17985,7 +18037,7 @@
         <v>84</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>680</v>
+        <v>695</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>82</v>
@@ -17997,7 +18049,7 @@
         <v>150</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>688</v>
+        <v>703</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>84</v>
@@ -18015,21 +18067,21 @@
         <v>84</v>
       </c>
       <c r="AP118" t="s" s="2">
-        <v>689</v>
+        <v>704</v>
       </c>
       <c r="AQ118" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR118" t="s" s="2">
-        <v>690</v>
+        <v>705</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>691</v>
+        <v>706</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>692</v>
+        <v>707</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -18150,10 +18202,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>693</v>
+        <v>708</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>694</v>
+        <v>709</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -18276,10 +18328,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>695</v>
+        <v>710</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>696</v>
+        <v>711</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18302,19 +18354,19 @@
         <v>94</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>697</v>
+        <v>712</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>698</v>
+        <v>713</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>699</v>
+        <v>714</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="O121" t="s" s="2">
-        <v>701</v>
+        <v>716</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>84</v>
@@ -18363,7 +18415,7 @@
         <v>84</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>702</v>
+        <v>717</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>82</v>
@@ -18378,10 +18430,10 @@
         <v>106</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>703</v>
+        <v>718</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>665</v>
+        <v>680</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>84</v>
@@ -18393,21 +18445,21 @@
         <v>84</v>
       </c>
       <c r="AP121" t="s" s="2">
-        <v>704</v>
+        <v>719</v>
       </c>
       <c r="AQ121" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR121" t="s" s="2">
-        <v>705</v>
+        <v>720</v>
       </c>
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>706</v>
+        <v>721</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>707</v>
+        <v>722</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18433,20 +18485,20 @@
         <v>114</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>708</v>
+        <v>723</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>710</v>
+        <v>725</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q122" t="s" s="2">
-        <v>711</v>
+        <v>726</v>
       </c>
       <c r="R122" t="s" s="2">
         <v>84</v>
@@ -18467,13 +18519,13 @@
         <v>84</v>
       </c>
       <c r="X122" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>84</v>
@@ -18491,7 +18543,7 @@
         <v>84</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>714</v>
+        <v>729</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>82</v>
@@ -18521,21 +18573,21 @@
         <v>84</v>
       </c>
       <c r="AP122" t="s" s="2">
-        <v>715</v>
+        <v>730</v>
       </c>
       <c r="AQ122" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR122" t="s" s="2">
-        <v>716</v>
+        <v>731</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>717</v>
+        <v>732</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>718</v>
+        <v>733</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18561,14 +18613,14 @@
         <v>153</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>719</v>
+        <v>734</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>720</v>
+        <v>735</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>721</v>
+        <v>736</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>84</v>
@@ -18617,7 +18669,7 @@
         <v>84</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>722</v>
+        <v>737</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>82</v>
@@ -18632,10 +18684,10 @@
         <v>106</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>723</v>
+        <v>738</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>724</v>
+        <v>739</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>84</v>
@@ -18647,21 +18699,21 @@
         <v>84</v>
       </c>
       <c r="AP123" t="s" s="2">
-        <v>725</v>
+        <v>740</v>
       </c>
       <c r="AQ123" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR123" t="s" s="2">
-        <v>726</v>
+        <v>741</v>
       </c>
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>727</v>
+        <v>742</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>728</v>
+        <v>743</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18687,14 +18739,14 @@
         <v>108</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>729</v>
+        <v>744</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>730</v>
+        <v>745</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>731</v>
+        <v>746</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>84</v>
@@ -18743,7 +18795,7 @@
         <v>84</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>732</v>
+        <v>747</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>82</v>
@@ -18752,7 +18804,7 @@
         <v>93</v>
       </c>
       <c r="AI124" t="s" s="2">
-        <v>733</v>
+        <v>748</v>
       </c>
       <c r="AJ124" t="s" s="2">
         <v>106</v>
@@ -18773,21 +18825,21 @@
         <v>84</v>
       </c>
       <c r="AP124" t="s" s="2">
-        <v>734</v>
+        <v>749</v>
       </c>
       <c r="AQ124" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR124" t="s" s="2">
-        <v>726</v>
+        <v>741</v>
       </c>
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>735</v>
+        <v>750</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18813,16 +18865,16 @@
         <v>114</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>737</v>
+        <v>752</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>740</v>
+        <v>755</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>84</v>
@@ -18871,7 +18923,7 @@
         <v>84</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>741</v>
+        <v>756</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>82</v>
@@ -18901,21 +18953,21 @@
         <v>84</v>
       </c>
       <c r="AP125" t="s" s="2">
-        <v>742</v>
+        <v>757</v>
       </c>
       <c r="AQ125" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR125" t="s" s="2">
-        <v>726</v>
+        <v>741</v>
       </c>
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>743</v>
+        <v>758</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>743</v>
+        <v>758</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18938,19 +18990,19 @@
         <v>94</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>744</v>
+        <v>759</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>745</v>
+        <v>760</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>746</v>
+        <v>761</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>747</v>
+        <v>762</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>748</v>
+        <v>763</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>84</v>
@@ -18999,7 +19051,7 @@
         <v>84</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>749</v>
+        <v>764</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>82</v>
@@ -19029,21 +19081,21 @@
         <v>84</v>
       </c>
       <c r="AP126" t="s" s="2">
-        <v>750</v>
+        <v>765</v>
       </c>
       <c r="AQ126" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR126" t="s" s="2">
-        <v>751</v>
+        <v>766</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>752</v>
+        <v>767</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>752</v>
+        <v>767</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -19066,19 +19118,19 @@
         <v>94</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>753</v>
+        <v>768</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>754</v>
+        <v>769</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>755</v>
+        <v>770</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>756</v>
+        <v>771</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>757</v>
+        <v>772</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>84</v>
@@ -19127,7 +19179,7 @@
         <v>84</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>758</v>
+        <v>773</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>82</v>
@@ -19157,21 +19209,21 @@
         <v>84</v>
       </c>
       <c r="AP127" t="s" s="2">
-        <v>759</v>
+        <v>774</v>
       </c>
       <c r="AQ127" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR127" t="s" s="2">
-        <v>760</v>
+        <v>775</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>761</v>
+        <v>776</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>761</v>
+        <v>776</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -19194,19 +19246,19 @@
         <v>94</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>684</v>
+        <v>699</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>762</v>
+        <v>777</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>763</v>
+        <v>778</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>764</v>
+        <v>779</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>765</v>
+        <v>780</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>84</v>
@@ -19255,7 +19307,7 @@
         <v>84</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>766</v>
+        <v>781</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>82</v>
@@ -19285,7 +19337,7 @@
         <v>84</v>
       </c>
       <c r="AP128" t="s" s="2">
-        <v>767</v>
+        <v>782</v>
       </c>
       <c r="AQ128" t="s" s="2">
         <v>84</v>
@@ -19296,10 +19348,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19322,17 +19374,17 @@
         <v>94</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>684</v>
+        <v>699</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>769</v>
+        <v>784</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>770</v>
+        <v>785</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>771</v>
+        <v>786</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>84</v>
@@ -19381,7 +19433,7 @@
         <v>84</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>772</v>
+        <v>787</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>82</v>
@@ -19411,7 +19463,7 @@
         <v>84</v>
       </c>
       <c r="AP129" t="s" s="2">
-        <v>767</v>
+        <v>782</v>
       </c>
       <c r="AQ129" t="s" s="2">
         <v>84</v>
@@ -19422,10 +19474,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>773</v>
+        <v>788</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>773</v>
+        <v>788</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19448,13 +19500,13 @@
         <v>84</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>774</v>
+        <v>789</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>775</v>
+        <v>790</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>776</v>
+        <v>791</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -19505,7 +19557,7 @@
         <v>84</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>773</v>
+        <v>788</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>82</v>
@@ -19532,10 +19584,10 @@
         <v>84</v>
       </c>
       <c r="AO130" t="s" s="2">
-        <v>777</v>
+        <v>792</v>
       </c>
       <c r="AP130" t="s" s="2">
-        <v>778</v>
+        <v>793</v>
       </c>
       <c r="AQ130" t="s" s="2">
         <v>84</v>
@@ -19546,10 +19598,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>779</v>
+        <v>794</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>779</v>
+        <v>794</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19670,10 +19722,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>780</v>
+        <v>795</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>780</v>
+        <v>795</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19796,14 +19848,14 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>781</v>
+        <v>796</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -19825,16 +19877,16 @@
         <v>139</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="N133" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>84</v>
@@ -19883,7 +19935,7 @@
         <v>84</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>82</v>
@@ -19924,10 +19976,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>782</v>
+        <v>797</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>782</v>
+        <v>797</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19950,16 +20002,16 @@
         <v>84</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>774</v>
+        <v>789</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>783</v>
+        <v>798</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>784</v>
+        <v>799</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>785</v>
+        <v>800</v>
       </c>
       <c r="O134" s="2"/>
       <c r="P134" t="s" s="2">
@@ -20009,7 +20061,7 @@
         <v>84</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>782</v>
+        <v>797</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>82</v>
@@ -20039,7 +20091,7 @@
         <v>84</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>786</v>
+        <v>801</v>
       </c>
       <c r="AQ134" t="s" s="2">
         <v>84</v>
@@ -20050,10 +20102,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>787</v>
+        <v>802</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>787</v>
+        <v>802</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -20174,10 +20226,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>788</v>
+        <v>803</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>788</v>
+        <v>803</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -20300,14 +20352,14 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>789</v>
+        <v>804</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
@@ -20329,16 +20381,16 @@
         <v>139</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="N137" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>84</v>
@@ -20387,7 +20439,7 @@
         <v>84</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>82</v>
@@ -20428,10 +20480,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>790</v>
+        <v>805</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>790</v>
+        <v>805</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -20454,13 +20506,13 @@
         <v>84</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>684</v>
+        <v>699</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>791</v>
+        <v>806</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>792</v>
+        <v>807</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -20511,7 +20563,7 @@
         <v>84</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>790</v>
+        <v>805</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>82</v>
@@ -20541,7 +20593,7 @@
         <v>84</v>
       </c>
       <c r="AP138" t="s" s="2">
-        <v>793</v>
+        <v>808</v>
       </c>
       <c r="AQ138" t="s" s="2">
         <v>84</v>
@@ -20552,10 +20604,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>794</v>
+        <v>809</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>794</v>
+        <v>809</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20578,13 +20630,13 @@
         <v>84</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>795</v>
+        <v>810</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>796</v>
+        <v>811</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>797</v>
+        <v>812</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -20635,7 +20687,7 @@
         <v>84</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>794</v>
+        <v>809</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>82</v>
@@ -20665,7 +20717,7 @@
         <v>84</v>
       </c>
       <c r="AP139" t="s" s="2">
-        <v>798</v>
+        <v>813</v>
       </c>
       <c r="AQ139" t="s" s="2">
         <v>84</v>
@@ -20676,10 +20728,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>799</v>
+        <v>814</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>799</v>
+        <v>814</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20702,13 +20754,13 @@
         <v>84</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>795</v>
+        <v>810</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>800</v>
+        <v>815</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>801</v>
+        <v>816</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -20759,7 +20811,7 @@
         <v>84</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>799</v>
+        <v>814</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>82</v>
@@ -20789,7 +20841,7 @@
         <v>84</v>
       </c>
       <c r="AP140" t="s" s="2">
-        <v>798</v>
+        <v>813</v>
       </c>
       <c r="AQ140" t="s" s="2">
         <v>84</v>
@@ -20800,10 +20852,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>802</v>
+        <v>817</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>802</v>
+        <v>817</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20826,19 +20878,19 @@
         <v>84</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>803</v>
+        <v>818</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>804</v>
+        <v>819</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>805</v>
+        <v>820</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>806</v>
+        <v>821</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>807</v>
+        <v>822</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>84</v>
@@ -20887,7 +20939,7 @@
         <v>84</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>802</v>
+        <v>817</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>82</v>
@@ -20914,10 +20966,10 @@
         <v>84</v>
       </c>
       <c r="AO141" t="s" s="2">
-        <v>808</v>
+        <v>823</v>
       </c>
       <c r="AP141" t="s" s="2">
-        <v>809</v>
+        <v>824</v>
       </c>
       <c r="AQ141" t="s" s="2">
         <v>84</v>
@@ -20928,10 +20980,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>810</v>
+        <v>825</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -21052,10 +21104,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>811</v>
+        <v>826</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>811</v>
+        <v>826</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -21178,10 +21230,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>812</v>
+        <v>827</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>812</v>
+        <v>827</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -21204,16 +21256,16 @@
         <v>94</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>813</v>
+        <v>828</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>814</v>
+        <v>829</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>815</v>
+        <v>830</v>
       </c>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -21263,7 +21315,7 @@
         <v>84</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>816</v>
+        <v>831</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>82</v>
@@ -21272,7 +21324,7 @@
         <v>93</v>
       </c>
       <c r="AI144" t="s" s="2">
-        <v>817</v>
+        <v>832</v>
       </c>
       <c r="AJ144" t="s" s="2">
         <v>106</v>
@@ -21293,21 +21345,21 @@
         <v>84</v>
       </c>
       <c r="AP144" t="s" s="2">
-        <v>818</v>
+        <v>833</v>
       </c>
       <c r="AQ144" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR144" t="s" s="2">
-        <v>819</v>
+        <v>834</v>
       </c>
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>820</v>
+        <v>835</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21330,23 +21382,23 @@
         <v>94</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>821</v>
+        <v>836</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>822</v>
+        <v>837</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>823</v>
+        <v>838</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q145" t="s" s="2">
-        <v>824</v>
+        <v>839</v>
       </c>
       <c r="R145" t="s" s="2">
         <v>84</v>
@@ -21391,7 +21443,7 @@
         <v>84</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>825</v>
+        <v>840</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>82</v>
@@ -21400,13 +21452,13 @@
         <v>93</v>
       </c>
       <c r="AI145" t="s" s="2">
-        <v>817</v>
+        <v>832</v>
       </c>
       <c r="AJ145" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK145" t="s" s="2">
-        <v>826</v>
+        <v>841</v>
       </c>
       <c r="AL145" t="s" s="2">
         <v>84</v>
@@ -21421,21 +21473,21 @@
         <v>84</v>
       </c>
       <c r="AP145" t="s" s="2">
-        <v>827</v>
+        <v>842</v>
       </c>
       <c r="AQ145" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR145" t="s" s="2">
-        <v>828</v>
+        <v>843</v>
       </c>
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>829</v>
+        <v>844</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>829</v>
+        <v>844</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21458,16 +21510,16 @@
         <v>84</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>830</v>
+        <v>845</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>831</v>
+        <v>846</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>832</v>
+        <v>847</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>833</v>
+        <v>848</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" t="s" s="2">
@@ -21517,7 +21569,7 @@
         <v>84</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>829</v>
+        <v>844</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>82</v>
@@ -21544,24 +21596,24 @@
         <v>84</v>
       </c>
       <c r="AO146" t="s" s="2">
-        <v>834</v>
+        <v>849</v>
       </c>
       <c r="AP146" t="s" s="2">
-        <v>835</v>
+        <v>850</v>
       </c>
       <c r="AQ146" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR146" t="s" s="2">
-        <v>836</v>
+        <v>851</v>
       </c>
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>837</v>
+        <v>852</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>837</v>
+        <v>852</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21584,13 +21636,13 @@
         <v>84</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>684</v>
+        <v>699</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>838</v>
+        <v>853</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>839</v>
+        <v>854</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -21641,7 +21693,7 @@
         <v>84</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>837</v>
+        <v>852</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>82</v>
@@ -21668,24 +21720,24 @@
         <v>84</v>
       </c>
       <c r="AO147" t="s" s="2">
-        <v>840</v>
+        <v>855</v>
       </c>
       <c r="AP147" t="s" s="2">
-        <v>841</v>
+        <v>856</v>
       </c>
       <c r="AQ147" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR147" t="s" s="2">
-        <v>842</v>
+        <v>857</v>
       </c>
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>843</v>
+        <v>858</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>843</v>
+        <v>858</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21806,10 +21858,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>844</v>
+        <v>859</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>844</v>
+        <v>859</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21932,10 +21984,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>845</v>
+        <v>860</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>845</v>
+        <v>860</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -21958,19 +22010,19 @@
         <v>94</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>697</v>
+        <v>712</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>698</v>
+        <v>713</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>699</v>
+        <v>714</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>700</v>
+        <v>715</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>701</v>
+        <v>716</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>84</v>
@@ -22019,7 +22071,7 @@
         <v>84</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>702</v>
+        <v>717</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>82</v>
@@ -22034,13 +22086,13 @@
         <v>106</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>846</v>
+        <v>861</v>
       </c>
       <c r="AL150" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>847</v>
+        <v>862</v>
       </c>
       <c r="AN150" t="s" s="2">
         <v>84</v>
@@ -22049,21 +22101,21 @@
         <v>84</v>
       </c>
       <c r="AP150" t="s" s="2">
-        <v>704</v>
+        <v>719</v>
       </c>
       <c r="AQ150" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR150" t="s" s="2">
-        <v>705</v>
+        <v>720</v>
       </c>
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>848</v>
+        <v>863</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>848</v>
+        <v>863</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -22089,20 +22141,20 @@
         <v>114</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>708</v>
+        <v>723</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" t="s" s="2">
-        <v>710</v>
+        <v>725</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>84</v>
       </c>
       <c r="Q151" t="s" s="2">
-        <v>711</v>
+        <v>726</v>
       </c>
       <c r="R151" t="s" s="2">
         <v>84</v>
@@ -22123,13 +22175,13 @@
         <v>84</v>
       </c>
       <c r="X151" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Y151" t="s" s="2">
-        <v>712</v>
+        <v>727</v>
       </c>
       <c r="Z151" t="s" s="2">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>84</v>
@@ -22147,7 +22199,7 @@
         <v>84</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>714</v>
+        <v>729</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>82</v>
@@ -22177,21 +22229,21 @@
         <v>84</v>
       </c>
       <c r="AP151" t="s" s="2">
-        <v>715</v>
+        <v>730</v>
       </c>
       <c r="AQ151" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR151" t="s" s="2">
-        <v>716</v>
+        <v>731</v>
       </c>
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>849</v>
+        <v>864</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>849</v>
+        <v>864</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -22217,14 +22269,14 @@
         <v>153</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>719</v>
+        <v>734</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>720</v>
+        <v>735</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>721</v>
+        <v>736</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>84</v>
@@ -22273,7 +22325,7 @@
         <v>84</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>722</v>
+        <v>737</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>82</v>
@@ -22288,7 +22340,7 @@
         <v>106</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>850</v>
+        <v>865</v>
       </c>
       <c r="AL152" t="s" s="2">
         <v>84</v>
@@ -22303,21 +22355,21 @@
         <v>84</v>
       </c>
       <c r="AP152" t="s" s="2">
-        <v>725</v>
+        <v>740</v>
       </c>
       <c r="AQ152" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR152" t="s" s="2">
-        <v>726</v>
+        <v>741</v>
       </c>
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>851</v>
+        <v>866</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>851</v>
+        <v>866</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -22343,14 +22395,14 @@
         <v>108</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>729</v>
+        <v>744</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>730</v>
+        <v>745</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" t="s" s="2">
-        <v>731</v>
+        <v>746</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>84</v>
@@ -22399,7 +22451,7 @@
         <v>84</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>732</v>
+        <v>747</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>82</v>
@@ -22408,7 +22460,7 @@
         <v>93</v>
       </c>
       <c r="AI153" t="s" s="2">
-        <v>733</v>
+        <v>748</v>
       </c>
       <c r="AJ153" t="s" s="2">
         <v>106</v>
@@ -22429,21 +22481,21 @@
         <v>84</v>
       </c>
       <c r="AP153" t="s" s="2">
-        <v>734</v>
+        <v>749</v>
       </c>
       <c r="AQ153" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR153" t="s" s="2">
-        <v>726</v>
+        <v>741</v>
       </c>
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>852</v>
+        <v>867</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>852</v>
+        <v>867</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22469,16 +22521,16 @@
         <v>114</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>737</v>
+        <v>752</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="N154" t="s" s="2">
-        <v>739</v>
+        <v>754</v>
       </c>
       <c r="O154" t="s" s="2">
-        <v>740</v>
+        <v>755</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>84</v>
@@ -22527,7 +22579,7 @@
         <v>84</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>741</v>
+        <v>756</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>82</v>
@@ -22557,21 +22609,21 @@
         <v>84</v>
       </c>
       <c r="AP154" t="s" s="2">
-        <v>742</v>
+        <v>757</v>
       </c>
       <c r="AQ154" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR154" t="s" s="2">
-        <v>726</v>
+        <v>741</v>
       </c>
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>853</v>
+        <v>868</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>853</v>
+        <v>868</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -22594,16 +22646,16 @@
         <v>84</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>795</v>
+        <v>810</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>854</v>
+        <v>869</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>855</v>
+        <v>870</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>856</v>
+        <v>871</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -22653,7 +22705,7 @@
         <v>84</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>853</v>
+        <v>868</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>82</v>
@@ -22668,22 +22720,22 @@
         <v>106</v>
       </c>
       <c r="AK155" t="s" s="2">
-        <v>857</v>
+        <v>872</v>
       </c>
       <c r="AL155" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AM155" t="s" s="2">
-        <v>858</v>
+        <v>873</v>
       </c>
       <c r="AN155" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO155" t="s" s="2">
-        <v>859</v>
+        <v>874</v>
       </c>
       <c r="AP155" t="s" s="2">
-        <v>860</v>
+        <v>875</v>
       </c>
       <c r="AQ155" t="s" s="2">
         <v>84</v>
@@ -22694,10 +22746,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>861</v>
+        <v>876</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>861</v>
+        <v>876</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -22720,13 +22772,13 @@
         <v>84</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>862</v>
+        <v>877</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>863</v>
+        <v>878</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>864</v>
+        <v>879</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -22777,7 +22829,7 @@
         <v>84</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>861</v>
+        <v>876</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>82</v>
@@ -22807,10 +22859,10 @@
         <v>84</v>
       </c>
       <c r="AP156" t="s" s="2">
-        <v>865</v>
+        <v>880</v>
       </c>
       <c r="AQ156" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="AR156" t="s" s="2">
         <v>84</v>
@@ -22818,10 +22870,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>866</v>
+        <v>881</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>866</v>
+        <v>881</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -22844,13 +22896,13 @@
         <v>84</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>774</v>
+        <v>789</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>867</v>
+        <v>882</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>868</v>
+        <v>883</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -22901,7 +22953,7 @@
         <v>84</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>866</v>
+        <v>881</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>82</v>
@@ -22928,10 +22980,10 @@
         <v>84</v>
       </c>
       <c r="AO157" t="s" s="2">
-        <v>869</v>
+        <v>884</v>
       </c>
       <c r="AP157" t="s" s="2">
-        <v>870</v>
+        <v>885</v>
       </c>
       <c r="AQ157" t="s" s="2">
         <v>84</v>
@@ -22942,10 +22994,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>871</v>
+        <v>886</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>871</v>
+        <v>886</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -23066,10 +23118,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>872</v>
+        <v>887</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>872</v>
+        <v>887</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -23192,14 +23244,14 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>873</v>
+        <v>888</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>873</v>
+        <v>888</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="E160" s="2"/>
       <c r="F160" t="s" s="2">
@@ -23221,16 +23273,16 @@
         <v>139</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="N160" t="s" s="2">
         <v>182</v>
       </c>
       <c r="O160" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>84</v>
@@ -23279,7 +23331,7 @@
         <v>84</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>82</v>
@@ -23320,10 +23372,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>874</v>
+        <v>889</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>874</v>
+        <v>889</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23346,16 +23398,16 @@
         <v>84</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>875</v>
+        <v>890</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>876</v>
+        <v>891</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>877</v>
+        <v>892</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
@@ -23381,13 +23433,13 @@
         <v>84</v>
       </c>
       <c r="X161" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Y161" t="s" s="2">
-        <v>878</v>
+        <v>893</v>
       </c>
       <c r="Z161" t="s" s="2">
-        <v>879</v>
+        <v>894</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>84</v>
@@ -23405,7 +23457,7 @@
         <v>84</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>874</v>
+        <v>889</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>93</v>
@@ -23432,24 +23484,24 @@
         <v>84</v>
       </c>
       <c r="AO161" t="s" s="2">
-        <v>869</v>
+        <v>884</v>
       </c>
       <c r="AP161" t="s" s="2">
-        <v>880</v>
+        <v>895</v>
       </c>
       <c r="AQ161" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR161" t="s" s="2">
-        <v>881</v>
+        <v>896</v>
       </c>
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>882</v>
+        <v>897</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>882</v>
+        <v>897</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23472,13 +23524,13 @@
         <v>84</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>883</v>
+        <v>898</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>884</v>
+        <v>899</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
@@ -23505,13 +23557,13 @@
         <v>84</v>
       </c>
       <c r="X162" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Y162" t="s" s="2">
-        <v>885</v>
+        <v>900</v>
       </c>
       <c r="Z162" t="s" s="2">
-        <v>886</v>
+        <v>901</v>
       </c>
       <c r="AA162" t="s" s="2">
         <v>84</v>
@@ -23529,7 +23581,7 @@
         <v>84</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>882</v>
+        <v>897</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>82</v>
@@ -23556,24 +23608,24 @@
         <v>84</v>
       </c>
       <c r="AO162" t="s" s="2">
-        <v>887</v>
+        <v>902</v>
       </c>
       <c r="AP162" t="s" s="2">
-        <v>888</v>
+        <v>903</v>
       </c>
       <c r="AQ162" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR162" t="s" s="2">
-        <v>889</v>
+        <v>904</v>
       </c>
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>890</v>
+        <v>905</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>890</v>
+        <v>905</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -23596,13 +23648,13 @@
         <v>84</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>891</v>
+        <v>906</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>892</v>
+        <v>907</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>893</v>
+        <v>908</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -23653,7 +23705,7 @@
         <v>84</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>890</v>
+        <v>905</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>82</v>
@@ -23677,13 +23729,13 @@
         <v>84</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>894</v>
+        <v>909</v>
       </c>
       <c r="AO163" t="s" s="2">
-        <v>887</v>
+        <v>902</v>
       </c>
       <c r="AP163" t="s" s="2">
-        <v>895</v>
+        <v>910</v>
       </c>
       <c r="AQ163" t="s" s="2">
         <v>84</v>
@@ -23694,14 +23746,14 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>896</v>
+        <v>911</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>896</v>
+        <v>911</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
-        <v>897</v>
+        <v>912</v>
       </c>
       <c r="E164" s="2"/>
       <c r="F164" t="s" s="2">
@@ -23720,16 +23772,16 @@
         <v>84</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>898</v>
+        <v>913</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>899</v>
+        <v>914</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>900</v>
+        <v>915</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>901</v>
+        <v>916</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -23779,7 +23831,7 @@
         <v>84</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>896</v>
+        <v>911</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>82</v>
@@ -23809,7 +23861,7 @@
         <v>84</v>
       </c>
       <c r="AP164" t="s" s="2">
-        <v>902</v>
+        <v>917</v>
       </c>
       <c r="AQ164" t="s" s="2">
         <v>84</v>
@@ -23820,10 +23872,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>903</v>
+        <v>918</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>903</v>
+        <v>918</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -23846,16 +23898,16 @@
         <v>84</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>904</v>
+        <v>919</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>905</v>
+        <v>920</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>906</v>
+        <v>921</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>907</v>
+        <v>922</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -23905,7 +23957,7 @@
         <v>84</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>903</v>
+        <v>918</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>82</v>
@@ -23929,13 +23981,13 @@
         <v>84</v>
       </c>
       <c r="AN165" t="s" s="2">
-        <v>908</v>
+        <v>923</v>
       </c>
       <c r="AO165" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AP165" t="s" s="2">
-        <v>909</v>
+        <v>924</v>
       </c>
       <c r="AQ165" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
+++ b/docs/StructureDefinition-MedicationRequestOutpatientMedicationRequest.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
